--- a/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
+++ b/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
@@ -28962,8 +28962,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DecisionsTasks" displayName="DecisionsTasks" ref="A4:E20" totalsRowCount="1" headerRowDxfId="1946" headerRowBorderDxfId="1945">
-  <autoFilter ref="A4:E19" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DecisionsTasks" displayName="DecisionsTasks" ref="A4:E25" totalsRowCount="1" headerRowDxfId="1946" headerRowBorderDxfId="1945">
+  <autoFilter ref="A4:E24" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" totalsRowLabel="Totals" dataDxfId="1944"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Task or Decision" totalsRowFunction="count" totalsRowDxfId="1943"/>
@@ -29233,8 +29233,8 @@
 </file>
 
 <file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF13000000}" name="Table6" displayName="Table6" ref="A4:F21" totalsRowCount="1" headerRowDxfId="1481" dataDxfId="1479" headerRowBorderDxfId="1480" dataCellStyle="20% - Accent1">
-  <autoFilter ref="A4:F20" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF13000000}" name="Table6" displayName="Table6" ref="A4:F23" totalsRowCount="1" headerRowDxfId="1481" dataDxfId="1479" headerRowBorderDxfId="1480" dataCellStyle="20% - Accent1">
+  <autoFilter ref="A4:F22" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-1300-000001000000}" name="#" totalsRowLabel="Total" dataDxfId="1478" totalsRowDxfId="1477" dataCellStyle="20% - Accent1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-1300-000002000000}" name="Object Name" dataDxfId="1476" totalsRowDxfId="1475" dataCellStyle="20% - Accent1"/>
@@ -30016,7 +30016,7 @@
       <c r="F27" s="165"/>
       <c r="G27" s="165"/>
     </row>
-    <row r="28" ht="57.6" thickBot="1" x14ac:dyDescent="0.6" customHeight="1">
+    <row r="28" ht="72.0" thickBot="1" x14ac:dyDescent="0.6" customHeight="1">
       <c r="B28" s="212">
         <v>1.2</v>
       </c>
@@ -30030,7 +30030,7 @@
       </c>
       <c r="E28" s="214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala requirements - DRAFT for Design Workshop (27-Oct-2026). Sources: ILX App Overview 19-Oct-2026, Impala internal pre-design 20-Oct-2026, 'MOC Proposal.xlsx', SOW v1.5. Changes flagged A/R/M, highlighted in yellow, rationale in 'Impala Notes' columns. Open points marked [TBC].</t>
+          <t xml:space="preserve">Impala requirements - DRAFT for Design Workshop (27-Oct-2026). Sources: ILX App Overview 19-Oct-2026, Impala internal pre-design 20-Oct-2026, 'MOC Proposal.xlsx' (priority), BRD BO-61 v2.0 B.3 (complementary), SOW v1.5. Changes flagged A/R/M, highlighted in yellow, rationale in 'Impala Notes' columns. Open points marked [TBC].</t>
         </is>
       </c>
       <c r="F28" s="214" t="inlineStr">
@@ -30086,7 +30086,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="6.1015625" customWidth="1"/>
@@ -30534,18 +30534,94 @@
         </is>
       </c>
     </row>
-    <row r="21" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="159" t="s">
+    <row r="21" ht="43.2" customHeight="1">
+      <c r="A21" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AH16</t>
+        </is>
+      </c>
+      <c r="B21" s="272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="C21" s="272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporary change extension limit</t>
+        </is>
+      </c>
+      <c r="D21" s="272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Max 3 extensions (BRD RULE-B3-08).</t>
+        </is>
+      </c>
+      <c r="E21" s="272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Create, Update</t>
+        </is>
+      </c>
+      <c r="F21" s="273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If NumberOfExtensions &gt; 3
+• then error: 'A temporary change cannot be extended more than 3 times - raise a permanent MOC.'</t>
+        </is>
+      </c>
+      <c r="G21" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A - Impala requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="43.2" customHeight="1">
+      <c r="A22" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AH17</t>
+        </is>
+      </c>
+      <c r="B22" s="272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="C22" s="272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergency regularisation gate</t>
+        </is>
+      </c>
+      <c r="D22" s="272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergency MOC cannot close until regularised (BRD RULE-B3-14).</t>
+        </is>
+      </c>
+      <c r="E22" s="272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Update</t>
+        </is>
+      </c>
+      <c r="F22" s="273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If EmergencyChange = Yes and action = Close and (unanswered screening questions or open tasks)
+• then error: 'Complete the retrospective MOC dossier before closing.'</t>
+        </is>
+      </c>
+      <c r="G22" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A - Impala requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="159" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="159"/>
-      <c r="C21" s="160">
+      <c r="B23" s="159"/>
+      <c r="C23" s="160">
         <f>SUBTOTAL(103,Table6[Action Handler Name])</f>
         <v>13</v>
       </c>
-      <c r="D21" s="159"/>
-      <c r="E21" s="159"/>
-      <c r="F21" s="159"/>
+      <c r="D23" s="159"/>
+      <c r="E23" s="159"/>
+      <c r="F23" s="159"/>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -36391,7 +36467,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="29.5234375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -36744,15 +36820,120 @@
       </c>
       <c r="E19" s="52"/>
     </row>
-    <row r="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
+    <row r="20" ht="72.0" customHeight="1">
+      <c r="A20" s="217">
+        <v>16</v>
+      </c>
+      <c r="B20" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ratify deviations from approved BRD BO-61 v2.0 (B.3)</t>
+        </is>
+      </c>
+      <c r="C20" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Shaun Jones (MoC Process Owner)</t>
+        </is>
+      </c>
+      <c r="D20" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The 20-Oct design prevails but deviates from the approved BRD: (a) Level 0-5 scoring (FR-B3-006, RULE-B3-04) replaced by Type x Grade; (b) like-for-like exclusions not recorded in the system (FR-B3-002, Must) - rationale kept in the procedure; (c) Minor = single Terminal Manager approval vs RULE-B3-06 minimum of 2 approvers for Levels 0-3. Update Requirements Register BO61-203 and procedure CO-HS-GEN-PRO-002.</t>
+        </is>
+      </c>
+      <c r="E20" s="52"/>
+    </row>
+    <row r="21" ht="43.2" customHeight="1">
+      <c r="A21" s="217">
+        <v>17</v>
+      </c>
+      <c r="B21" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Return for revision vs formal rejection</t>
+        </is>
+      </c>
+      <c r="C21" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intelex - Ian</t>
+        </is>
+      </c>
+      <c r="D21" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-035 (Must): Roll Back from Approval = return for revision, closed approvals are KEPT; formal rejection resets the approval chain (RULE-B3-07). Intelex to confirm OOTB behaviour of approvals on Roll Back.</t>
+        </is>
+      </c>
+      <c r="E21" s="52"/>
+    </row>
+    <row r="22" ht="43.2" customHeight="1">
+      <c r="A22" s="217">
+        <v>18</v>
+      </c>
+      <c r="B22" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergency MOC regularisation</t>
+        </is>
+      </c>
+      <c r="C22" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Shaun Jones</t>
+        </is>
+      </c>
+      <c r="D22" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD RULE-B3-14: single senior approval, immediate execution, full dossier (checklist, tasks) completed retrospectively within [TBC] days; record flagged 'pending regularisation' and reported overdue; cannot be closed until regularised (AH17).</t>
+        </is>
+      </c>
+      <c r="E22" s="52"/>
+    </row>
+    <row r="23" ht="43.2" customHeight="1">
+      <c r="A23" s="217">
+        <v>19</v>
+      </c>
+      <c r="B23" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporary change extensions</t>
+        </is>
+      </c>
+      <c r="C23" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
+        </is>
+      </c>
+      <c r="D23" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD RULE-B3-08 / FR-B3-014: review date, max 3 extensions each with rationale and re-approval at the MOC grade (ad hoc approval); conversion to permanent = new MOC linked through Related MOCs.</t>
+        </is>
+      </c>
+      <c r="E23" s="52"/>
+    </row>
+    <row r="24" ht="43.2" customHeight="1">
+      <c r="A24" s="217">
+        <v>20</v>
+      </c>
+      <c r="B24" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MoC KPIs and leadership reporting</t>
+        </is>
+      </c>
+      <c r="C24" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Rodrigo Llamas</t>
+        </is>
+      </c>
+      <c r="D24" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-019 / FR-B3-033: monthly YTD permanent/temporary MOCs, open MOCs, overdue temporary MOCs, MoC-related incidents, open MoC actions + leading indicators. To be built as reports/dashboards (reporting phase), fields already captured in this workbook.</t>
+        </is>
+      </c>
+      <c r="E24" s="52"/>
+    </row>
+    <row r="25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B25" s="29">
         <f>SUBTOTAL(103,DecisionsTasks[Task or Decision])</f>
         <v>2</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E25" s="29">
         <f>SUBTOTAL(103,DecisionsTasks[Date Complete])</f>
         <v>0</v>
       </c>
@@ -37012,7 +37193,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="158.4" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="72" ht="187.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A72" s="136">
         <v>3</v>
       </c>
@@ -37056,7 +37237,8 @@
 - Major: Local &gt; Regional &gt; Global HSEC + Global Operations [TBC Regional step for Major]
 Approvals are SEQUENTIAL: next level requested only when the previous level is closed (Intelex to confirm solution).
 Ad hoc approvers can be added by the MOC Coordinator.
-Prior to transitioning: at least one approval exists and all approvals are closed (accepted).</t>
+Prior to transitioning: at least one approval exists and all approvals are closed (accepted).
+Roll Back = return for revision, closed approvals are kept; a formal rejection resets the chain (BRD FR-B3-035) [Intelex to confirm].</t>
         </is>
       </c>
       <c r="J72" s="239" t="inlineStr">
@@ -37108,7 +37290,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="28.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="75" ht="72.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A75" s="139">
         <v>4</v>
       </c>
@@ -37142,7 +37324,8 @@
       <c r="I75" s="223" t="inlineStr">
         <is>
           <t xml:space="preserve">Recipient(s): Change Requester
-Prior to transitioning to next stage, all tasks have to be completed.</t>
+Prior to transitioning to next stage, all tasks have to be completed.
+Tasks of this stage = pre-startup actions (incl. PSSR where required by Type/Grade): Start Up is blocked until they are closed (BRD FR-B3-028 / FR-B3-032). Post-startup actions are created in Follow Up.</t>
         </is>
       </c>
     </row>
@@ -37268,7 +37451,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="72.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="81" ht="129.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A81" s="139">
         <v>6</v>
       </c>
@@ -37304,7 +37487,9 @@
           <t xml:space="preserve">Recipient(s): Change Requester
 Prior to closing:
 - All tasks and approvals have to be completed.
-- If 'Temporary Change' = Yes, then 'Has Temporary Change been scheduled for permanent MOC?' must be 'Yes' (or temporary change removed).</t>
+- If 'Temporary Change' = Yes, then 'Has Temporary Change been scheduled for permanent MOC?' must be 'Yes' (or temporary change removed).
+- If 'Emergency Change' = Yes: all screening questions answered and tasks closed (retrospective regularisation, BRD RULE-B3-14).
+- Post-MoC verification fields completed (field check, communication, downstream impacts).</t>
         </is>
       </c>
     </row>
@@ -38716,7 +38901,7 @@
         </is>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.55000000000000004" ht="14.4" customHeight="1">
+    <row r="9" x14ac:dyDescent="0.55000000000000004" ht="28.8" customHeight="1">
       <c r="A9" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">Regional Operations Manager</t>
@@ -38744,11 +38929,11 @@
       </c>
       <c r="F9" s="250" t="inlineStr">
         <is>
-          <t xml:space="preserve">A - Regional approval level.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="14.4" customHeight="1">
+          <t xml:space="preserve">A - Regional approval level. BRD FR-B3-007: ROM / Country Operations Manager.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28.8" customHeight="1">
       <c r="A10" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">Global HSEC</t>
@@ -38776,11 +38961,11 @@
       </c>
       <c r="F10" s="250" t="inlineStr">
         <is>
-          <t xml:space="preserve">A - Global approval level (assigned at top location).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" x14ac:dyDescent="0.55000000000000004" ht="14.4" customHeight="1">
+          <t xml:space="preserve">A - Global approval level (assigned at top location). BRD FR-B3-007: Head of HSEQ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" x14ac:dyDescent="0.55000000000000004" ht="28.8" customHeight="1">
       <c r="A11" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Operations</t>
@@ -38808,7 +38993,7 @@
       </c>
       <c r="F11" s="250" t="inlineStr">
         <is>
-          <t xml:space="preserve">A - Global approval level (assigned at top location).</t>
+          <t xml:space="preserve">A - Global approval level (assigned at top location). BRD FR-B3-007: COO.</t>
         </is>
       </c>
     </row>
@@ -40072,7 +40257,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AC341"/>
+  <dimension ref="A1:AC354"/>
   <sheetFormatPr defaultColWidth="26.41796875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.89453125" style="64" customWidth="1"/>
@@ -56899,6 +57084,1575 @@
       <c r="AA341" s="256" t="inlineStr">
         <is>
           <t xml:space="preserve">Alonso / Sam: traceability of actions back to the MOC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="57.6" customHeight="1">
+      <c r="A342" s="253">
+        <v>10</v>
+      </c>
+      <c r="B342" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C342" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D342" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E342" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change Owner</t>
+        </is>
+      </c>
+      <c r="F342" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change Owner</t>
+        </is>
+      </c>
+      <c r="G342" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accountable for the change through to closure.</t>
+        </is>
+      </c>
+      <c r="H342" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Relations</t>
+        </is>
+      </c>
+      <c r="I342" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: Person accountable for the change until closure (may be the requester).</t>
+        </is>
+      </c>
+      <c r="J342" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M:1 relation to Employee. Default Value: Change Requester.</t>
+        </is>
+      </c>
+      <c r="K342" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L342" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M342" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O342" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P342" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA342" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-026 (Should) / FR-B3-004: originator vs owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="43.2" customHeight="1">
+      <c r="A343" s="253">
+        <v>11</v>
+      </c>
+      <c r="B343" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C343" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D343" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E343" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operational Owner</t>
+        </is>
+      </c>
+      <c r="F343" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operational Owner</t>
+        </is>
+      </c>
+      <c r="G343" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Owner of the affected area or asset.</t>
+        </is>
+      </c>
+      <c r="H343" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Relations</t>
+        </is>
+      </c>
+      <c r="I343" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: Responsible for operational readiness before start-up.</t>
+        </is>
+      </c>
+      <c r="J343" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M:1 relation to Employee.</t>
+        </is>
+      </c>
+      <c r="K343" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L343" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M343" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O343" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P343" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA343" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-004 (Must).</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="57.6" customHeight="1">
+      <c r="A344" s="253">
+        <v>12</v>
+      </c>
+      <c r="B344" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C344" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D344" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E344" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason for Change &amp; Technical Basis</t>
+        </is>
+      </c>
+      <c r="F344" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason for Change &amp; Technical Basis</t>
+        </is>
+      </c>
+      <c r="G344" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detailed justification.</t>
+        </is>
+      </c>
+      <c r="H344" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text (multi-line)</t>
+        </is>
+      </c>
+      <c r="I344" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: Why the change is needed, technical basis, scope and current situation.</t>
+        </is>
+      </c>
+      <c r="J344" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No length limit.</t>
+        </is>
+      </c>
+      <c r="K344" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L344" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M344" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O344" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P344" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA344" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-001 (Must); Change Description is limited to 255 characters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="28.8" customHeight="1">
+      <c r="A345" s="253">
+        <v>13</v>
+      </c>
+      <c r="B345" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C345" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D345" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E345" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Affected Equipment / Process / System</t>
+        </is>
+      </c>
+      <c r="F345" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Affected Equipment / Process / System</t>
+        </is>
+      </c>
+      <c r="G345" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What the change touches.</t>
+        </is>
+      </c>
+      <c r="H345" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="I345" s="254"/>
+      <c r="J345" s="256"/>
+      <c r="K345" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L345" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M345" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O345" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P345" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA345" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-001 (Must).</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="57.6" customHeight="1">
+      <c r="A346" s="253">
+        <v>14</v>
+      </c>
+      <c r="B346" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C346" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D346" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E346" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporary Change Review Date</t>
+        </is>
+      </c>
+      <c r="F346" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporary Change Review Date</t>
+        </is>
+      </c>
+      <c r="G346" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Next review of the temporary change.</t>
+        </is>
+      </c>
+      <c r="H346" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="I346" s="254"/>
+      <c r="J346" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible and mandatory if Temporary Change = Yes. Must be on or before Change Expiry.</t>
+        </is>
+      </c>
+      <c r="K346" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L346" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M346" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O346" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P346" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="S346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="U346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="W346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="AA346" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-003 / FR-B3-014 (Must).</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="43.2" customHeight="1">
+      <c r="A347" s="253">
+        <v>15</v>
+      </c>
+      <c r="B347" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow Up</t>
+        </is>
+      </c>
+      <c r="C347" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D347" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow-Up Details</t>
+        </is>
+      </c>
+      <c r="E347" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number of Extensions</t>
+        </is>
+      </c>
+      <c r="F347" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number of Extensions</t>
+        </is>
+      </c>
+      <c r="G347" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Times the temporary change has been extended.</t>
+        </is>
+      </c>
+      <c r="H347" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Number</t>
+        </is>
+      </c>
+      <c r="I347" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: Each extension needs a rationale and re-approval at the MOC grade.</t>
+        </is>
+      </c>
+      <c r="J347" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible if Temporary Change = Yes. Max 3 (AH16).</t>
+        </is>
+      </c>
+      <c r="K347" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L347" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M347" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O347" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P347" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="S347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="U347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="W347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="AA347" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD RULE-B3-08 (Must).</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="28.8" customHeight="1">
+      <c r="A348" s="253">
+        <v>16</v>
+      </c>
+      <c r="B348" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow Up</t>
+        </is>
+      </c>
+      <c r="C348" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D348" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow-Up Details</t>
+        </is>
+      </c>
+      <c r="E348" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extension Rationale</t>
+        </is>
+      </c>
+      <c r="F348" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extension Rationale</t>
+        </is>
+      </c>
+      <c r="G348" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Why the temporary change is extended.</t>
+        </is>
+      </c>
+      <c r="H348" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="I348" s="254"/>
+      <c r="J348" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible and mandatory if Number of Extensions &gt; 0.</t>
+        </is>
+      </c>
+      <c r="K348" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L348" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M348" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N348" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O348" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P348" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q348" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R348" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="S348" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T348" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="U348" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V348" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="W348" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X348" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="AA348" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-003 (Must).</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="57.6" customHeight="1">
+      <c r="A349" s="253">
+        <v>17</v>
+      </c>
+      <c r="B349" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C349" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D349" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E349" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regularisation Due Date</t>
+        </is>
+      </c>
+      <c r="F349" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regularisation Due Date</t>
+        </is>
+      </c>
+      <c r="G349" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deadline to complete the emergency MOC dossier.</t>
+        </is>
+      </c>
+      <c r="H349" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date (calculated, read-only)</t>
+        </is>
+      </c>
+      <c r="I349" s="254"/>
+      <c r="J349" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible if Emergency Change = Yes. = date of approval + [TBC] days. Overdue flag in reports.</t>
+        </is>
+      </c>
+      <c r="K349" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L349" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M349" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N349" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O349" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P349" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q349" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R349" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S349" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T349" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U349" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V349" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W349" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X349" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA349" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD RULE-B3-14 / FR-B3-015 (Must).</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="28.8" customHeight="1">
+      <c r="A350" s="253">
+        <v>18</v>
+      </c>
+      <c r="B350" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
+        </is>
+      </c>
+      <c r="C350" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D350" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis Details</t>
+        </is>
+      </c>
+      <c r="E350" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed Implementation Plan</t>
+        </is>
+      </c>
+      <c r="F350" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proposed Implementation Plan</t>
+        </is>
+      </c>
+      <c r="G350" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How and when the change will be implemented.</t>
+        </is>
+      </c>
+      <c r="H350" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text (multi-line)</t>
+        </is>
+      </c>
+      <c r="I350" s="254"/>
+      <c r="J350" s="256"/>
+      <c r="K350" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L350" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M350" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N350" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O350" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P350" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q350" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R350" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S350" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T350" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U350" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V350" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W350" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X350" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA350" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-001 (Must).</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="72.0" customHeight="1">
+      <c r="A351" s="253">
+        <v>19</v>
+      </c>
+      <c r="B351" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
+        </is>
+      </c>
+      <c r="C351" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D351" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis Details</t>
+        </is>
+      </c>
+      <c r="E351" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Affected Personnel / Groups</t>
+        </is>
+      </c>
+      <c r="F351" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Affected Personnel / Groups</t>
+        </is>
+      </c>
+      <c r="G351" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People or groups to inform and train.</t>
+        </is>
+      </c>
+      <c r="H351" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="I351" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: e.g. all operators at the terminal, maintenance contractor. Create Change Communication and Training tasks.</t>
+        </is>
+      </c>
+      <c r="J351" s="256"/>
+      <c r="K351" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L351" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M351" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N351" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O351" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P351" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q351" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R351" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S351" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T351" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U351" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V351" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W351" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X351" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA351" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-016 (Must) / RULE-B3-10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="28.8" customHeight="1">
+      <c r="A352" s="253">
+        <v>20</v>
+      </c>
+      <c r="B352" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow Up</t>
+        </is>
+      </c>
+      <c r="C352" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D352" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow-Up Details</t>
+        </is>
+      </c>
+      <c r="E352" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field Verification (walk-around) Completed?</t>
+        </is>
+      </c>
+      <c r="F352" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field Verification (walk-around) Completed?</t>
+        </is>
+      </c>
+      <c r="G352" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post-MoC field check.</t>
+        </is>
+      </c>
+      <c r="H352" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No</t>
+        </is>
+      </c>
+      <c r="I352" s="254"/>
+      <c r="J352" s="256"/>
+      <c r="K352" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L352" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M352" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N352" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O352" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P352" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q352" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R352" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="S352" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T352" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="U352" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V352" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="W352" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="X352" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="AA352" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-012 (Must).</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="28.8" customHeight="1">
+      <c r="A353" s="253">
+        <v>21</v>
+      </c>
+      <c r="B353" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow Up</t>
+        </is>
+      </c>
+      <c r="C353" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D353" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow-Up Details</t>
+        </is>
+      </c>
+      <c r="E353" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Affected Personnel Interviewed / Communication Confirmed?</t>
+        </is>
+      </c>
+      <c r="F353" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Affected Personnel Interviewed / Communication Confirmed?</t>
+        </is>
+      </c>
+      <c r="G353" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post-MoC communication check.</t>
+        </is>
+      </c>
+      <c r="H353" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No</t>
+        </is>
+      </c>
+      <c r="I353" s="254"/>
+      <c r="J353" s="256"/>
+      <c r="K353" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L353" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M353" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N353" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O353" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P353" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q353" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R353" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="S353" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T353" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="U353" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V353" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="W353" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="X353" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="AA353" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-012 (Must).</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="28.8" customHeight="1">
+      <c r="A354" s="253">
+        <v>22</v>
+      </c>
+      <c r="B354" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow Up</t>
+        </is>
+      </c>
+      <c r="C354" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D354" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow-Up Details</t>
+        </is>
+      </c>
+      <c r="E354" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downstream &amp; Cumulative Impacts Reviewed?</t>
+        </is>
+      </c>
+      <c r="F354" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Downstream &amp; Cumulative Impacts Reviewed?</t>
+        </is>
+      </c>
+      <c r="G354" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post-MoC impact review.</t>
+        </is>
+      </c>
+      <c r="H354" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No</t>
+        </is>
+      </c>
+      <c r="I354" s="254"/>
+      <c r="J354" s="256"/>
+      <c r="K354" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L354" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M354" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O354" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P354" s="267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="S354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="U354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="W354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="X354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="AA354" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-012 (Must).</t>
         </is>
       </c>
     </row>

--- a/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
+++ b/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
@@ -36626,7 +36626,7 @@
       </c>
       <c r="D10" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROPOSED (20-Oct): Minor = Local (TM), Moderate = Regional (HSEC + Ops), Major = Global (HSEC + Ops). Grade descriptors per type + 'Automatic Major' list (floating roof/deck landing, tank entry, SCE...). Pending sign-off by Global HSE (Stylianos). Procedure update + retraining required.</t>
+          <t xml:space="preserve">AGREED internally (20-Oct), per 'MOC Proposal.xlsx' (Sam): Minor = Local (TM), Moderate = Regional (HSEC + Ops), Major = Global (HSEC + Ops). Grade descriptors per type + 'Automatic Major' examples. Sam to circulate the updated matrix; Shaun to explain the rationale to Stylianos (internal alignment, not a configuration blocker). Procedure update + retraining required.</t>
         </is>
       </c>
       <c r="E10" s="52"/>
@@ -36826,17 +36826,17 @@
       </c>
       <c r="B20" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ratify deviations from approved BRD BO-61 v2.0 (B.3)</t>
+          <t xml:space="preserve">Minimum number of approvers per grade</t>
         </is>
       </c>
       <c r="C20" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Shaun Jones (MoC Process Owner)</t>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
         </is>
       </c>
       <c r="D20" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">The 20-Oct design prevails but deviates from the approved BRD: (a) Level 0-5 scoring (FR-B3-006, RULE-B3-04) replaced by Type x Grade; (b) like-for-like exclusions not recorded in the system (FR-B3-002, Must) - rationale kept in the procedure; (c) Minor = single Terminal Manager approval vs RULE-B3-06 minimum of 2 approvers for Levels 0-3. Update Requirements Register BO61-203 and procedure CO-HS-GEN-PRO-002.</t>
+          <t xml:space="preserve">OPEN (internal workshop 21-Oct): 'MOC Proposal' defines the approval LEVEL per grade (Minor = Local - TM) but not the NUMBER of approvers. Current procedure/BRD: min. 2 approvers for lower levels, 3 for the highest. Confirm the rule to give Intelex. Note: Sam's design replaces Level 0-5 scoring and removes like-for-like from the module; BRD BO-61 to be updated accordingly (housekeeping).</t>
         </is>
       </c>
       <c r="E20" s="52"/>

--- a/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
+++ b/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
@@ -30799,7 +30799,7 @@
       </c>
       <c r="N6" s="275" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - columns: Replacement in Kind removed; Type of Change + Grade of Change. Grouping by Status instead of Category [TBC].</t>
+          <t xml:space="preserve">M - columns: Replacement in Kind removed (unless re-used as 'Simplified MOC?' [TBC]); Type of Change + Grade of Change. Grouping by Status instead of Category [TBC].</t>
         </is>
       </c>
     </row>
@@ -36547,23 +36547,23 @@
       </c>
       <c r="E6" s="52"/>
     </row>
-    <row r="7" x14ac:dyDescent="0.55000000000000004" ht="28.8" customHeight="1">
+    <row r="7" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
       <c r="A7" s="5">
         <v>3</v>
       </c>
       <c r="B7" s="215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove 'Replacement in Kind' (field and workflow path)</t>
+          <t xml:space="preserve">Replacement in Kind: remove or re-use as 'Simplified MOC' route</t>
         </is>
       </c>
       <c r="C7" s="215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Sam Robinson</t>
+          <t xml:space="preserve">Impala - Sam Robinson / Rodrigo Llamas</t>
         </is>
       </c>
       <c r="D7" s="215" t="inlineStr">
         <is>
-          <t xml:space="preserve">DECIDED (Impala internal 20-Oct). Per Impala MoC procedure a like-for-like replacement is not a change, so it is out of MoC scope.</t>
+          <t xml:space="preserve">ON HOLD (internal workshop 21-Oct). 20-Oct: like-for-like is not a change per procedure, so the field as such is not needed. But its OOTB skip-path could be re-captioned (e.g. 'Simplified MOC?') to give the simplified route for organisational / IT changes without a new workflow. Decide: remove, or re-use (and define which stages it skips).</t>
         </is>
       </c>
       <c r="E7" s="52"/>
@@ -37103,7 +37103,7 @@
       </c>
       <c r="J68" s="239" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - Impala proposal (internal pre-design 20-Oct-2026, 'MOC Proposal.xlsx'). 6 stages instead of 7. Replacement in Kind path removed. The diagram above shows the OOTB workflow and must be redrawn by Intelex.</t>
+          <t xml:space="preserve">M - Impala proposal (internal pre-design 20-Oct-2026, 'MOC Proposal.xlsx'). 6 stages instead of 7. Replacement in Kind path ON HOLD: may be re-used as the 'Simplified MOC' route [TBC]. The diagram above shows the OOTB workflow and must be redrawn by Intelex.</t>
         </is>
       </c>
     </row>
@@ -41348,12 +41348,14 @@
       <c r="I16" s="187" t="s">
         <v>564</v>
       </c>
-      <c r="J16" s="187" t="s">
-        <v>565</v>
+      <c r="J16" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[TBC] Remove, or re-caption as 'Simplified MOC?' re-using the OOTB skip path (organisational / IT changes).</t>
+        </is>
       </c>
       <c r="K16" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
+          <t xml:space="preserve">M</t>
         </is>
       </c>
       <c r="L16" s="187" t="s">
@@ -41403,7 +41405,7 @@
       <c r="Z16" s="253"/>
       <c r="AA16" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Out of MoC scope per Impala procedure (like-for-like is not a change). Remove field and workflow path.</t>
+          <t xml:space="preserve">ON HOLD: like-for-like is out of MoC scope, but the field/path may become the simplified-MOC switch (decision 21-Oct).</t>
         </is>
       </c>
       <c r="AB16" s="61"/>

--- a/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
+++ b/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
@@ -6573,6 +6573,9 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="10" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyFill="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -6596,9 +6599,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyAlignment="1" applyFill="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -28962,8 +28962,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DecisionsTasks" displayName="DecisionsTasks" ref="A4:E25" totalsRowCount="1" headerRowDxfId="1946" headerRowBorderDxfId="1945">
-  <autoFilter ref="A4:E24" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DecisionsTasks" displayName="DecisionsTasks" ref="A4:E30" totalsRowCount="1" headerRowDxfId="1946" headerRowBorderDxfId="1945">
+  <autoFilter ref="A4:E29" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" totalsRowLabel="Totals" dataDxfId="1944"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Task or Decision" totalsRowFunction="count" totalsRowDxfId="1943"/>
@@ -29471,8 +29471,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table5" displayName="Table5" ref="A5:E12" totalsRowCount="1" headerRowDxfId="1907" dataDxfId="1905" headerRowBorderDxfId="1906" dataCellStyle="20% - Accent1">
-  <autoFilter ref="A5:E11" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table5" displayName="Table5" ref="A5:E13" totalsRowCount="1" headerRowDxfId="1907" dataDxfId="1905" headerRowBorderDxfId="1906" dataCellStyle="20% - Accent1">
+  <autoFilter ref="A5:E12" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Role Name" totalsRowLabel="Total" dataDxfId="1904" totalsRowDxfId="1903" dataCellStyle="20% - Accent1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Description" dataDxfId="1902" totalsRowDxfId="1901" dataCellStyle="20% - Accent1"/>
@@ -30030,7 +30030,7 @@
       </c>
       <c r="E28" s="214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala requirements - DRAFT for Design Workshop (27-Oct-2026). Sources: ILX App Overview 19-Oct-2026, Impala internal pre-design 20-Oct-2026, 'MOC Proposal.xlsx' (priority), BRD BO-61 v2.0 B.3 (complementary), SOW v1.5. Changes flagged A/R/M, highlighted in yellow, rationale in 'Impala Notes' columns. Open points marked [TBC].</t>
+          <t xml:space="preserve">Impala requirements - DRAFT for Design Workshop (27-Oct-2026). Sources: ILX App Overview 19-Oct-2026, Impala internal pre-design sessions 20-Oct and 21-Oct-2026, 'MOC Proposal.xlsx' (priority), BRD BO-61 v2.0 B.3 (complementary), SOW v1.5. Changes flagged A/R/M, highlighted in yellow, rationale in 'Impala Notes' columns. Open points marked [TBC].</t>
         </is>
       </c>
       <c r="F28" s="214" t="inlineStr">
@@ -31561,7 +31561,7 @@
       </c>
       <c r="H14" s="250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approval object captions change (Local / Regional / Global) - permissions unchanged.</t>
+          <t xml:space="preserve">Approval types to be adapted (functional + level approvals) - permissions per type unchanged.</t>
         </is>
       </c>
     </row>
@@ -36467,7 +36467,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="29.5234375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -36547,7 +36547,7 @@
       </c>
       <c r="E6" s="52"/>
     </row>
-    <row r="7" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
+    <row r="7" x14ac:dyDescent="0.55000000000000004" ht="72.0" customHeight="1">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -36563,12 +36563,12 @@
       </c>
       <c r="D7" s="215" t="inlineStr">
         <is>
-          <t xml:space="preserve">ON HOLD (internal workshop 21-Oct). 20-Oct: like-for-like is not a change per procedure, so the field as such is not needed. But its OOTB skip-path could be re-captioned (e.g. 'Simplified MOC?') to give the simplified route for organisational / IT changes without a new workflow. Decide: remove, or re-use (and define which stages it skips).</t>
+          <t xml:space="preserve">STILL OPEN after 21-Oct (Sam: 'remove it or use it for a simplified workflow, come back to that'). 20-Oct: like-for-like is not a change per procedure, so the field as such is not needed. But its OOTB skip-path could be re-captioned (e.g. 'Simplified MOC?') to give the simplified route for organisational / IT changes without a new workflow. Decide: remove, or re-use (and define which stages it skips).</t>
         </is>
       </c>
       <c r="E7" s="52"/>
     </row>
-    <row r="8" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
+    <row r="8" x14ac:dyDescent="0.55000000000000004" ht="72.0" customHeight="1">
       <c r="A8" s="5">
         <v>4</v>
       </c>
@@ -36584,12 +36584,12 @@
       </c>
       <c r="D8" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">DECIDED by Impala (20-Oct): remove Pre-Approval, merge Evaluation + Design &amp; Analysis, new Approval stage before Implementation, Emergency goes Initiation &gt; Approval. Intelex to confirm it fits SOW 'Moderate configuration' (minor modification of stages) - no Change Order expected by Impala.</t>
+          <t xml:space="preserve">CONFIRMED 21-Oct (Shaun: 'the workflow looks good'): remove Pre-Approval, merge Evaluation + Design &amp; Analysis, ONE main approval stage before Implementation (approve before construction/activity starts); pre-startup checks handled locally. Emergency route not discussed yet. Intelex to confirm it fits SOW 'Moderate configuration' (minor modification of stages) - no Change Order expected by Impala.</t>
         </is>
       </c>
       <c r="E8" s="52"/>
     </row>
-    <row r="9" x14ac:dyDescent="0.55000000000000004" ht="43.2" customHeight="1">
+    <row r="9" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -36605,12 +36605,12 @@
       </c>
       <c r="D9" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">REQUIRED: Terminal Manager approves first; Regional approvals only requested after Local is closed; Global only after Regional. OOTB approvals are not ordered. Intelex to propose solution (native ordering, sub-stages or action handler) and scope impact.</t>
+          <t xml:space="preserve">CONFIRMED 21-Oct: Major = Local &gt; Regional &gt; Global; as soon as the TM approves, the next level must be added and triggered AUTOMATICALLY (Sam: 'leave less down to human error'), not entered manually by the TM. OOTB approvals are not ordered. Intelex to propose solution (native ordering, sub-stages or action handler) and scope impact.</t>
         </is>
       </c>
       <c r="E9" s="52"/>
     </row>
-    <row r="10" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
+    <row r="10" x14ac:dyDescent="0.55000000000000004" ht="100.8" customHeight="1">
       <c r="A10" s="5">
         <v>6</v>
       </c>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="D10" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGREED internally (20-Oct), per 'MOC Proposal.xlsx' (Sam): Minor = Local (TM), Moderate = Regional (HSEC + Ops), Major = Global (HSEC + Ops). Grade descriptors per type + 'Automatic Major' examples. Sam to circulate the updated matrix; Shaun to explain the rationale to Stylianos (internal alignment, not a configuration blocker). Procedure update + retraining required.</t>
+          <t xml:space="preserve">21-Oct: Change Impact linked to the category (= type of change); matrix covers grade of change AND grade of hazard, so no scoring needed. Matrix OUT FOR TEAM REVIEW (check nothing previously Level 4 now comes out Minor). Per 'MOC Proposal.xlsx' (Sam): Minor = Local (TM), Moderate = Regional (HSEC + Ops), Major = Global (HSEC + Ops). Grade descriptors per type + 'Automatic Major' examples. Sam to circulate the updated matrix; Shaun to explain the rationale to Stylianos (internal alignment, not a configuration blocker). Procedure update + retraining required.</t>
         </is>
       </c>
       <c r="E10" s="52"/>
     </row>
-    <row r="11" x14ac:dyDescent="0.55000000000000004" ht="43.2" customHeight="1">
+    <row r="11" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -36647,39 +36647,39 @@
       </c>
       <c r="D11" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Checklist 'Evaluation, D&amp;A Checklist' loaded as screening questions (Excel import). Part 1 at top location, Part 2 at Liquids segment, Part 3 at Dry segment. Open: reduce question set by Grade (Minor short list, Major full) [TBC]. Location-specific checklists = Phase 2.</t>
+          <t xml:space="preserve">Checklist 'Evaluation, D&amp;A Checklist' loaded as screening questions (Excel import). Part 1 at top location, Part 2 at Liquids segment, Part 3 at Dry segment (triggered by location - confirmed 21-Oct). List under team review. OPEN: same checklist for all changes, or questions shown only for certain types of change [TBC]. Location-specific checklists = Phase 2.</t>
         </is>
       </c>
       <c r="E11" s="52"/>
     </row>
-    <row r="12" x14ac:dyDescent="0.55000000000000004" ht="43.2" customHeight="1">
+    <row r="12" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
       <c r="A12" s="5">
         <v>8</v>
       </c>
       <c r="B12" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link Action Plans to the MOC</t>
+          <t xml:space="preserve">MOC Tasks vs Action Plans</t>
         </is>
       </c>
       <c r="C12" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelex - Ian</t>
+          <t xml:space="preserve">Impala - Shaun Jones / Intelex - Ian</t>
         </is>
       </c>
       <c r="D12" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">REQUIRED: actions arising from the MOC (permits, licences, site checks) raised as Action Plans with traceability back to the MOC No. (grid on MOC). Intelex to confirm feasibility (Action Plans in Phase 1 scope).</t>
+          <t xml:space="preserve">21-Oct: keep MOC TASKS as the MOC actions (Shaun: tasks are part of the MOC; if overdue, the MOC is overdue). Sam would prefer Action Plans (single overdue-actions reporting) but is 'happy either way'; Alonso: replacing tasks with Action Plans is probably not a minor change. Ask Intelex only for effort of an Action Plans link (nice-to-have).</t>
         </is>
       </c>
       <c r="E12" s="52"/>
     </row>
-    <row r="13" x14ac:dyDescent="0.55000000000000004" ht="43.2" customHeight="1">
+    <row r="13" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
       <c r="A13" s="5">
         <v>9</v>
       </c>
       <c r="B13" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simplified MOC workflow (organisational / IT changes)</t>
+          <t xml:space="preserve">Task completion stage (pre-startup vs post-startup)</t>
         </is>
       </c>
       <c r="C13" s="216" t="inlineStr">
@@ -36689,39 +36689,39 @@
       </c>
       <c r="D13" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN: Intelex to confirm whether the simplified/'Change Request' workflow seen in the demo site is in SOW. Impala priority: finalise the full MOC first; Emergency kept minimal (low volume).</t>
+          <t xml:space="preserve">REQUIRED 21-Oct (Khesar / Sam): OOTB a stage cannot be submitted with open tasks, but some tasks identified in Evaluation are only due later (e.g. P&amp;ID update post-change). Add on each MOC Task a 'Complete before stage' field (Implementation / Start Up / Follow Up); the stage gate checks only tasks due for that stage. Covers BRD FR-B3-032.</t>
         </is>
       </c>
       <c r="E13" s="52"/>
     </row>
-    <row r="14" x14ac:dyDescent="0.55000000000000004" ht="43.2" customHeight="1">
+    <row r="14" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
       <c r="A14" s="5">
         <v>10</v>
       </c>
       <c r="B14" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage gating rules</t>
+          <t xml:space="preserve">Local (Minor) approval: no single-person MOC</t>
         </is>
       </c>
       <c r="C14" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Sam Robinson</t>
+          <t xml:space="preserve">Impala - Shaun Jones</t>
         </is>
       </c>
       <c r="D14" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">REQUIRED: OOTB nothing forces tasks/approvals per stage. Proposed: all screening questions answered + stage tasks closed before Approval; at least one approval (Local) and all approvals closed before Implementation.</t>
+          <t xml:space="preserve">21-Oct (Shaun): a MOC must never be raised, completed and approved by one person (seen in Sphera, e.g. Rotterdam). Local approval = functional review (Operations / Maintenance, other specialists) + Terminal Manager final sign-off (Khesar). Automatic where possible; specialist input (e.g. electrical) may be proceduralised (Sam).</t>
         </is>
       </c>
       <c r="E14" s="52"/>
     </row>
-    <row r="15" ht="28.8" customHeight="1">
+    <row r="15" ht="72.0" customHeight="1">
       <c r="A15" s="217">
         <v>11</v>
       </c>
       <c r="B15" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approvals generated only after evaluation is complete</t>
+          <t xml:space="preserve">Approval types list</t>
         </is>
       </c>
       <c r="C15" s="216" t="inlineStr">
@@ -36731,28 +36731,28 @@
       </c>
       <c r="D15" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolved by design: approvals auto-generate on entry to the Approval stage (after the checklist). Intelex to confirm generation timing.</t>
+          <t xml:space="preserve">21-Oct: OOTB types (Engineering, Environmental, Safety, Risk Mgmt, Financial, Start Up) kept so users can add functional approvals; 'Operations' missing (Khesar); list to be adapted to the business. Needed: functional types (Operations, Maintenance, Engineering, Safety, Environmental) + level approvals (TM, Regional HSEC/Ops, Global HSEC/Ops). Intelex to propose (re-caption existing objects vs new).</t>
         </is>
       </c>
       <c r="E15" s="52"/>
     </row>
-    <row r="16" ht="28.8" customHeight="1">
+    <row r="16" ht="57.6" customHeight="1">
       <c r="A16" s="217">
         <v>12</v>
       </c>
       <c r="B16" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">External parties (contractors) in tasks/approvals</t>
+          <t xml:space="preserve">Manual MOC form retired - digital only</t>
         </is>
       </c>
       <c r="C16" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Alonso Maranon Barrios</t>
+          <t xml:space="preserve">Impala - Shaun Jones</t>
         </is>
       </c>
       <c r="D16" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">DECIDED: no Intelex access for externals; internal owner of the task collects and uploads evidence. Public Forms are not in SOW.</t>
+          <t xml:space="preserve">DECIDED 21-Oct: no paper/Word MOC form (it only existed because of the Sphera approver limit). Supporting documents (JSA/risk assessment, method statements, procedures, P&amp;IDs, design documents) attached in Intelex; instruction text under Attachments listing expected documents (Khesar).</t>
         </is>
       </c>
       <c r="E16" s="52"/>
@@ -36763,101 +36763,101 @@
       </c>
       <c r="B17" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security groups and location roles population</t>
+          <t xml:space="preserve">Per-stage requirements map</t>
         </is>
       </c>
       <c r="C17" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Rodrigo Llamas</t>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
         </is>
       </c>
       <c r="D17" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Users/groups via Workday (EDIS) feed; location roles (MOC Coordinator, Terminal Manager, Regional/Global approvers) nominated per terminal/region. Local variations handled by role assignment, not by workflow.</t>
+          <t xml:space="preserve">ACTION 21-Oct (Shaun): map per stage what we ask, which documents we expect/mandate and where we approve. Sam to update his workbook (EOD 21-Oct); Rodrigo to transfer to this workbook. Also: Follow Up questions from the MOC audit form (Sam).</t>
         </is>
       </c>
       <c r="E17" s="52"/>
     </row>
-    <row r="18" ht="14.4" customHeight="1">
+    <row r="18" ht="43.2" customHeight="1">
       <c r="A18" s="217">
         <v>14</v>
       </c>
       <c r="B18" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage due dates, reminders and escalations</t>
+          <t xml:space="preserve">Simplified MOC workflow (organisational / IT changes)</t>
         </is>
       </c>
       <c r="C18" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Shaun Jones</t>
+          <t xml:space="preserve">Intelex - Ian</t>
         </is>
       </c>
       <c r="D18" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN: confirm SLAs per stage and the escalation ladder proposed in 'Notification Schedules'.</t>
+          <t xml:space="preserve">OPEN: Intelex to confirm whether the simplified/'Change Request' workflow seen in the demo site is in SOW. Impala priority: finalise the full MOC first; Emergency kept minimal (low volume).</t>
         </is>
       </c>
       <c r="E18" s="52"/>
     </row>
-    <row r="19" ht="28.8" customHeight="1">
+    <row r="19" ht="57.6" customHeight="1">
       <c r="A19" s="217">
         <v>15</v>
       </c>
       <c r="B19" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Translations of custom configuration (ES)</t>
+          <t xml:space="preserve">Stage gating rules</t>
         </is>
       </c>
       <c r="C19" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Rodrigo Llamas</t>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
         </is>
       </c>
       <c r="D19" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Per SOW Impala translates custom captions, tooltips, instructions and e-mails (OOTB ES/FR/PT/ZH provided).</t>
+          <t xml:space="preserve">CONFIRMED 21-Oct: in the demo Sam reached Start Up without answering the stage questions - must be impossible. OOTB nothing forces tasks/approvals per stage. Proposed: all screening questions answered + stage tasks closed before Approval; at least one approval (Local) and all approvals closed before Implementation.</t>
         </is>
       </c>
       <c r="E19" s="52"/>
     </row>
-    <row r="20" ht="72.0" customHeight="1">
+    <row r="20" ht="28.8" customHeight="1">
       <c r="A20" s="217">
         <v>16</v>
       </c>
       <c r="B20" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minimum number of approvers per grade</t>
+          <t xml:space="preserve">Approvals generated only after evaluation is complete</t>
         </is>
       </c>
       <c r="C20" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Sam Robinson</t>
+          <t xml:space="preserve">Intelex - Ian</t>
         </is>
       </c>
       <c r="D20" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN (internal workshop 21-Oct): 'MOC Proposal' defines the approval LEVEL per grade (Minor = Local - TM) but not the NUMBER of approvers. Current procedure/BRD: min. 2 approvers for lower levels, 3 for the highest. Confirm the rule to give Intelex. Note: Sam's design replaces Level 0-5 scoring and removes like-for-like from the module; BRD BO-61 to be updated accordingly (housekeeping).</t>
+          <t xml:space="preserve">Resolved by design: approvals auto-generate on entry to the Approval stage (after the checklist). Intelex to confirm generation timing.</t>
         </is>
       </c>
       <c r="E20" s="52"/>
     </row>
-    <row r="21" ht="43.2" customHeight="1">
+    <row r="21" ht="28.8" customHeight="1">
       <c r="A21" s="217">
         <v>17</v>
       </c>
       <c r="B21" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Return for revision vs formal rejection</t>
+          <t xml:space="preserve">External parties (contractors) in tasks/approvals</t>
         </is>
       </c>
       <c r="C21" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelex - Ian</t>
+          <t xml:space="preserve">Impala - Alonso Maranon Barrios</t>
         </is>
       </c>
       <c r="D21" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD FR-B3-035 (Must): Roll Back from Approval = return for revision, closed approvals are KEPT; formal rejection resets the approval chain (RULE-B3-07). Intelex to confirm OOTB behaviour of approvals on Roll Back.</t>
+          <t xml:space="preserve">DECIDED: no Intelex access for externals; internal owner of the task collects and uploads evidence. Public Forms are not in SOW.</t>
         </is>
       </c>
       <c r="E21" s="52"/>
@@ -36868,17 +36868,17 @@
       </c>
       <c r="B22" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emergency MOC regularisation</t>
+          <t xml:space="preserve">Security groups and location roles population</t>
         </is>
       </c>
       <c r="C22" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Shaun Jones</t>
+          <t xml:space="preserve">Impala - Rodrigo Llamas</t>
         </is>
       </c>
       <c r="D22" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD RULE-B3-14: single senior approval, immediate execution, full dossier (checklist, tasks) completed retrospectively within [TBC] days; record flagged 'pending regularisation' and reported overdue; cannot be closed until regularised (AH17).</t>
+          <t xml:space="preserve">Users/groups via Workday (EDIS) feed; location roles (MOC Coordinator, Terminal Manager, Regional/Global approvers) nominated per terminal/region. Local variations handled by role assignment, not by workflow.</t>
         </is>
       </c>
       <c r="E22" s="52"/>
@@ -36889,51 +36889,156 @@
       </c>
       <c r="B23" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temporary change extensions</t>
+          <t xml:space="preserve">Stage due dates, reminders and escalations</t>
         </is>
       </c>
       <c r="C23" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Sam Robinson</t>
+          <t xml:space="preserve">Impala - Shaun Jones</t>
         </is>
       </c>
       <c r="D23" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD RULE-B3-08 / FR-B3-014: review date, max 3 extensions each with rationale and re-approval at the MOC grade (ad hoc approval); conversion to permanent = new MOC linked through Related MOCs.</t>
+          <t xml:space="preserve">21-Oct (Sam): Evaluation/Design &amp; Analysis cannot have a fixed SLA (project size varies wildly); only the Approval stage gets one: approvals within 7 days. Escalation ladder for tasks = BA proposal, to be confirmed.</t>
         </is>
       </c>
       <c r="E23" s="52"/>
     </row>
-    <row r="24" ht="43.2" customHeight="1">
+    <row r="24" ht="28.8" customHeight="1">
       <c r="A24" s="217">
         <v>20</v>
       </c>
       <c r="B24" s="216" t="inlineStr">
         <is>
+          <t xml:space="preserve">Translations of custom configuration (ES)</t>
+        </is>
+      </c>
+      <c r="C24" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Rodrigo Llamas</t>
+        </is>
+      </c>
+      <c r="D24" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per SOW Impala translates custom captions, tooltips, instructions and e-mails (OOTB ES/FR/PT/ZH provided).</t>
+        </is>
+      </c>
+      <c r="E24" s="52"/>
+    </row>
+    <row r="25" ht="43.2" customHeight="1">
+      <c r="A25" s="217">
+        <v>21</v>
+      </c>
+      <c r="B25" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minimum number of approvers per grade</t>
+        </is>
+      </c>
+      <c r="C25" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
+        </is>
+      </c>
+      <c r="D25" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTLY ANSWERED 21-Oct: Local = at least one functional reviewer (Ops/Maintenance) + TM (so &gt;= 2, in line with BRD). Regional and Global = HSEC + Operations. Exact rule per level to be written in Sam's per-stage map. BRD BO-61 to be updated for Level 0-5 scoring (housekeeping).</t>
+        </is>
+      </c>
+      <c r="E25" s="52"/>
+    </row>
+    <row r="26" ht="43.2" customHeight="1">
+      <c r="A26" s="217">
+        <v>22</v>
+      </c>
+      <c r="B26" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Return for revision vs formal rejection</t>
+        </is>
+      </c>
+      <c r="C26" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intelex - Ian</t>
+        </is>
+      </c>
+      <c r="D26" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD FR-B3-035 (Must): Roll Back from Approval = return for revision, closed approvals are KEPT; formal rejection resets the approval chain (RULE-B3-07). Intelex to confirm OOTB behaviour of approvals on Roll Back.</t>
+        </is>
+      </c>
+      <c r="E26" s="52"/>
+    </row>
+    <row r="27" ht="43.2" customHeight="1">
+      <c r="A27" s="217">
+        <v>23</v>
+      </c>
+      <c r="B27" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergency MOC regularisation</t>
+        </is>
+      </c>
+      <c r="C27" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Shaun Jones</t>
+        </is>
+      </c>
+      <c r="D27" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD RULE-B3-14: single senior approval, immediate execution, full dossier (checklist, tasks) completed retrospectively within [TBC] days; record flagged 'pending regularisation' and reported overdue; cannot be closed until regularised (AH17).</t>
+        </is>
+      </c>
+      <c r="E27" s="52"/>
+    </row>
+    <row r="28" ht="43.2" customHeight="1">
+      <c r="A28" s="217">
+        <v>24</v>
+      </c>
+      <c r="B28" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporary change extensions</t>
+        </is>
+      </c>
+      <c r="C28" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
+        </is>
+      </c>
+      <c r="D28" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRD RULE-B3-08 / FR-B3-014: review date, max 3 extensions each with rationale and re-approval at the MOC grade (ad hoc approval); conversion to permanent = new MOC linked through Related MOCs (Related MOCs kept 21-Oct for traceability, e.g. phased tank works).</t>
+        </is>
+      </c>
+      <c r="E28" s="52"/>
+    </row>
+    <row r="29" ht="43.2" customHeight="1">
+      <c r="A29" s="217">
+        <v>25</v>
+      </c>
+      <c r="B29" s="216" t="inlineStr">
+        <is>
           <t xml:space="preserve">MoC KPIs and leadership reporting</t>
         </is>
       </c>
-      <c r="C24" s="216" t="inlineStr">
+      <c r="C29" s="216" t="inlineStr">
         <is>
           <t xml:space="preserve">Impala - Rodrigo Llamas</t>
         </is>
       </c>
-      <c r="D24" s="216" t="inlineStr">
+      <c r="D29" s="216" t="inlineStr">
         <is>
           <t xml:space="preserve">BRD FR-B3-019 / FR-B3-033: monthly YTD permanent/temporary MOCs, open MOCs, overdue temporary MOCs, MoC-related incidents, open MoC actions + leading indicators. To be built as reports/dashboards (reporting phase), fields already captured in this workbook.</t>
         </is>
       </c>
-      <c r="E24" s="52"/>
-    </row>
-    <row r="25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
+      <c r="E29" s="52"/>
+    </row>
+    <row r="30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B30" s="29">
         <f>SUBTOTAL(103,DecisionsTasks[Task or Decision])</f>
         <v>2</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E30" s="29">
         <f>SUBTOTAL(103,DecisionsTasks[Date Complete])</f>
         <v>0</v>
       </c>
@@ -37098,7 +37203,7 @@
         <is>
           <t xml:space="preserve">Recipient(s): Change Requester, MOC Coordinator (Role)
 N11 to Terminal Manager + Regional HSEC if Emergency = Yes.
-Prior to submit: Change Description, Type of Change, Grade of Change, Grade Justification mandatory; Emergency Justification if Emergency = Yes; Change Expiry if Temporary = Yes.</t>
+Prior to submit: Change Description, Type of Change, Grade of Change, Reason for Change &amp; Technical Basis mandatory; Emergency Justification if Emergency = Yes; Change Expiry if Temporary = Yes.</t>
         </is>
       </c>
       <c r="J68" s="239" t="inlineStr">
@@ -37107,7 +37212,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="57.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="69" ht="72.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A69" s="133">
         <v>2</v>
       </c>
@@ -37126,7 +37231,7 @@
       </c>
       <c r="E69" s="220" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TBC] e.g. 30 days from stage entry</t>
+          <t xml:space="preserve">N/A (project dependent - 21-Oct)</t>
         </is>
       </c>
       <c r="F69" s="14" t="s">
@@ -37144,7 +37249,7 @@
         <is>
           <t xml:space="preserve">Recipient(s): Change Requester
 Replaces OOTB Pre-Approval, Evaluation and Design &amp; Analysis stages.
-Prior to transitioning: all screening questions answered and all tasks of this stage closed.</t>
+Prior to transitioning: all screening questions and stage questions answered, design documents attached, and tasks whose 'Complete before stage' = Approval closed (tasks due later stay open).</t>
         </is>
       </c>
       <c r="J69" s="239" t="inlineStr">
@@ -37193,7 +37298,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="187.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="72" ht="201.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A72" s="136">
         <v>3</v>
       </c>
@@ -37212,7 +37317,7 @@
       </c>
       <c r="E72" s="226" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TBC] e.g. 14 days from stage entry</t>
+          <t xml:space="preserve">7 days from stage entry (21-Oct)</t>
         </is>
       </c>
       <c r="F72" s="16" t="s">
@@ -37232,10 +37337,10 @@
         <is>
           <t xml:space="preserve">Recipient(s): Change Requester
 Approvals auto-generated on stage entry by Grade of Change:
-- Minor: Local (Terminal Manager)
+- Minor: Local = functional review (Operations / Maintenance) + Terminal Manager final sign-off
 - Moderate: Local &gt; Regional HSEC + Regional Operations
-- Major: Local &gt; Regional &gt; Global HSEC + Global Operations [TBC Regional step for Major]
-Approvals are SEQUENTIAL: next level requested only when the previous level is closed (Intelex to confirm solution).
+- Major: Local &gt; Regional &gt; Global HSEC + Global Operations (confirmed 21-Oct)
+Approvals are SEQUENTIAL and AUTOMATIC: when the TM approves, the next level is added and triggered by the system (Intelex to confirm solution). The single main approval happens here, before construction/activity starts.
 Ad hoc approvers can be added by the MOC Coordinator.
 Prior to transitioning: at least one approval exists and all approvals are closed (accepted).
 Roll Back = return for revision, closed approvals are kept; a formal rejection resets the chain (BRD FR-B3-035) [Intelex to confirm].</t>
@@ -37324,8 +37429,8 @@
       <c r="I75" s="223" t="inlineStr">
         <is>
           <t xml:space="preserve">Recipient(s): Change Requester
-Prior to transitioning to next stage, all tasks have to be completed.
-Tasks of this stage = pre-startup actions (incl. PSSR where required by Type/Grade): Start Up is blocked until they are closed (BRD FR-B3-028 / FR-B3-032). Post-startup actions are created in Follow Up.</t>
+Prior to transitioning: tasks with 'Complete before stage' = Start Up (pre-startup actions, PSSR) closed; Implementation questions answered. Post-startup tasks (e.g. P&amp;ID update) stay open until Follow Up (BRD FR-B3-028 / FR-B3-032).
+Optional local pre-startup approval [TBC] - main approval already given.</t>
         </is>
       </c>
     </row>
@@ -37924,7 +38029,7 @@
       </c>
       <c r="B4" s="241" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOC Task / MOC Approval (reminders to Person Responsible)</t>
+          <t xml:space="preserve">MOC Approval (due 7 days after request - 21-Oct) and MOC Task (BA proposal [TBC])</t>
         </is>
       </c>
     </row>
@@ -37947,7 +38052,7 @@
     </row>
     <row r="6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="242">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="242" t="inlineStr">
         <is>
@@ -37956,12 +38061,12 @@
       </c>
       <c r="C6" s="243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Person Responsible</t>
+          <t xml:space="preserve">Person Responsible (approver / task owner)</t>
         </is>
       </c>
       <c r="D6" s="242" t="inlineStr">
         <is>
-          <t xml:space="preserve">N13 / N14</t>
+          <t xml:space="preserve">N14 / N13</t>
         </is>
       </c>
       <c r="E6" s="244" t="inlineStr">
@@ -37986,7 +38091,7 @@
       </c>
       <c r="D7" s="245" t="inlineStr">
         <is>
-          <t xml:space="preserve">N13 / N14</t>
+          <t xml:space="preserve">N14 / N13</t>
         </is>
       </c>
       <c r="E7" s="244" t="inlineStr">
@@ -37997,7 +38102,7 @@
     </row>
     <row r="8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="242">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B8" s="242" t="inlineStr">
         <is>
@@ -38011,18 +38116,18 @@
       </c>
       <c r="D8" s="242" t="inlineStr">
         <is>
-          <t xml:space="preserve">N13 / N14</t>
+          <t xml:space="preserve">N14 / N13</t>
         </is>
       </c>
       <c r="E8" s="244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every 7 days until closed</t>
+          <t xml:space="preserve">Every 3 days until closed [TBC]</t>
         </is>
       </c>
     </row>
     <row r="9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="245">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B9" s="245" t="inlineStr">
         <is>
@@ -38036,7 +38141,7 @@
       </c>
       <c r="D9" s="245" t="inlineStr">
         <is>
-          <t xml:space="preserve">N13 / N14</t>
+          <t xml:space="preserve">N14 / N13</t>
         </is>
       </c>
       <c r="E9" s="244" t="inlineStr">
@@ -38872,76 +38977,76 @@
     <row r="8" s="29" customFormat="1" x14ac:dyDescent="0.55000000000000004" ht="43.2" customHeight="1">
       <c r="A8" s="250" t="inlineStr">
         <is>
+          <t xml:space="preserve">Terminal Functional Reviewer (Operations / Maintenance)</t>
+        </is>
+      </c>
+      <c r="B8" s="251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Local functional review before the Terminal Manager sign-off, so no MOC is raised and approved by one person (21-Oct). Specialists (e.g. electrical) added ad hoc.</t>
+        </is>
+      </c>
+      <c r="C8" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Group</t>
+        </is>
+      </c>
+      <c r="D8" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="E8" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workflow Task</t>
+        </is>
+      </c>
+      <c r="F8" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A - 21-Oct (Shaun, Khesar). Automatic local approval step [TBC with Intelex].</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" x14ac:dyDescent="0.55000000000000004" ht="43.2" customHeight="1">
+      <c r="A9" s="250" t="inlineStr">
+        <is>
           <t xml:space="preserve">Regional HSEC Manager</t>
         </is>
       </c>
-      <c r="B8" s="251" t="inlineStr">
+      <c r="B9" s="251" t="inlineStr">
         <is>
           <t xml:space="preserve">Regional approver for Moderate and Major changes. Notified of Emergency MOCs.</t>
         </is>
       </c>
-      <c r="C8" s="250" t="inlineStr">
+      <c r="C9" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">Individual</t>
         </is>
       </c>
-      <c r="D8" s="250" t="inlineStr">
+      <c r="D9" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="E8" s="250" t="inlineStr">
+      <c r="E9" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">Workflow Task, Location-Based Notification</t>
         </is>
       </c>
-      <c r="F8" s="250" t="inlineStr">
+      <c r="F9" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">A - Regional approval level. Local variations (e.g. a different approver for a region) handled by role assignment, not by workflow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" x14ac:dyDescent="0.55000000000000004" ht="28.8" customHeight="1">
-      <c r="A9" s="250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Regional Operations Manager</t>
-        </is>
-      </c>
-      <c r="B9" s="251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Regional approver for Moderate and Major changes.</t>
-        </is>
-      </c>
-      <c r="C9" s="250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Individual</t>
-        </is>
-      </c>
-      <c r="D9" s="250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="E9" s="250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Workflow Task</t>
-        </is>
-      </c>
-      <c r="F9" s="250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A - Regional approval level. BRD FR-B3-007: ROM / Country Operations Manager.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28.8" customHeight="1">
       <c r="A10" s="250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global HSEC</t>
+          <t xml:space="preserve">Regional Operations Manager</t>
         </is>
       </c>
       <c r="B10" s="251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global approver for Major changes.</t>
+          <t xml:space="preserve">Regional approver for Moderate and Major changes.</t>
         </is>
       </c>
       <c r="C10" s="250" t="inlineStr">
@@ -38961,60 +39066,85 @@
       </c>
       <c r="F10" s="250" t="inlineStr">
         <is>
-          <t xml:space="preserve">A - Global approval level (assigned at top location). BRD FR-B3-007: Head of HSEQ.</t>
+          <t xml:space="preserve">A - Regional approval level. BRD FR-B3-007: ROM / Country Operations Manager.</t>
         </is>
       </c>
     </row>
     <row r="11" x14ac:dyDescent="0.55000000000000004" ht="28.8" customHeight="1">
       <c r="A11" s="250" t="inlineStr">
         <is>
+          <t xml:space="preserve">Global HSEC</t>
+        </is>
+      </c>
+      <c r="B11" s="251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global approver for Major changes.</t>
+        </is>
+      </c>
+      <c r="C11" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Individual</t>
+        </is>
+      </c>
+      <c r="D11" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="E11" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workflow Task</t>
+        </is>
+      </c>
+      <c r="F11" s="250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A - Global approval level (assigned at top location). BRD FR-B3-007: Head of HSEQ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" x14ac:dyDescent="0.55000000000000004" ht="28.8" customHeight="1">
+      <c r="A12" s="250" t="inlineStr">
+        <is>
           <t xml:space="preserve">Global Operations</t>
         </is>
       </c>
-      <c r="B11" s="251" t="inlineStr">
+      <c r="B12" s="251" t="inlineStr">
         <is>
           <t xml:space="preserve">Global approver for Major changes.</t>
         </is>
       </c>
-      <c r="C11" s="250" t="inlineStr">
+      <c r="C12" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">Individual</t>
         </is>
       </c>
-      <c r="D11" s="250" t="inlineStr">
+      <c r="D12" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="E11" s="250" t="inlineStr">
+      <c r="E12" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">Workflow Task</t>
         </is>
       </c>
-      <c r="F11" s="250" t="inlineStr">
+      <c r="F12" s="250" t="inlineStr">
         <is>
           <t xml:space="preserve">A - Global approval level (assigned at top location). BRD FR-B3-007: COO.</t>
         </is>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
+    <row r="13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="53">
+      <c r="B13" s="1"/>
+      <c r="C13" s="53">
         <f>SUBTOTAL(103,Table5[Individual / Group])</f>
         <v>1</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="3"/>
@@ -39347,7 +39477,7 @@
       </c>
       <c r="N47" s="245" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - caption: 'Local Approval (Terminal Manager)'</t>
+          <t xml:space="preserve">Keep as functional approval (21-Oct). See decision 'Approval types list'.</t>
         </is>
       </c>
     </row>
@@ -39393,7 +39523,7 @@
       </c>
       <c r="N48" s="245" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - caption: 'Regional Operations Approval'</t>
+          <t xml:space="preserve">Keep as functional approval (21-Oct).</t>
         </is>
       </c>
     </row>
@@ -39439,7 +39569,7 @@
       </c>
       <c r="N49" s="245" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - caption: 'Global Operations Approval'</t>
+          <t xml:space="preserve">[TBC] re-use for a missing type (e.g. Operations / Maintenance / level approval) - Intelex to propose.</t>
         </is>
       </c>
     </row>
@@ -39971,7 +40101,7 @@
       </c>
       <c r="N62" s="245" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - caption: 'Global HSEC Approval'</t>
+          <t xml:space="preserve">[TBC] re-use for a missing type - Intelex to propose.</t>
         </is>
       </c>
     </row>
@@ -40017,7 +40147,7 @@
       </c>
       <c r="N63" s="245" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - caption: 'Regional HSEC Approval'</t>
+          <t xml:space="preserve">Keep as functional approval (21-Oct).</t>
         </is>
       </c>
     </row>
@@ -40063,7 +40193,7 @@
       </c>
       <c r="N64" s="245" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - caption: 'Additional Approval (ad hoc)'</t>
+          <t xml:space="preserve">[TBC] re-use for a missing type - Intelex to propose.</t>
         </is>
       </c>
     </row>
@@ -41755,12 +41885,12 @@
       <c r="Z20" s="253"/>
       <c r="AA20" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not used: Grade of Change is the single criticality driver.</t>
+          <t xml:space="preserve">Not used: Grade of Change is the single criticality driver (Sam 21-Oct: not sure Priority drives anything).</t>
         </is>
       </c>
       <c r="AB20" s="61"/>
     </row>
-    <row r="21" s="59" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="21" s="59" customFormat="1" ht="72.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A21" s="188">
         <v>17</v>
       </c>
@@ -41775,12 +41905,12 @@
       </c>
       <c r="E21" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grade Justification</t>
+          <t xml:space="preserve">Reason for Change &amp; Technical Basis</t>
         </is>
       </c>
       <c r="F21" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grade Justification</t>
+          <t xml:space="preserve">Reason for Change &amp; Technical Basis</t>
         </is>
       </c>
       <c r="G21" s="187" t="s">
@@ -41791,12 +41921,12 @@
       </c>
       <c r="I21" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tooltip: Explain why the selected grade applies (reference the descriptor or the Automatic Major list).</t>
+          <t xml:space="preserve">Tooltip: Why the change is needed, technical basis, scope, current situation and what approvers should look out for.</t>
         </is>
       </c>
       <c r="J21" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text. Mandatory.</t>
+          <t xml:space="preserve">Text (multi-line, no length limit). Mandatory.</t>
         </is>
       </c>
       <c r="K21" s="254" t="inlineStr">
@@ -41851,7 +41981,7 @@
       <c r="Z21" s="253"/>
       <c r="AA21" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Re-purposed Priority Explanation.</t>
+          <t xml:space="preserve">21-Oct (Khesar, agreed by Sam): Priority Explanation re-worded as reason / technical basis - gives approvers context. Covers BRD FR-B3-001.</t>
         </is>
       </c>
       <c r="AB21" s="61"/>
@@ -42266,7 +42396,7 @@
       <c r="Z26" s="253"/>
       <c r="AA26" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approvals now controlled in the Approval stage.</t>
+          <t xml:space="preserve">CONFIRMED 21-Oct (Shaun: 'it's the point of the approval'). Approvals controlled in the Approval stage.</t>
         </is>
       </c>
     </row>
@@ -42440,7 +42570,7 @@
       <c r="Z28" s="253"/>
       <c r="AA28" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moved to combined stage.</t>
+          <t xml:space="preserve">Moved to combined stage. 21-Oct: keep 'Alternatives Considered' (important).</t>
         </is>
       </c>
     </row>
@@ -42701,7 +42831,7 @@
       <c r="Z31" s="253"/>
       <c r="AA31" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moved to combined stage.</t>
+          <t xml:space="preserve">Moved to combined stage. 21-Oct (Sam): design documentation should be attached to the MOC here.</t>
         </is>
       </c>
     </row>
@@ -43018,7 +43148,7 @@
       <c r="Y35" s="253"/>
       <c r="Z35" s="253"/>
     </row>
-    <row r="36" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" ht="187.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A36" s="188">
         <v>32</v>
       </c>
@@ -43093,8 +43223,13 @@
       </c>
       <c r="Y36" s="253"/>
       <c r="Z36" s="253"/>
-    </row>
-    <row r="37" ht="230.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA36" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21-Oct (Sam): not sure we need both 'Installation Complete?' and 'Installation Confirmed?' - keep one [TBC].</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="216.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A37" s="188">
         <v>33</v>
       </c>
@@ -43169,6 +43304,11 @@
       </c>
       <c r="Y37" s="253"/>
       <c r="Z37" s="253"/>
+      <c r="AA37" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[TBC] candidate for removal (see row above).</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="187.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="188">
@@ -43411,12 +43551,12 @@
       <c r="D41" s="201" t="s">
         <v>614</v>
       </c>
-      <c r="E41" s="262" t="inlineStr">
+      <c r="E41" s="263" t="inlineStr">
         <is>
           <t xml:space="preserve">Start-Up Confirmed?</t>
         </is>
       </c>
-      <c r="F41" s="263" t="inlineStr">
+      <c r="F41" s="264" t="inlineStr">
         <is>
           <t xml:space="preserve">Start-Up Confirmed?</t>
         </is>
@@ -43722,12 +43862,12 @@
       <c r="D45" s="201" t="s">
         <v>620</v>
       </c>
-      <c r="E45" s="262" t="inlineStr">
+      <c r="E45" s="263" t="inlineStr">
         <is>
           <t xml:space="preserve">Were MOC Procedures Followed?</t>
         </is>
       </c>
-      <c r="F45" s="263" t="inlineStr">
+      <c r="F45" s="264" t="inlineStr">
         <is>
           <t xml:space="preserve">Were MOC Procedures Followed?</t>
         </is>
@@ -43809,12 +43949,12 @@
       <c r="D46" s="201" t="s">
         <v>620</v>
       </c>
-      <c r="E46" s="262" t="inlineStr">
+      <c r="E46" s="263" t="inlineStr">
         <is>
           <t xml:space="preserve">MOC Process Effectiveness &amp; Feedback</t>
         </is>
       </c>
-      <c r="F46" s="263" t="inlineStr">
+      <c r="F46" s="264" t="inlineStr">
         <is>
           <t xml:space="preserve">MOC Process Effectiveness &amp; Feedback</t>
         </is>
@@ -43883,7 +44023,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" ht="28.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A47" s="188">
         <v>43</v>
       </c>
@@ -43954,6 +44094,11 @@
       </c>
       <c r="Y47" s="253"/>
       <c r="Z47" s="253"/>
+      <c r="AA47" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21-Oct (Sam): add questions from the MOC audit form to Follow Up (list from Sam) [TBC].</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="72.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A48" s="188">
@@ -44296,7 +44441,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" ht="100.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A52" s="188">
         <v>48</v>
       </c>
@@ -44367,8 +44512,13 @@
       </c>
       <c r="Y52" s="253"/>
       <c r="Z52" s="253"/>
-    </row>
-    <row r="53" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA52" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEEP - 21-Oct (Shaun, Hugo): traceability, e.g. phased tank works (roof removal, new roof, return to service).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" x14ac:dyDescent="0.55000000000000004" ht="86.4" customHeight="1">
       <c r="A53" s="188">
         <v>49</v>
       </c>
@@ -44391,11 +44541,19 @@
       <c r="H53" s="200" t="s">
         <v>169</v>
       </c>
-      <c r="I53" s="201"/>
+      <c r="I53" s="262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Instruction text: attach all supporting documents - risk assessment / JSA, method statement, procedures, P&amp;IDs, design documents, SDS, permits and licences.</t>
+        </is>
+      </c>
       <c r="J53" s="201" t="s">
         <v>632</v>
       </c>
-      <c r="K53" s="177"/>
+      <c r="K53" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L53" s="189" t="s">
         <v>14</v>
       </c>
@@ -44437,6 +44595,11 @@
       </c>
       <c r="Y53" s="253"/>
       <c r="Z53" s="253"/>
+      <c r="AA53" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21-Oct (Khesar): explain under Attachments which documents are expected. Manual MOC form retired.</t>
+        </is>
+      </c>
     </row>
     <row r="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="188">
@@ -44783,7 +44946,7 @@
         <v>108</v>
       </c>
       <c r="G64" s="182"/>
-      <c r="H64" s="264" t="inlineStr">
+      <c r="H64" s="265" t="inlineStr">
         <is>
           <t xml:space="preserve">Lookup</t>
         </is>
@@ -44794,7 +44957,7 @@
           <t xml:space="preserve">Values: Yes / No / N/A [TBC]</t>
         </is>
       </c>
-      <c r="K64" s="265" t="inlineStr">
+      <c r="K64" s="266" t="inlineStr">
         <is>
           <t xml:space="preserve">M</t>
         </is>
@@ -49303,7 +49466,7 @@
       <c r="K168" s="59"/>
       <c r="AA168" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - object caption: 'Local Approval (Terminal Manager)'</t>
+          <t xml:space="preserve">21-Oct: Keep (functional approval). Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -50101,7 +50264,7 @@
       <c r="K186" s="59"/>
       <c r="AA186" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - object caption: 'Regional Operations Approval'</t>
+          <t xml:space="preserve">21-Oct: Keep (functional approval). Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -50899,7 +51062,7 @@
       <c r="K204" s="59"/>
       <c r="AA204" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - object caption: 'Global Operations Approval'</t>
+          <t xml:space="preserve">21-Oct: [TBC] re-use for a missing type - Intelex to propose. Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -51697,7 +51860,7 @@
       <c r="K222" s="59"/>
       <c r="AA222" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - object caption: 'Global HSEC Approval'</t>
+          <t xml:space="preserve">21-Oct: [TBC] re-use for a missing type - Intelex to propose. Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -52495,7 +52658,7 @@
       <c r="K240" s="59"/>
       <c r="AA240" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - object caption: 'Regional HSEC Approval'</t>
+          <t xml:space="preserve">21-Oct: Keep (functional approval). Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -53293,7 +53456,7 @@
       <c r="K258" s="59"/>
       <c r="AA258" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - object caption: 'Additional Approval (ad hoc)'</t>
+          <t xml:space="preserve">21-Oct: [TBC] re-use for a missing type - Intelex to propose. Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -55003,7 +55166,7 @@
           <t xml:space="preserve">L04 - Grade of Change</t>
         </is>
       </c>
-      <c r="K303" s="266" t="inlineStr">
+      <c r="K303" s="267" t="inlineStr">
         <is>
           <t xml:space="preserve">M</t>
         </is>
@@ -55587,7 +55750,7 @@
           <t xml:space="preserve">L04 - Grade of Change</t>
         </is>
       </c>
-      <c r="K320" s="266" t="inlineStr">
+      <c r="K320" s="267" t="inlineStr">
         <is>
           <t xml:space="preserve">M</t>
         </is>
@@ -56047,7 +56210,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M333" s="267" t="inlineStr">
+      <c r="M333" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -56057,12 +56220,12 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O333" s="267" t="inlineStr">
+      <c r="O333" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P333" s="267" t="inlineStr">
+      <c r="P333" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56172,7 +56335,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M334" s="267" t="inlineStr">
+      <c r="M334" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56182,12 +56345,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O334" s="267" t="inlineStr">
+      <c r="O334" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P334" s="267" t="inlineStr">
+      <c r="P334" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56297,7 +56460,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M335" s="267" t="inlineStr">
+      <c r="M335" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56307,12 +56470,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O335" s="267" t="inlineStr">
+      <c r="O335" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P335" s="267" t="inlineStr">
+      <c r="P335" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56422,7 +56585,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M336" s="267" t="inlineStr">
+      <c r="M336" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56432,12 +56595,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O336" s="267" t="inlineStr">
+      <c r="O336" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P336" s="267" t="inlineStr">
+      <c r="P336" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56543,7 +56706,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M337" s="267" t="inlineStr">
+      <c r="M337" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56553,12 +56716,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O337" s="267" t="inlineStr">
+      <c r="O337" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P337" s="267" t="inlineStr">
+      <c r="P337" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56660,7 +56823,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M338" s="267" t="inlineStr">
+      <c r="M338" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -56670,12 +56833,12 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O338" s="267" t="inlineStr">
+      <c r="O338" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P338" s="267" t="inlineStr">
+      <c r="P338" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56777,7 +56940,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M339" s="267" t="inlineStr">
+      <c r="M339" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -56787,12 +56950,12 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O339" s="267" t="inlineStr">
+      <c r="O339" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P339" s="267" t="inlineStr">
+      <c r="P339" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56898,7 +57061,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M340" s="267" t="inlineStr">
+      <c r="M340" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -56908,12 +57071,12 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O340" s="267" t="inlineStr">
+      <c r="O340" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P340" s="267" t="inlineStr">
+      <c r="P340" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56964,7 +57127,7 @@
         </is>
       </c>
     </row>
-    <row r="341" x14ac:dyDescent="0.55000000000000004" ht="86.4" customHeight="1">
+    <row r="341" x14ac:dyDescent="0.55000000000000004" ht="115.2" customHeight="1">
       <c r="A341" s="253">
         <v>9</v>
       </c>
@@ -56989,12 +57152,12 @@
       </c>
       <c r="E341" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Action Plans</t>
+          <t xml:space="preserve">Action Plans (OPTIONAL)</t>
         </is>
       </c>
       <c r="F341" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Action Plans</t>
+          <t xml:space="preserve">Action Plans (OPTIONAL)</t>
         </is>
       </c>
       <c r="G341" s="254" t="inlineStr">
@@ -57010,7 +57173,7 @@
       <c r="I341" s="254"/>
       <c r="J341" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:M relation to Action Plan object; columns: Action No. | Description | Person Responsible | Due Date | Status. [Intelex to confirm]</t>
+          <t xml:space="preserve">1:M relation to Action Plan object; columns: Action No. | Description | Person Responsible | Due Date | Status. Only if Intelex confirms low effort. Decision 21-Oct: MOC Tasks remain the MOC actions.</t>
         </is>
       </c>
       <c r="K341" s="256" t="inlineStr">
@@ -57023,7 +57186,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M341" s="267" t="inlineStr">
+      <c r="M341" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -57033,12 +57196,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O341" s="267" t="inlineStr">
+      <c r="O341" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P341" s="267" t="inlineStr">
+      <c r="P341" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -57085,17 +57248,17 @@
       </c>
       <c r="AA341" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alonso / Sam: traceability of actions back to the MOC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="342" ht="57.6" customHeight="1">
+          <t xml:space="preserve">Nice-to-have (Sam). Shaun 21-Oct: OK with tasks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="72.0" customHeight="1">
       <c r="A342" s="253">
         <v>10</v>
       </c>
       <c r="B342" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation</t>
+          <t xml:space="preserve">Draft (MOC Task)</t>
         </is>
       </c>
       <c r="C342" s="255" t="inlineStr">
@@ -57105,37 +57268,37 @@
       </c>
       <c r="D342" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation Information Details</t>
+          <t xml:space="preserve">MOC Task Details</t>
         </is>
       </c>
       <c r="E342" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Change Owner</t>
+          <t xml:space="preserve">Complete Before Stage</t>
         </is>
       </c>
       <c r="F342" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Change Owner</t>
+          <t xml:space="preserve">Complete Before Stage</t>
         </is>
       </c>
       <c r="G342" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accountable for the change through to closure.</t>
+          <t xml:space="preserve">MOC stage by which the task must be closed.</t>
         </is>
       </c>
       <c r="H342" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Relations</t>
+          <t xml:space="preserve">Lookup (Approval / Start Up / Follow Up)</t>
         </is>
       </c>
       <c r="I342" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tooltip: Person accountable for the change until closure (may be the requester).</t>
+          <t xml:space="preserve">Tooltip: Pre-startup tasks = Start Up; post-change tasks (e.g. P&amp;ID update) = Follow Up.</t>
         </is>
       </c>
       <c r="J342" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">M:1 relation to Employee. Default Value: Change Requester.</t>
+          <t xml:space="preserve">Field on MOC Task (all task types). MOC stage gate checks only open tasks due for that stage [Intelex to confirm].</t>
         </is>
       </c>
       <c r="K342" s="256" t="inlineStr">
@@ -57148,9 +57311,9 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M342" s="267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
+      <c r="M342" s="268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="N342" s="253" t="inlineStr">
@@ -57158,12 +57321,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O342" s="267" t="inlineStr">
+      <c r="O342" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P342" s="267" t="inlineStr">
+      <c r="P342" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -57175,7 +57338,7 @@
       </c>
       <c r="R342" s="253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="S342" s="253" t="inlineStr">
@@ -57185,7 +57348,7 @@
       </c>
       <c r="T342" s="253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="U342" s="253" t="inlineStr">
@@ -57195,7 +57358,7 @@
       </c>
       <c r="V342" s="253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="W342" s="253" t="inlineStr">
@@ -57205,16 +57368,16 @@
       </c>
       <c r="X342" s="253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="AA342" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD FR-B3-026 (Should) / FR-B3-004: originator vs owner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="343" ht="43.2" customHeight="1">
+          <t xml:space="preserve">21-Oct (Khesar / Sam): tasks due later must not block the MOC. BRD FR-B3-032.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="57.6" customHeight="1">
       <c r="A343" s="253">
         <v>11</v>
       </c>
@@ -57235,17 +57398,17 @@
       </c>
       <c r="E343" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Owner</t>
+          <t xml:space="preserve">Change Owner</t>
         </is>
       </c>
       <c r="F343" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational Owner</t>
+          <t xml:space="preserve">Change Owner</t>
         </is>
       </c>
       <c r="G343" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owner of the affected area or asset.</t>
+          <t xml:space="preserve">Accountable for the change through to closure.</t>
         </is>
       </c>
       <c r="H343" s="254" t="inlineStr">
@@ -57255,12 +57418,12 @@
       </c>
       <c r="I343" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tooltip: Responsible for operational readiness before start-up.</t>
+          <t xml:space="preserve">Tooltip: Person accountable for the change until closure (may be the requester).</t>
         </is>
       </c>
       <c r="J343" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">M:1 relation to Employee.</t>
+          <t xml:space="preserve">M:1 relation to Employee. Default Value: Change Requester.</t>
         </is>
       </c>
       <c r="K343" s="256" t="inlineStr">
@@ -57273,7 +57436,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M343" s="267" t="inlineStr">
+      <c r="M343" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -57283,12 +57446,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O343" s="267" t="inlineStr">
+      <c r="O343" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P343" s="267" t="inlineStr">
+      <c r="P343" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -57335,11 +57498,11 @@
       </c>
       <c r="AA343" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD FR-B3-004 (Must).</t>
-        </is>
-      </c>
-    </row>
-    <row r="344" ht="57.6" customHeight="1">
+          <t xml:space="preserve">BRD FR-B3-026 (Should) / FR-B3-004: originator vs owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="43.2" customHeight="1">
       <c r="A344" s="253">
         <v>12</v>
       </c>
@@ -57360,32 +57523,32 @@
       </c>
       <c r="E344" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reason for Change &amp; Technical Basis</t>
+          <t xml:space="preserve">Operational Owner</t>
         </is>
       </c>
       <c r="F344" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reason for Change &amp; Technical Basis</t>
+          <t xml:space="preserve">Operational Owner</t>
         </is>
       </c>
       <c r="G344" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detailed justification.</t>
+          <t xml:space="preserve">Owner of the affected area or asset.</t>
         </is>
       </c>
       <c r="H344" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text (multi-line)</t>
+          <t xml:space="preserve">Relations</t>
         </is>
       </c>
       <c r="I344" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tooltip: Why the change is needed, technical basis, scope and current situation.</t>
+          <t xml:space="preserve">Tooltip: Responsible for operational readiness before start-up.</t>
         </is>
       </c>
       <c r="J344" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">No length limit.</t>
+          <t xml:space="preserve">M:1 relation to Employee.</t>
         </is>
       </c>
       <c r="K344" s="256" t="inlineStr">
@@ -57398,7 +57561,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M344" s="267" t="inlineStr">
+      <c r="M344" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -57408,12 +57571,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O344" s="267" t="inlineStr">
+      <c r="O344" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P344" s="267" t="inlineStr">
+      <c r="P344" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -57460,7 +57623,7 @@
       </c>
       <c r="AA344" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD FR-B3-001 (Must); Change Description is limited to 255 characters.</t>
+          <t xml:space="preserve">BRD FR-B3-004 (Must).</t>
         </is>
       </c>
     </row>
@@ -57515,7 +57678,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M345" s="267" t="inlineStr">
+      <c r="M345" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -57525,12 +57688,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O345" s="267" t="inlineStr">
+      <c r="O345" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P345" s="267" t="inlineStr">
+      <c r="P345" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -57636,7 +57799,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M346" s="267" t="inlineStr">
+      <c r="M346" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -57646,12 +57809,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O346" s="267" t="inlineStr">
+      <c r="O346" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P346" s="267" t="inlineStr">
+      <c r="P346" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -57761,7 +57924,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M347" s="267" t="inlineStr">
+      <c r="M347" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -57771,12 +57934,12 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O347" s="267" t="inlineStr">
+      <c r="O347" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P347" s="267" t="inlineStr">
+      <c r="P347" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -57882,7 +58045,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M348" s="267" t="inlineStr">
+      <c r="M348" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -57892,12 +58055,12 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O348" s="267" t="inlineStr">
+      <c r="O348" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P348" s="267" t="inlineStr">
+      <c r="P348" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58003,7 +58166,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M349" s="267" t="inlineStr">
+      <c r="M349" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58013,12 +58176,12 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O349" s="267" t="inlineStr">
+      <c r="O349" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P349" s="267" t="inlineStr">
+      <c r="P349" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -58120,7 +58283,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M350" s="267" t="inlineStr">
+      <c r="M350" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58130,12 +58293,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O350" s="267" t="inlineStr">
+      <c r="O350" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="P350" s="267" t="inlineStr">
+      <c r="P350" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58241,7 +58404,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M351" s="267" t="inlineStr">
+      <c r="M351" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58251,12 +58414,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O351" s="267" t="inlineStr">
+      <c r="O351" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="P351" s="267" t="inlineStr">
+      <c r="P351" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58358,7 +58521,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M352" s="267" t="inlineStr">
+      <c r="M352" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58368,12 +58531,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O352" s="267" t="inlineStr">
+      <c r="O352" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P352" s="267" t="inlineStr">
+      <c r="P352" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58475,7 +58638,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M353" s="267" t="inlineStr">
+      <c r="M353" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58485,12 +58648,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O353" s="267" t="inlineStr">
+      <c r="O353" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P353" s="267" t="inlineStr">
+      <c r="P353" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58592,7 +58755,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M354" s="267" t="inlineStr">
+      <c r="M354" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -58602,12 +58765,12 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O354" s="267" t="inlineStr">
+      <c r="O354" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P354" s="267" t="inlineStr">
+      <c r="P354" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -63926,7 +64089,7 @@
         <v>387</v>
       </c>
       <c r="B4" s="74"/>
-      <c r="C4" s="268" t="inlineStr">
+      <c r="C4" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">R - Priority field removed (Grade of Change is the single driver).</t>
         </is>
@@ -63977,7 +64140,7 @@
         <v>190</v>
       </c>
       <c r="B11" s="74"/>
-      <c r="C11" s="268" t="inlineStr">
+      <c r="C11" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Check: values are the Approval objects (same as L07); Task Type should list MOC Task children (L06). Intelex to confirm.</t>
         </is>
@@ -64060,7 +64223,7 @@
         <v>197</v>
       </c>
       <c r="B20" s="74"/>
-      <c r="C20" s="268" t="inlineStr">
+      <c r="C20" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">M - aligned to the new 6-stage workflow.</t>
         </is>
@@ -64089,12 +64252,12 @@
       <c r="E22" s="13"/>
     </row>
     <row r="23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="268" t="inlineStr">
+      <c r="A23" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
         </is>
       </c>
-      <c r="B23" s="268" t="inlineStr">
+      <c r="B23" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
         </is>
@@ -64103,12 +64266,12 @@
       <c r="E23" s="13"/>
     </row>
     <row r="24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="269" t="inlineStr">
+      <c r="A24" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Approval</t>
         </is>
       </c>
-      <c r="B24" s="269" t="inlineStr">
+      <c r="B24" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Approval</t>
         </is>
@@ -64117,12 +64280,12 @@
       <c r="E24" s="13"/>
     </row>
     <row r="25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="269" t="inlineStr">
+      <c r="A25" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Implementation</t>
         </is>
       </c>
-      <c r="B25" s="269" t="inlineStr">
+      <c r="B25" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Implementation</t>
         </is>
@@ -64131,12 +64294,12 @@
       <c r="E25" s="13"/>
     </row>
     <row r="26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="269" t="inlineStr">
+      <c r="A26" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Start-Up</t>
         </is>
       </c>
-      <c r="B26" s="269" t="inlineStr">
+      <c r="B26" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Start-Up</t>
         </is>
@@ -64145,12 +64308,12 @@
       <c r="E26" s="13"/>
     </row>
     <row r="27" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="269" t="inlineStr">
+      <c r="A27" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Follow-Up</t>
         </is>
       </c>
-      <c r="B27" s="269" t="inlineStr">
+      <c r="B27" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Follow-Up</t>
         </is>
@@ -64159,17 +64322,17 @@
       <c r="E27" s="13"/>
     </row>
     <row r="28" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="269"/>
-      <c r="B28" s="269"/>
+      <c r="A28" s="270"/>
+      <c r="B28" s="270"/>
     </row>
     <row r="30" ht="43.2" x14ac:dyDescent="0.85" customHeight="1">
-      <c r="A30" s="270" t="inlineStr">
+      <c r="A30" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">L04 - Grade of Change (Change Impact)</t>
         </is>
       </c>
       <c r="B30" s="74"/>
-      <c r="C30" s="268" t="inlineStr">
+      <c r="C30" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">M - single criticality list used by MOC and by Screening / Task / Approval setups. Minor = Local, Moderate = Regional, Major = Global approval.</t>
         </is>
@@ -64184,36 +64347,36 @@
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="268" t="inlineStr">
+      <c r="A32" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Minor</t>
         </is>
       </c>
-      <c r="B32" s="268" t="inlineStr">
+      <c r="B32" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Minor</t>
         </is>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="268" t="inlineStr">
+      <c r="A33" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Moderate</t>
         </is>
       </c>
-      <c r="B33" s="268" t="inlineStr">
+      <c r="B33" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Moderate</t>
         </is>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="269" t="inlineStr">
+      <c r="A34" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Major</t>
         </is>
       </c>
-      <c r="B34" s="269" t="inlineStr">
+      <c r="B34" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Major</t>
         </is>
@@ -64224,7 +64387,7 @@
         <v>382</v>
       </c>
       <c r="B36" s="74"/>
-      <c r="C36" s="268" t="inlineStr">
+      <c r="C36" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">R - duplicate of L01; replace its references (Task/Approval setup, Change Impact) by L04.</t>
         </is>
@@ -64267,7 +64430,7 @@
         <v>447</v>
       </c>
       <c r="B42" s="74"/>
-      <c r="C42" s="268" t="inlineStr">
+      <c r="C42" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Keep. Mapping to checklist sections: Impact/Hazard Assessment (B), Process (C, E-H), Documentation (D), Training + Change Communication (I), PSSR (K), Checklist (generic).</t>
         </is>
@@ -64337,14 +64500,14 @@
         <v>196</v>
       </c>
     </row>
-    <row r="52" ht="28.8" x14ac:dyDescent="0.85" customHeight="1">
+    <row r="52" ht="72.0" x14ac:dyDescent="0.85" customHeight="1">
       <c r="A52" s="61" t="s">
         <v>769</v>
       </c>
       <c r="B52" s="74"/>
-      <c r="C52" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M - captions only (existing approval objects re-used for Local / Regional / Global levels).</t>
+      <c r="C52" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[TBC] 21-Oct: keep OOTB types for functional approvals; add Operations (Khesar) and Maintenance; level approvals (TM / Regional HSEC-Ops / Global HSEC-Ops) also needed. Intelex to propose re-caption vs new objects.</t>
         </is>
       </c>
     </row>
@@ -64360,60 +64523,48 @@
       <c r="A54" s="13" t="s">
         <v>418</v>
       </c>
-      <c r="B54" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Regional Operations Approval</t>
-        </is>
+      <c r="B54" s="13" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="55" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="13" t="s">
         <v>420</v>
       </c>
-      <c r="B55" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Regional HSEC Approval</t>
-        </is>
+      <c r="B55" s="13" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="56" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>422</v>
       </c>
-      <c r="B56" s="269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Local Approval (Terminal Manager)</t>
-        </is>
+      <c r="B56" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="57" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>424</v>
       </c>
-      <c r="B57" s="269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Global HSEC Approval</t>
-        </is>
+      <c r="B57" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="58" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>426</v>
       </c>
-      <c r="B58" s="269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Global Operations Approval</t>
-        </is>
+      <c r="B58" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="59" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>428</v>
       </c>
-      <c r="B59" s="269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Additional Approval (ad hoc)</t>
-        </is>
+      <c r="B59" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="62">
@@ -64422,7 +64573,7 @@
           <t xml:space="preserve">L08 - Type of Change (MOC Category data)</t>
         </is>
       </c>
-      <c r="C62" s="268" t="inlineStr">
+      <c r="C62" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">A - records of the MOC Category object (caption 'Type of Change').</t>
         </is>
@@ -64441,96 +64592,96 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="268" t="inlineStr">
+      <c r="A64" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Change of Design / Equipment</t>
         </is>
       </c>
-      <c r="B64" s="271" t="inlineStr">
+      <c r="B64" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Change of Design / Equipment</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="268" t="inlineStr">
+      <c r="A65" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Change of Process</t>
         </is>
       </c>
-      <c r="B65" s="271" t="inlineStr">
+      <c r="B65" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Change of Process</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="268" t="inlineStr">
+      <c r="A66" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Change of Procedure</t>
         </is>
       </c>
-      <c r="B66" s="271" t="inlineStr">
+      <c r="B66" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Change of Procedure</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="268" t="inlineStr">
+      <c r="A67" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Change of Control Systems / IT / SIS</t>
         </is>
       </c>
-      <c r="B67" s="271" t="inlineStr">
+      <c r="B67" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Change of Control Systems / IT / SIS</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="268" t="inlineStr">
+      <c r="A68" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">5. Organisational / Personnel Change</t>
         </is>
       </c>
-      <c r="B68" s="271" t="inlineStr">
+      <c r="B68" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">5. Organisational / Personnel Change</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="268" t="inlineStr">
+      <c r="A69" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">6. Temporary Change</t>
         </is>
       </c>
-      <c r="B69" s="271" t="inlineStr">
+      <c r="B69" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">6. Temporary Change</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="268" t="inlineStr">
+      <c r="A70" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Regulatory / Permit-Driven Change</t>
         </is>
       </c>
-      <c r="B70" s="271" t="inlineStr">
+      <c r="B70" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Regulatory / Permit-Driven Change</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="268" t="inlineStr">
+      <c r="A71" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">8. Changes to Utility &amp; HSE Protection Systems</t>
         </is>
       </c>
-      <c r="B71" s="271" t="inlineStr">
+      <c r="B71" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">8. Changes to Utility &amp; HSE Protection Systems</t>
         </is>
@@ -64566,176 +64717,176 @@
       </c>
     </row>
     <row r="76" ht="144.0" customHeight="1">
-      <c r="A76" s="268" t="inlineStr">
+      <c r="A76" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Change of Design / Equipment</t>
         </is>
       </c>
-      <c r="B76" s="268" t="inlineStr">
+      <c r="B76" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Replace for an identical one. Replacement by an identical component with the same engineering specifications, construction material, and design range. Includes relocation of equipment within the same service and operating conditions</t>
         </is>
       </c>
-      <c r="C76" s="268" t="inlineStr">
+      <c r="C76" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Replace for a similar one. Replacement by a functionally similar component; may differ in brand or model but remains within the same design range. Includes relocation to a different service or operating environment, or decommissioning of non-safety-critical equipment</t>
         </is>
       </c>
-      <c r="D76" s="268" t="inlineStr">
+      <c r="D76" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Replace for a different one. Technologically different component, different construction material, or outside the original design range. Includes any departure from original design intent, decommissioning of safety-critical equipment, or permanent removal of equipment with associated safeguard implications</t>
         </is>
       </c>
     </row>
     <row r="77" ht="144.0" customHeight="1">
-      <c r="A77" s="268" t="inlineStr">
+      <c r="A77" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Change of Process</t>
         </is>
       </c>
-      <c r="B77" s="268" t="inlineStr">
+      <c r="B77" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Change of environment. Process carried out in same-size equipment with same construction materials and instrumentation. Capacity change ≤ 10%. Substitution of a non-hazardous material with an equivalent; no change to process parameters</t>
         </is>
       </c>
-      <c r="C77" s="268" t="inlineStr">
+      <c r="C77" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Change of scale. Capacity change &gt; 10% in volume, weight, or flow. Substitution of a hazardous material (Risk Class ≥ 3) with an equivalent within the same risk class and quantity variation ≤ 20%. Modifications to process systems (vessels, piping, relief devices) within existing design parameters</t>
         </is>
       </c>
-      <c r="D77" s="268" t="inlineStr">
+      <c r="D77" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Change of conditions. a) New process or component; b) New hazardous materials not currently present; c) Change of any process parameter that affects system integrity, the Safe Operating Envelope, or existing safeguards; d) Modifications to process systems (vessels, piping, relief devices) outside existing design parameters or affecting safeguard integrity</t>
         </is>
       </c>
     </row>
     <row r="78" ht="86.4" customHeight="1">
-      <c r="A78" s="268" t="inlineStr">
+      <c r="A78" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Change of Procedure</t>
         </is>
       </c>
-      <c r="B78" s="268" t="inlineStr">
+      <c r="B78" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Minor update. Editorial correction or clarification of an existing procedure with no change to operational sequence, frequency, or responsibilities</t>
         </is>
       </c>
-      <c r="C78" s="268" t="inlineStr">
+      <c r="C78" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Operational modification. Change of sequence, frequency, or responsible party in a key operational, maintenance, or emergency response procedure</t>
         </is>
       </c>
-      <c r="D78" s="268" t="inlineStr">
+      <c r="D78" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">New procedure or elimination of control. Creation of a procedure for a previously undefined operation, or removal of an existing safety critical control step. Includes changes to emergency response plans</t>
         </is>
       </c>
     </row>
     <row r="79" ht="86.4" customHeight="1">
-      <c r="A79" s="268" t="inlineStr">
+      <c r="A79" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Change of Control Systems / IT / SIS</t>
         </is>
       </c>
-      <c r="B79" s="268" t="inlineStr">
+      <c r="B79" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Configuration change. Minor adjustment to alarm setpoints or display parameters within approved operating ranges; no change to logic or interlocks</t>
         </is>
       </c>
-      <c r="C79" s="268" t="inlineStr">
+      <c r="C79" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Software or logic modification. Modification to control system logic, PLC/DCS programming, or alarm management system; no change to SIS/SIL functions</t>
         </is>
       </c>
-      <c r="D79" s="268" t="inlineStr">
+      <c r="D79" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Safety system modification. Any change to Safety Instrumented Systems (SIS/SIL), emergency shutdown systems, or IT/OT systems that interface with safety-critical functions; or introduction of new control system architecture</t>
         </is>
       </c>
     </row>
     <row r="80" ht="86.4" customHeight="1">
-      <c r="A80" s="268" t="inlineStr">
+      <c r="A80" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">5. Organisational / Personnel Change</t>
         </is>
       </c>
-      <c r="B80" s="268" t="inlineStr">
+      <c r="B80" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Minor role change. Temporary reassignment of an operator within the same competency level, with no impact on critical safety roles or staffing levels</t>
         </is>
       </c>
-      <c r="C80" s="268" t="inlineStr">
+      <c r="C80" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Change of area responsible. Change of supervisor, coordinator, or key contractor in an operational area; safety-critical roles remain filled by competent personnel</t>
         </is>
       </c>
-      <c r="D80" s="268" t="inlineStr">
+      <c r="D80" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Loss or change of critical competency. Team restructuring, contractor change-out, or reduction of staffing in a risk-critical area. Includes situations where inexperienced personnel assume critical decision-making roles</t>
         </is>
       </c>
     </row>
     <row r="81" ht="129.6" customHeight="1">
-      <c r="A81" s="268" t="inlineStr">
+      <c r="A81" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">6. Temporary Change</t>
         </is>
       </c>
-      <c r="B81" s="268" t="inlineStr">
+      <c r="B81" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Short duration, low risk. Fully reversible, no impact on safeguards or safety-critical systems. Includes installation of temporary equipment with no safeguard implications. Removal date defined prior to implementation</t>
         </is>
       </c>
-      <c r="C81" s="268" t="inlineStr">
+      <c r="C81" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Extended duration, moderate risk. Reversible, with defined monitoring plan, removal date, and re-approval authority. Includes temporary equipment that affects operating procedures or non-safety-critical instrumentation. Scope clearly bounded and documented</t>
         </is>
       </c>
-      <c r="D81" s="268" t="inlineStr">
+      <c r="D81" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Safeguard-affecting. Any duration if it affects safety devices, alarms, interlocks, or passive safeguards. Includes installation or removal of temporary equipment that bypasses or impairs any safeguard. Scope or duration must not be exceeded without formal review and re-approval</t>
         </is>
       </c>
     </row>
     <row r="82" ht="72.0" customHeight="1">
-      <c r="A82" s="268" t="inlineStr">
+      <c r="A82" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Regulatory / Permit-Driven Change</t>
         </is>
       </c>
-      <c r="B82" s="268" t="inlineStr">
+      <c r="B82" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Administrative update. Change requires notification to a regulatory body but no amendment to existing permits or licences</t>
         </is>
       </c>
-      <c r="C82" s="268" t="inlineStr">
+      <c r="C82" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Permit amendment. Change requires amendment to one or more existing environmental or operating permits</t>
         </is>
       </c>
-      <c r="D82" s="268" t="inlineStr">
+      <c r="D82" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">New permit or consent required. Change requires a new licence, permit, or regulatory consent (e.g. Environmental Permit, HSE Reports, Hazardous Substances Consent) prior to implementation</t>
         </is>
       </c>
     </row>
     <row r="83" ht="144.0" customHeight="1">
-      <c r="A83" s="268" t="inlineStr">
+      <c r="A83" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">8. Changes to Utility &amp; HSE Protection Systems</t>
         </is>
       </c>
-      <c r="B83" s="268" t="inlineStr">
+      <c r="B83" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Minor adjustment. Modification to utility systems (steam, air, nitrogen, water) or HSE protection infrastructure (bunding, drainage, fire suppression, gas detection) within existing design parameters and with no reduction in protection standard</t>
         </is>
       </c>
-      <c r="C83" s="268" t="inlineStr">
+      <c r="C83" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Moderate modification. Change to utility systems or HSE protection infrastructure that temporarily reduces protection standard but with compensatory measures defined and in place; or change that requires review and update of inspection or maintenance schedules</t>
         </is>
       </c>
-      <c r="D83" s="268" t="inlineStr">
+      <c r="D83" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Significant modification or removal. Change that permanently reduces the standard of HSE protection (e.g. reduction in bund capacity, removal or relocation of gas detection, modification to fire suppression coverage); or change to utility systems that affects the operability of safety-critical equipment</t>
         </is>
@@ -64749,35 +64900,35 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="268" t="inlineStr">
+      <c r="A86" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Landing of a floating deck / roof (IFR landing)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="268" t="inlineStr">
+      <c r="A87" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Tank entry</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="268" t="inlineStr">
+      <c r="A88" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Any change to Safety Critical Equipment purchasing, maintenance or spares holding</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="268" t="inlineStr">
+      <c r="A89" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Safety Critical Equipment out of service / safeguard bypassed (any duration)</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="268" t="inlineStr">
+      <c r="A90" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Over-capacity of a dry bulk terminal [TBC]</t>
         </is>

--- a/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
+++ b/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
@@ -5836,7 +5836,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="279">
+  <cellXfs count="280">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6561,11 +6561,11 @@
     <xf numFmtId="0" fontId="26" fillId="10" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyFill="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyFill="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyFill="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyFill="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -6582,14 +6582,17 @@
     <xf numFmtId="0" fontId="33" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyFill="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyFill="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="32" xfId="0" applyBorder="1" applyAlignment="1" applyFill="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyFill="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyFill="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="10" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyFill="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -28962,8 +28965,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DecisionsTasks" displayName="DecisionsTasks" ref="A4:E30" totalsRowCount="1" headerRowDxfId="1946" headerRowBorderDxfId="1945">
-  <autoFilter ref="A4:E29" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DecisionsTasks" displayName="DecisionsTasks" ref="A4:E33" totalsRowCount="1" headerRowDxfId="1946" headerRowBorderDxfId="1945">
+  <autoFilter ref="A4:E32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="#" totalsRowLabel="Totals" dataDxfId="1944"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Task or Decision" totalsRowFunction="count" totalsRowDxfId="1943"/>
@@ -30016,7 +30019,7 @@
       <c r="F27" s="165"/>
       <c r="G27" s="165"/>
     </row>
-    <row r="28" ht="72.0" thickBot="1" x14ac:dyDescent="0.6" customHeight="1">
+    <row r="28" ht="86.4" thickBot="1" x14ac:dyDescent="0.6" customHeight="1">
       <c r="B28" s="212">
         <v>1.2</v>
       </c>
@@ -30030,7 +30033,7 @@
       </c>
       <c r="E28" s="214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala requirements - DRAFT for Design Workshop (27-Oct-2026). Sources: ILX App Overview 19-Oct-2026, Impala internal pre-design sessions 20-Oct and 21-Oct-2026, 'MOC Proposal.xlsx' (priority), BRD BO-61 v2.0 B.3 (complementary), SOW v1.5. Changes flagged A/R/M, highlighted in yellow, rationale in 'Impala Notes' columns. Open points marked [TBC].</t>
+          <t xml:space="preserve">Impala requirements - DRAFT for Design Workshop (27-Oct-2026). Sources: ILX App Overview 19-Oct-2026, Impala internal pre-design sessions 20-Oct and 21-Oct-2026, 'MOC Proposal Rev2.xlsx' incl. 'Workflow Stage Requirements' (priority), BRD BO-61 v2.0 B.3 (complementary), SOW v1.5. Changes flagged A/R/M, highlighted in yellow, rationale in 'Impala Notes' columns. Open points marked [TBC].</t>
         </is>
       </c>
       <c r="F28" s="214" t="inlineStr">
@@ -30305,7 +30308,7 @@
       </c>
       <c r="G11" s="250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Screening questions filtered by Type of Change, stage, Grade and location (Universal / Liquids / Dry).</t>
+          <t xml:space="preserve">Screening questions filtered by Change Type, stage, Change Impact, Simple Change and location (Universal / Liquids / Dry).</t>
         </is>
       </c>
     </row>
@@ -30426,27 +30429,27 @@
           <t xml:space="preserve">AH13</t>
         </is>
       </c>
-      <c r="B18" s="272" t="inlineStr">
+      <c r="B18" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">MOC</t>
         </is>
       </c>
-      <c r="C18" s="272" t="inlineStr">
+      <c r="C18" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Automatic Major validation</t>
         </is>
       </c>
-      <c r="D18" s="272" t="inlineStr">
+      <c r="D18" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Activities on the Automatic Major list must be graded Major.</t>
         </is>
       </c>
-      <c r="E18" s="272" t="inlineStr">
+      <c r="E18" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Create, Update</t>
         </is>
       </c>
-      <c r="F18" s="273" t="inlineStr">
+      <c r="F18" s="274" t="inlineStr">
         <is>
           <t xml:space="preserve">If AutomaticMajor = Yes and ChangeImpact &lt;&gt; 'Major'
 • then error: 'Activities on the Automatic Major list must be graded Major.'</t>
@@ -30464,27 +30467,27 @@
           <t xml:space="preserve">AH14</t>
         </is>
       </c>
-      <c r="B19" s="272" t="inlineStr">
+      <c r="B19" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">MOC</t>
         </is>
       </c>
-      <c r="C19" s="272" t="inlineStr">
+      <c r="C19" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Approval stage gate</t>
         </is>
       </c>
-      <c r="D19" s="272" t="inlineStr">
+      <c r="D19" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">At least one approval before leaving the Approval stage.</t>
         </is>
       </c>
-      <c r="E19" s="272" t="inlineStr">
+      <c r="E19" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Update</t>
         </is>
       </c>
-      <c r="F19" s="273" t="inlineStr">
+      <c r="F19" s="274" t="inlineStr">
         <is>
           <t xml:space="preserve">If Workflow.CurrentStage = 'Approval' and action = Submit and count(Approvals) = 0
 • then error: 'At least one approval is required.'</t>
@@ -30502,27 +30505,27 @@
           <t xml:space="preserve">AH15</t>
         </is>
       </c>
-      <c r="B20" s="272" t="inlineStr">
+      <c r="B20" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">MOC Approval</t>
         </is>
       </c>
-      <c r="C20" s="272" t="inlineStr">
+      <c r="C20" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Sequential approvals</t>
         </is>
       </c>
-      <c r="D20" s="272" t="inlineStr">
+      <c r="D20" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Request next approval level only when the previous one is closed.</t>
         </is>
       </c>
-      <c r="E20" s="272" t="inlineStr">
+      <c r="E20" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Update</t>
         </is>
       </c>
-      <c r="F20" s="273" t="inlineStr">
+      <c r="F20" s="274" t="inlineStr">
         <is>
           <t xml:space="preserve">When all Local approvals are Closed • submit Regional approvals (Draft &gt; In Progress).
 When all Regional approvals are Closed • submit Global approvals. [Intelex to propose solution / confirm scope]</t>
@@ -30540,27 +30543,27 @@
           <t xml:space="preserve">AH16</t>
         </is>
       </c>
-      <c r="B21" s="272" t="inlineStr">
+      <c r="B21" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">MOC</t>
         </is>
       </c>
-      <c r="C21" s="272" t="inlineStr">
+      <c r="C21" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Temporary change extension limit</t>
         </is>
       </c>
-      <c r="D21" s="272" t="inlineStr">
+      <c r="D21" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Max 3 extensions (BRD RULE-B3-08).</t>
         </is>
       </c>
-      <c r="E21" s="272" t="inlineStr">
+      <c r="E21" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Create, Update</t>
         </is>
       </c>
-      <c r="F21" s="273" t="inlineStr">
+      <c r="F21" s="274" t="inlineStr">
         <is>
           <t xml:space="preserve">If NumberOfExtensions &gt; 3
 • then error: 'A temporary change cannot be extended more than 3 times - raise a permanent MOC.'</t>
@@ -30578,27 +30581,27 @@
           <t xml:space="preserve">AH17</t>
         </is>
       </c>
-      <c r="B22" s="272" t="inlineStr">
+      <c r="B22" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">MOC</t>
         </is>
       </c>
-      <c r="C22" s="272" t="inlineStr">
+      <c r="C22" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Emergency regularisation gate</t>
         </is>
       </c>
-      <c r="D22" s="272" t="inlineStr">
+      <c r="D22" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Emergency MOC cannot close until regularised (BRD RULE-B3-14).</t>
         </is>
       </c>
-      <c r="E22" s="272" t="inlineStr">
+      <c r="E22" s="273" t="inlineStr">
         <is>
           <t xml:space="preserve">Update</t>
         </is>
       </c>
-      <c r="F22" s="273" t="inlineStr">
+      <c r="F22" s="274" t="inlineStr">
         <is>
           <t xml:space="preserve">If EmergencyChange = Yes and action = Close and (unanswered screening questions or open tasks)
 • then error: 'Complete the retrospective MOC dossier before closing.'</t>
@@ -30768,9 +30771,9 @@
       <c r="D6" s="102" t="s">
         <v>680</v>
       </c>
-      <c r="E6" s="274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC No. | Location | Change Description | Emergency Change? | Temporary Change? | Type of Change | Grade of Change | Requested Date Change | Status | Workflow Status</t>
+      <c r="E6" s="275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC No. | Location | Change Description | Emergency Change? | Simple Change? | Temporary Change? | Change Type | Change Impact | Requested Date Change | Status | Workflow Status</t>
         </is>
       </c>
       <c r="F6" s="103" t="s">
@@ -30797,9 +30800,9 @@
       <c r="M6" s="102" t="s">
         <v>184</v>
       </c>
-      <c r="N6" s="275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M - columns: Replacement in Kind removed (unless re-used as 'Simplified MOC?' [TBC]); Type of Change + Grade of Change. Grouping by Status instead of Category [TBC].</t>
+      <c r="N6" s="276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M - columns: Replacement in Kind -&gt; Simple Change?; Change Type + Change Impact. Grouping by Status instead of Category [TBC].</t>
         </is>
       </c>
     </row>
@@ -30956,7 +30959,7 @@
       <c r="M10" s="101" t="s">
         <v>184</v>
       </c>
-      <c r="N10" s="275" t="inlineStr">
+      <c r="N10" s="276" t="inlineStr">
         <is>
           <t xml:space="preserve">Screening questions loaded by Excel import (Universal / Liquids / Dry).</t>
         </is>
@@ -31051,62 +31054,62 @@
           <t xml:space="preserve">My MOCs</t>
         </is>
       </c>
-      <c r="C13" s="276" t="inlineStr">
+      <c r="C13" s="277" t="inlineStr">
         <is>
           <t xml:space="preserve">Inventory</t>
         </is>
       </c>
-      <c r="D13" s="276" t="inlineStr">
+      <c r="D13" s="277" t="inlineStr">
         <is>
           <t xml:space="preserve">MOCs where the user is Change Requester or Person Responsible</t>
         </is>
       </c>
-      <c r="E13" s="276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC No. | Location | Change Description | Type of Change | Grade of Change | Status | Person Responsible</t>
-        </is>
-      </c>
-      <c r="F13" s="277" t="inlineStr">
+      <c r="E13" s="277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC No. | Location | Change Description | Change Type | Change Impact | Status | Person Responsible</t>
+        </is>
+      </c>
+      <c r="F13" s="278" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="G13" s="277" t="inlineStr">
+      <c r="G13" s="278" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="H13" s="277" t="inlineStr">
+      <c r="H13" s="278" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="I13" s="278" t="inlineStr">
+      <c r="I13" s="279" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="J13" s="278" t="inlineStr">
+      <c r="J13" s="279" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="K13" s="275" t="inlineStr">
+      <c r="K13" s="276" t="inlineStr">
         <is>
           <t xml:space="preserve">MOC No. (descending)</t>
         </is>
       </c>
-      <c r="L13" s="275" t="inlineStr">
+      <c r="L13" s="276" t="inlineStr">
         <is>
           <t xml:space="preserve">N/A</t>
         </is>
       </c>
-      <c r="M13" s="275" t="inlineStr">
+      <c r="M13" s="276" t="inlineStr">
         <is>
           <t xml:space="preserve">Change Requester = Me OR Person Responsible = Me</t>
         </is>
       </c>
-      <c r="N13" s="275" t="inlineStr">
+      <c r="N13" s="276" t="inlineStr">
         <is>
           <t xml:space="preserve">A - new tab.</t>
         </is>
@@ -31123,62 +31126,62 @@
           <t xml:space="preserve">Temporary Changes</t>
         </is>
       </c>
-      <c r="C14" s="276" t="inlineStr">
+      <c r="C14" s="277" t="inlineStr">
         <is>
           <t xml:space="preserve">Inventory</t>
         </is>
       </c>
-      <c r="D14" s="276" t="inlineStr">
+      <c r="D14" s="277" t="inlineStr">
         <is>
           <t xml:space="preserve">Open temporary changes ordered by expiry</t>
         </is>
       </c>
-      <c r="E14" s="276" t="inlineStr">
+      <c r="E14" s="277" t="inlineStr">
         <is>
           <t xml:space="preserve">MOC No. | Location | Change Description | Change Expiry | Status | Person Responsible</t>
         </is>
       </c>
-      <c r="F14" s="277" t="inlineStr">
+      <c r="F14" s="278" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="G14" s="277" t="inlineStr">
+      <c r="G14" s="278" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="H14" s="277" t="inlineStr">
+      <c r="H14" s="278" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="I14" s="278" t="inlineStr">
+      <c r="I14" s="279" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="J14" s="278" t="inlineStr">
+      <c r="J14" s="279" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="K14" s="275" t="inlineStr">
+      <c r="K14" s="276" t="inlineStr">
         <is>
           <t xml:space="preserve">Change Expiry (ascending)</t>
         </is>
       </c>
-      <c r="L14" s="275" t="inlineStr">
+      <c r="L14" s="276" t="inlineStr">
         <is>
           <t xml:space="preserve">N/A</t>
         </is>
       </c>
-      <c r="M14" s="275" t="inlineStr">
+      <c r="M14" s="276" t="inlineStr">
         <is>
           <t xml:space="preserve">Temporary Change = Yes AND Status not Closed/Cancelled</t>
         </is>
       </c>
-      <c r="N14" s="275" t="inlineStr">
+      <c r="N14" s="276" t="inlineStr">
         <is>
           <t xml:space="preserve">A - new tab.</t>
         </is>
@@ -31292,7 +31295,7 @@
         </is>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.55000000000000004" ht="28.8" customHeight="1">
+    <row r="4" x14ac:dyDescent="0.55000000000000004" ht="14.4" customHeight="1">
       <c r="A4" s="150" t="s">
         <v>217</v>
       </c>
@@ -31316,7 +31319,7 @@
       </c>
       <c r="H4" s="250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of Change data maintained by System Admin / MOC Administrator.</t>
+          <t xml:space="preserve">Change Type data maintained by System Admin / MOC Administrator.</t>
         </is>
       </c>
     </row>
@@ -36467,7 +36470,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultColWidth="29.5234375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -36547,23 +36550,23 @@
       </c>
       <c r="E6" s="52"/>
     </row>
-    <row r="7" x14ac:dyDescent="0.55000000000000004" ht="72.0" customHeight="1">
+    <row r="7" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
       <c r="A7" s="5">
         <v>3</v>
       </c>
       <c r="B7" s="215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Replacement in Kind: remove or re-use as 'Simplified MOC' route</t>
+          <t xml:space="preserve">Replacement in Kind re-used as 'Simple Change'</t>
         </is>
       </c>
       <c r="C7" s="215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impala - Sam Robinson / Rodrigo Llamas</t>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
         </is>
       </c>
       <c r="D7" s="215" t="inlineStr">
         <is>
-          <t xml:space="preserve">STILL OPEN after 21-Oct (Sam: 'remove it or use it for a simplified workflow, come back to that'). 20-Oct: like-for-like is not a change per procedure, so the field as such is not needed. But its OOTB skip-path could be re-captioned (e.g. 'Simplified MOC?') to give the simplified route for organisational / IT changes without a new workflow. Decide: remove, or re-use (and define which stages it skips).</t>
+          <t xml:space="preserve">DECIDED (Sam Rev2): 'Replacement in Kind' re-captioned 'Simple Change?' (mandatory). Same workflow but WITHOUT the Evaluation, D&amp;A checklist; intended for IT / organisational changes. OOTB skip-to-Implementation path removed. [TBC] what the 'different process review' for IT / Org changes requires.</t>
         </is>
       </c>
       <c r="E7" s="52"/>
@@ -36616,7 +36619,7 @@
       </c>
       <c r="B10" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Change classification = Type of Change (8) x Grade (Minor/Moderate/Major); Level 1-5 scoring dropped</t>
+          <t xml:space="preserve">Change classification = Change Type (8) x Change Impact (Minor/Moderate/Major); Level 1-5 scoring dropped</t>
         </is>
       </c>
       <c r="C10" s="216" t="inlineStr">
@@ -36626,12 +36629,12 @@
       </c>
       <c r="D10" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct: Change Impact linked to the category (= type of change); matrix covers grade of change AND grade of hazard, so no scoring needed. Matrix OUT FOR TEAM REVIEW (check nothing previously Level 4 now comes out Minor). Per 'MOC Proposal.xlsx' (Sam): Minor = Local (TM), Moderate = Regional (HSEC + Ops), Major = Global (HSEC + Ops). Grade descriptors per type + 'Automatic Major' examples. Sam to circulate the updated matrix; Shaun to explain the rationale to Stylianos (internal alignment, not a configuration blocker). Procedure update + retraining required.</t>
+          <t xml:space="preserve">21-Oct: Change Impact linked to the category (= type of change); matrix covers grade of change AND grade of hazard, so no scoring needed. Matrix OUT FOR TEAM REVIEW (check nothing previously Level 4 now comes out Minor). Per 'MOC Proposal.xlsx' (Sam): Minor = Local (TM), Moderate = Regional (HSEC + Ops), Major = Global (HSEC + Ops). Change Impact guidance per type + 'Automatic Major' examples. Sam to circulate the updated matrix; Shaun to explain the rationale to Stylianos (internal alignment, not a configuration blocker). Procedure update + retraining required.</t>
         </is>
       </c>
       <c r="E10" s="52"/>
     </row>
-    <row r="11" x14ac:dyDescent="0.55000000000000004" ht="57.6" customHeight="1">
+    <row r="11" x14ac:dyDescent="0.55000000000000004" ht="86.4" customHeight="1">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -36647,7 +36650,7 @@
       </c>
       <c r="D11" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Checklist 'Evaluation, D&amp;A Checklist' loaded as screening questions (Excel import). Part 1 at top location, Part 2 at Liquids segment, Part 3 at Dry segment (triggered by location - confirmed 21-Oct). List under team review. OPEN: same checklist for all changes, or questions shown only for certain types of change [TBC]. Location-specific checklists = Phase 2.</t>
+          <t xml:space="preserve">Checklist 'Evaluation, D&amp;A Checklist' loaded as screening questions (Excel import). Part 1 at top location, Part 2 at Liquids segment, Part 3 at Dry segment (triggered by location - confirmed 21-Oct). List under team review. Sam Rev2: checklist is a MINIMUM, users can add items; answered in Evaluation, D&amp;A, view-only afterwards; not generated for Simple Changes. OPEN: link checklist items to Change Type / Change Impact (e.g. HAZOP mandatory for Major equipment change) [TBC]. Location-specific checklists = Phase 2.</t>
         </is>
       </c>
       <c r="E11" s="52"/>
@@ -36689,7 +36692,7 @@
       </c>
       <c r="D13" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">REQUIRED 21-Oct (Khesar / Sam): OOTB a stage cannot be submitted with open tasks, but some tasks identified in Evaluation are only due later (e.g. P&amp;ID update post-change). Add on each MOC Task a 'Complete before stage' field (Implementation / Start Up / Follow Up); the stage gate checks only tasks due for that stage. Covers BRD FR-B3-032.</t>
+          <t xml:space="preserve">REQUIRED 21-Oct (Khesar / Sam): OOTB a stage cannot be submitted with open tasks, but some tasks identified in Evaluation are only due later (e.g. P&amp;ID update post-change). Add on each MOC Task a 'Complete before stage' field 'Required Before' = Pre-Implementation / Pre-Follow Up (Sam Rev2); the stage gate checks only tasks due for that stage. Covers BRD FR-B3-032.</t>
         </is>
       </c>
       <c r="E13" s="52"/>
@@ -36757,7 +36760,7 @@
       </c>
       <c r="E16" s="52"/>
     </row>
-    <row r="17" ht="43.2" customHeight="1">
+    <row r="17" ht="57.6" customHeight="1">
       <c r="A17" s="217">
         <v>13</v>
       </c>
@@ -36773,12 +36776,12 @@
       </c>
       <c r="D17" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">ACTION 21-Oct (Shaun): map per stage what we ask, which documents we expect/mandate and where we approve. Sam to update his workbook (EOD 21-Oct); Rodrigo to transfer to this workbook. Also: Follow Up questions from the MOC audit form (Sam).</t>
+          <t xml:space="preserve">DONE: Sam Rev2 tab 'Workflow Stage Requirements' transferred to Fields (mandatory flags, conditional justifications). Origin: 21-Oct (Shaun): map per stage what we ask, which documents we expect/mandate and where we approve. Sam to update his workbook (EOD 21-Oct); Rodrigo to transfer to this workbook. Also: Follow Up questions from the MOC audit form (Sam).</t>
         </is>
       </c>
       <c r="E17" s="52"/>
     </row>
-    <row r="18" ht="43.2" customHeight="1">
+    <row r="18" ht="14.4" customHeight="1">
       <c r="A18" s="217">
         <v>14</v>
       </c>
@@ -36789,12 +36792,12 @@
       </c>
       <c r="C18" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intelex - Ian</t>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
         </is>
       </c>
       <c r="D18" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN: Intelex to confirm whether the simplified/'Change Request' workflow seen in the demo site is in SOW. Impala priority: finalise the full MOC first; Emergency kept minimal (low volume).</t>
+          <t xml:space="preserve">COVERED by 'Simple Change?' (Sam Rev2) - no separate workflow requested from Intelex.</t>
         </is>
       </c>
       <c r="E18" s="52"/>
@@ -36941,7 +36944,7 @@
       </c>
       <c r="D25" s="216" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTLY ANSWERED 21-Oct: Local = at least one functional reviewer (Ops/Maintenance) + TM (so &gt;= 2, in line with BRD). Regional and Global = HSEC + Operations. Exact rule per level to be written in Sam's per-stage map. BRD BO-61 to be updated for Level 0-5 scoring (housekeeping).</t>
+          <t xml:space="preserve">DECIDED (Sam Rev2 matrix): Minor = TM plus at least one technical specialist from within the terminal (&gt;= 2, in line with BRD). Moderate = Regional HSEC + Ops; Major = Global HSEC + Ops (after Local and Regional). BRD BO-61 to be updated for Level 0-5 scoring (housekeeping).</t>
         </is>
       </c>
       <c r="E25" s="52"/>
@@ -37009,36 +37012,99 @@
       </c>
       <c r="E28" s="52"/>
     </row>
-    <row r="29" ht="43.2" customHeight="1">
+    <row r="29" ht="28.8" customHeight="1">
       <c r="A29" s="217">
         <v>25</v>
       </c>
       <c r="B29" s="216" t="inlineStr">
         <is>
+          <t xml:space="preserve">Priority kept</t>
+        </is>
+      </c>
+      <c r="C29" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
+        </is>
+      </c>
+      <c r="D29" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sam Rev2: Priority is mandatory (selection list). [TBC] values (Low/Medium/High?) and whether it drives anything.</t>
+        </is>
+      </c>
+      <c r="E29" s="52"/>
+    </row>
+    <row r="30" ht="28.8" customHeight="1">
+      <c r="A30" s="217">
+        <v>26</v>
+      </c>
+      <c r="B30" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TM re-approval at later stages?</t>
+        </is>
+      </c>
+      <c r="C30" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
+        </is>
+      </c>
+      <c r="D30" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN (Sam Rev2: 'Terminal Manager must re-approve at this stage??' at Implementation, Start Up and Follow Up). Ad hoc approvals allowed in all stages anyway.</t>
+        </is>
+      </c>
+      <c r="E30" s="52"/>
+    </row>
+    <row r="31" ht="14.4" customHeight="1">
+      <c r="A31" s="217">
+        <v>27</v>
+      </c>
+      <c r="B31" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PSSR mandatory only for Moderate / Major?</t>
+        </is>
+      </c>
+      <c r="C31" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impala - Sam Robinson</t>
+        </is>
+      </c>
+      <c r="D31" s="216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN (Sam Rev2: 'Mandated for Moderate/Major only?').</t>
+        </is>
+      </c>
+      <c r="E31" s="52"/>
+    </row>
+    <row r="32" ht="43.2" customHeight="1">
+      <c r="A32" s="217">
+        <v>28</v>
+      </c>
+      <c r="B32" s="216" t="inlineStr">
+        <is>
           <t xml:space="preserve">MoC KPIs and leadership reporting</t>
         </is>
       </c>
-      <c r="C29" s="216" t="inlineStr">
+      <c r="C32" s="216" t="inlineStr">
         <is>
           <t xml:space="preserve">Impala - Rodrigo Llamas</t>
         </is>
       </c>
-      <c r="D29" s="216" t="inlineStr">
+      <c r="D32" s="216" t="inlineStr">
         <is>
           <t xml:space="preserve">BRD FR-B3-019 / FR-B3-033: monthly YTD permanent/temporary MOCs, open MOCs, overdue temporary MOCs, MoC-related incidents, open MoC actions + leading indicators. To be built as reports/dashboards (reporting phase), fields already captured in this workbook.</t>
         </is>
       </c>
-      <c r="E29" s="52"/>
-    </row>
-    <row r="30" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
+      <c r="E32" s="52"/>
+    </row>
+    <row r="33" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B33" s="29">
         <f>SUBTOTAL(103,DecisionsTasks[Task or Decision])</f>
         <v>2</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E33" s="29">
         <f>SUBTOTAL(103,DecisionsTasks[Date Complete])</f>
         <v>0</v>
       </c>
@@ -37169,7 +37235,7 @@
         </is>
       </c>
     </row>
-    <row r="68" x14ac:dyDescent="0.55000000000000004" ht="72.0" customHeight="1">
+    <row r="68" x14ac:dyDescent="0.55000000000000004" ht="86.4" customHeight="1">
       <c r="A68" s="132">
         <v>1</v>
       </c>
@@ -37203,7 +37269,7 @@
         <is>
           <t xml:space="preserve">Recipient(s): Change Requester, MOC Coordinator (Role)
 N11 to Terminal Manager + Regional HSEC if Emergency = Yes.
-Prior to submit: Change Description, Type of Change, Grade of Change, Reason for Change &amp; Technical Basis mandatory; Emergency Justification if Emergency = Yes; Change Expiry if Temporary = Yes.</t>
+Prior to submit (Sam Rev2): Location, Change Description, Emergency, Simple, Temporary, Change Type, Change Impact, Priority, Change Justification, Requested Change Date mandatory. Simple Change = Yes: same workflow, no checklist; Emergency Justification if Emergency = Yes; Change Expiry if Temporary = Yes.</t>
         </is>
       </c>
       <c r="J68" s="239" t="inlineStr">
@@ -37249,7 +37315,7 @@
         <is>
           <t xml:space="preserve">Recipient(s): Change Requester
 Replaces OOTB Pre-Approval, Evaluation and Design &amp; Analysis stages.
-Prior to transitioning: all screening questions and stage questions answered, design documents attached, and tasks whose 'Complete before stage' = Approval closed (tasks due later stay open).</t>
+Prior to transitioning (Sam Rev2): all checklist items and mandatory D&amp;A questions answered (with justifications), design documents attached. Tasks stay open until their 'Required Before' stage.</t>
         </is>
       </c>
       <c r="J69" s="239" t="inlineStr">
@@ -37336,8 +37402,8 @@
       <c r="I72" s="219" t="inlineStr">
         <is>
           <t xml:space="preserve">Recipient(s): Change Requester
-Approvals auto-generated on stage entry by Grade of Change:
-- Minor: Local = functional review (Operations / Maintenance) + Terminal Manager final sign-off
+Approvals auto-generated on stage entry by Change Impact:
+- Minor: Local = Terminal Manager + at least one technical specialist from the terminal (Sam Rev2)
 - Moderate: Local &gt; Regional HSEC + Regional Operations
 - Major: Local &gt; Regional &gt; Global HSEC + Global Operations (confirmed 21-Oct)
 Approvals are SEQUENTIAL and AUTOMATIC: when the TM approves, the next level is added and triggered by the system (Intelex to confirm solution). The single main approval happens here, before construction/activity starts.
@@ -37395,7 +37461,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="72.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="75" ht="86.4" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A75" s="139">
         <v>4</v>
       </c>
@@ -37429,8 +37495,9 @@
       <c r="I75" s="223" t="inlineStr">
         <is>
           <t xml:space="preserve">Recipient(s): Change Requester
-Prior to transitioning: tasks with 'Complete before stage' = Start Up (pre-startup actions, PSSR) closed; Implementation questions answered. Post-startup tasks (e.g. P&amp;ID update) stay open until Follow Up (BRD FR-B3-028 / FR-B3-032).
-Optional local pre-startup approval [TBC] - main approval already given.</t>
+Entry from Approval only when tasks 'Required Before' = Pre-Implementation are closed.
+Prior to transitioning: mandatory Implementation questions answered (PSSR [TBC Moderate/Major only], training, communication, installation, critical PSSR items) with justifications.
+TM re-approval at this stage? [TBC]</t>
         </is>
       </c>
     </row>
@@ -37556,7 +37623,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="129.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="81" ht="158.4" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A81" s="139">
         <v>6</v>
       </c>
@@ -37593,6 +37660,7 @@
 Prior to closing:
 - All tasks and approvals have to be completed.
 - If 'Temporary Change' = Yes, then 'Has Temporary Change been scheduled for permanent MOC?' must be 'Yes' (or temporary change removed).
+- Entry from Start Up only when tasks 'Required Before' = Pre-Follow Up are closed (Sam Rev2).
 - If 'Emergency Change' = Yes: all screening questions answered and tasks closed (retrospective regularisation, BRD RULE-B3-14).
 - Post-MoC verification fields completed (field check, communication, downstream impacts).</t>
         </is>
@@ -38383,9 +38451,10 @@
 Status : {#Workflow.Status}
 Change Description: {#ChanDescription}
 Emergency Change : {#EmergencyChange}
+Simple Change : {#ReplacemeinKind}
 Temporary Change: {#TemporaryChange}
-Type of Change: {#MOCCategory}
-Grade of Change: {#ChangeImpact}
+Change Type: {#MOCCategory}
+Change Impact: {#ChangeImpact}
 Requested Change Date: {#RequeChangeDate}
 Change Requester: {#ChangeRequester}
 --------------------------------------------------------
@@ -38394,7 +38463,7 @@
       </c>
       <c r="G5" s="251" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - stages renamed; body: Replacement in kind removed, Type of Change + Grade of Change added ({#ChangeImpact} system name to be confirmed by Intelex).</t>
+          <t xml:space="preserve">M - stages renamed; body: Replacement in kind -&gt; Simple Change, Change Type + Change Impact added ({#ChangeImpact} system name to be confirmed by Intelex).</t>
         </is>
       </c>
     </row>
@@ -38423,9 +38492,10 @@
 Status : {#Workflow.Status}
 Change Description: {#ChanDescription}
 Emergency Change : {#EmergencyChange}
+Simple Change : {#ReplacemeinKind}
 Temporary Change: {#TemporaryChange}
-Type of Change: {#MOCCategory}
-Grade of Change: {#ChangeImpact}
+Change Type: {#MOCCategory}
+Change Impact: {#ChangeImpact}
 Requested Change Date: {#RequeChangeDate}
 --------------------------------------------------------
 Please login to view full details of the report.</t>
@@ -38433,7 +38503,7 @@
       </c>
       <c r="G6" s="251" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - body: Replacement in kind removed, Type/Grade of Change added.</t>
+          <t xml:space="preserve">M - body: Replacement in kind -&gt; Simple Change, Change Type / Change Impact added.</t>
         </is>
       </c>
     </row>
@@ -38462,6 +38532,7 @@
 Status : Cancelled
 Change Description: {#ChanDescription}
 Emergency Change : {#EmergencyChange}
+Simple Change : {#ReplacemeinKind}
 Temporary Change: {#TemporaryChange}
 Change Impact: {#ChangeImpact}
 MOC Category: {#Category}
@@ -38473,7 +38544,7 @@
       </c>
       <c r="G7" s="251" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - body: Replacement in kind removed, Type/Grade of Change added.</t>
+          <t xml:space="preserve">M - body: Replacement in kind -&gt; Simple Change, Change Type / Change Impact added.</t>
         </is>
       </c>
     </row>
@@ -38502,9 +38573,10 @@
 Status : Closed
 Change Description: {#ChanDescription}
 Emergency Change : {#EmergencyChange}
+Simple Change : {#ReplacemeinKind}
 Temporary Change: {#TemporaryChange}
-Type of Change: {#MOCCategory}
-Grade of Change: {#ChangeImpact}
+Change Type: {#MOCCategory}
+Change Impact: {#ChangeImpact}
 Requested Change Date: {#RequeChangeDate}
 Completion Date: {#Workflow.DateModified}
 --------------------------------------------------------
@@ -38513,7 +38585,7 @@
       </c>
       <c r="G8" s="251" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - body: Replacement in kind removed, Type/Grade of Change added.</t>
+          <t xml:space="preserve">M - body: Replacement in kind -&gt; Simple Change, Change Type / Change Impact added.</t>
         </is>
       </c>
     </row>
@@ -38691,8 +38763,8 @@
 Location: {#Location}
 Change Description: {#ChanDescription}
 Emergency Justification: {#EmergencyJustification}
-Type of Change: {#MOCCategory}
-Grade of Change: {#ChangeImpact}
+Change Type: {#MOCCategory}
+Change Impact: {#ChangeImpact}
 Change Requester: {#ChangeRequester}
 --------------------------------------------------------
 Please login to view full details of the report.</t>
@@ -39776,7 +39848,7 @@
       </c>
       <c r="N54" s="245" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - caption: 'Type of Change'. Data = 8 types (Lookup Values L08).</t>
+          <t xml:space="preserve">M - caption: 'Change Type'. Data = 8 types (Lookup Values L08).</t>
         </is>
       </c>
     </row>
@@ -40387,7 +40459,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AC354"/>
+  <dimension ref="A1:AC357"/>
   <sheetFormatPr defaultColWidth="26.41796875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="2.89453125" style="64" customWidth="1"/>
@@ -40560,7 +40632,7 @@
       </c>
       <c r="AB4" s="61"/>
     </row>
-    <row r="5" s="59" customFormat="1" ht="216.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="5" s="59" customFormat="1" ht="187.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A5" s="188">
         <v>1</v>
       </c>
@@ -40588,7 +40660,7 @@
       <c r="I5" s="187"/>
       <c r="J5" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value: Step 1. Select the Location and describe the change (what, why, technical basis, affected systems/people). Step 2. Select the Type of Change and the Grade of Change (Minor / Moderate / Major) using the guidance displayed for the selected type. Activities on the 'Automatic Major' list are always Major. Step 3. For temporary changes enter the Change Expiry date. Step 4. Submit.</t>
+          <t xml:space="preserve">Value: Step 1. Select the Location and describe the change. Step 2. Select Emergency, Simple and Temporary change flags. Step 3. Select the Change Type, then the Change Impact (Minor / Moderate / Major) using the guidance displayed for the selected type. Step 4. Enter Priority, Change Justification and Requested Change Date. Submit.</t>
         </is>
       </c>
       <c r="K5" s="254" t="inlineStr">
@@ -40639,7 +40711,7 @@
       <c r="Z5" s="253"/>
       <c r="AA5" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instructions rewritten for Type x Grade classification.</t>
+          <t xml:space="preserve">[SAM Rev2] Instructions follow the Initiation requirements.</t>
         </is>
       </c>
       <c r="AB5" s="61"/>
@@ -40721,12 +40793,12 @@
       <c r="Z6" s="253"/>
       <c r="AA6" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-Approval stage removed.</t>
+          <t xml:space="preserve">[SAM Rev2] Pre-Approval stage removed.</t>
         </is>
       </c>
       <c r="AB6" s="61"/>
     </row>
-    <row r="7" s="59" customFormat="1" ht="216.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="7" s="59" customFormat="1" ht="172.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A7" s="188">
         <v>3</v>
       </c>
@@ -40756,7 +40828,7 @@
       <c r="I7" s="187"/>
       <c r="J7" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value: Step 1. Answer all screening questions (checklist) generated for this MOC. Step 2. Create tasks for every item that requires action (Risk Assessment/HAZOP, Documentation, Training, PSSR...) and attach evidence. Step 3. Complete the Evaluation, Design &amp; Analysis details. Step 4. Submit to Approval when all screening questions are answered and all tasks of this stage are closed.</t>
+          <t xml:space="preserve">Value: Step 1. Answer all checklist items (add more if needed). Step 2. Create tasks and set whether each is required Pre-Implementation or Pre-Follow Up. Step 3. Complete the Design &amp; Analysis details and attach supporting documents. Step 4. Submit to Approval when all mandatory items are completed.</t>
         </is>
       </c>
       <c r="K7" s="254" t="inlineStr">
@@ -40807,12 +40879,12 @@
       <c r="Z7" s="253"/>
       <c r="AA7" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evaluation and Design &amp; Analysis merged into one stage.</t>
+          <t xml:space="preserve">[SAM Rev2] Evaluation and Design &amp; Analysis merged.</t>
         </is>
       </c>
       <c r="AB7" s="61"/>
     </row>
-    <row r="8" s="59" customFormat="1" ht="201.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="8" s="59" customFormat="1" ht="129.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A8" s="188">
         <v>4</v>
       </c>
@@ -40842,7 +40914,7 @@
       <c r="I8" s="187"/>
       <c r="J8" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value: Step 1. Review the approvals generated for the Grade of Change (Minor: Terminal Manager; Moderate: + Regional HSEC and Operations; Major: + Global HSEC and Operations). Step 2. Add additional approvers if needed. Step 3. Approvals are requested in sequence Local &gt; Regional &gt; Global. Step 4. Submit to Implementation when all approvals are closed.</t>
+          <t xml:space="preserve">Value: Mandated approvals are generated from the Change Impact matrix and requested in sequence Local &gt; Regional &gt; Global. Add ad hoc approvals if needed. Submit to Implementation when all approvals are closed.</t>
         </is>
       </c>
       <c r="K8" s="254" t="inlineStr">
@@ -40893,7 +40965,7 @@
       <c r="Z8" s="253"/>
       <c r="AA8" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Re-used as instructions of the new Approval stage.</t>
+          <t xml:space="preserve">[SAM Rev2] Re-used as instructions of the Approval stage.</t>
         </is>
       </c>
       <c r="AB8" s="61"/>
@@ -41120,7 +41192,7 @@
       <c r="AA11" s="60"/>
       <c r="AB11" s="61"/>
     </row>
-    <row r="12" s="59" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" s="59" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A12" s="188">
         <v>8</v>
       </c>
@@ -41193,7 +41265,11 @@
       </c>
       <c r="Y12" s="253"/>
       <c r="Z12" s="253"/>
-      <c r="AA12" s="60"/>
+      <c r="AA12" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Mandatory, selection list.</t>
+        </is>
+      </c>
       <c r="AB12" s="61"/>
     </row>
     <row r="13" s="59" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
@@ -41355,7 +41431,7 @@
       <c r="Z14" s="253"/>
       <c r="AA14" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mandatory (already changed by Intelex in TEST on 19-Oct).</t>
+          <t xml:space="preserve">[SAM Rev2] Mandatory, free form (already changed by Intelex in TEST).</t>
         </is>
       </c>
       <c r="AB14" s="61"/>
@@ -41390,7 +41466,7 @@
       </c>
       <c r="J15" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Default Value: Static Value: No. If Yes: Initiation &gt; Approval (skips Evaluation, Design &amp; Analysis).</t>
+          <t xml:space="preserve">Default Value: No. If Yes: Initiation &gt; Approval (skips Evaluation, Design &amp; Analysis).</t>
         </is>
       </c>
       <c r="K15" s="254" t="inlineStr">
@@ -41445,12 +41521,12 @@
       <c r="Z15" s="253"/>
       <c r="AA15" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emergency path now goes straight to Approval. Emergency Justification field added (new fields block).</t>
+          <t xml:space="preserve">[SAM Rev2] Mandatory; straight from Initiation to Approval.</t>
         </is>
       </c>
       <c r="AB15" s="61"/>
     </row>
-    <row r="16" s="59" customFormat="1" ht="172.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="16" s="59" customFormat="1" ht="115.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A16" s="188">
         <v>12</v>
       </c>
@@ -41463,11 +41539,15 @@
       <c r="D16" s="57" t="s">
         <v>578</v>
       </c>
-      <c r="E16" s="196" t="s">
-        <v>181</v>
-      </c>
-      <c r="F16" s="196" t="s">
-        <v>399</v>
+      <c r="E16" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simple Change?</t>
+        </is>
+      </c>
+      <c r="F16" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simple Change?</t>
+        </is>
       </c>
       <c r="G16" s="187" t="s">
         <v>563</v>
@@ -41475,12 +41555,14 @@
       <c r="H16" s="187" t="s">
         <v>108</v>
       </c>
-      <c r="I16" s="187" t="s">
-        <v>564</v>
+      <c r="I16" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: Select Yes for IT / organisational changes that follow a different process review. The MOC follows the same workflow but without the Evaluation, Design &amp; Analysis checklist.</t>
+        </is>
       </c>
       <c r="J16" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TBC] Remove, or re-caption as 'Simplified MOC?' re-using the OOTB skip path (organisational / IT changes).</t>
+          <t xml:space="preserve">Yes/No. Mandatory. Replaces 'Replacement in Kind'. Same workflow (the OOTB skip-to-Implementation path is REMOVED); checklist questions are not generated when Yes (setup parameter 'Simple Change?' = No).</t>
         </is>
       </c>
       <c r="K16" s="254" t="inlineStr">
@@ -41535,12 +41617,12 @@
       <c r="Z16" s="253"/>
       <c r="AA16" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">ON HOLD: like-for-like is out of MoC scope, but the field/path may become the simplified-MOC switch (decision 21-Oct).</t>
+          <t xml:space="preserve">[SAM Rev2] Replaces Replacement in Kind. [TBC] what the 'different process review' for IT / Org changes requires.</t>
         </is>
       </c>
       <c r="AB16" s="61"/>
     </row>
-    <row r="17" s="59" customFormat="1" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" s="59" customFormat="1" ht="115.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A17" s="188">
         <v>13</v>
       </c>
@@ -41571,7 +41653,11 @@
       <c r="J17" s="187" t="s">
         <v>565</v>
       </c>
-      <c r="K17" s="187"/>
+      <c r="K17" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L17" s="187" t="s">
         <v>14</v>
       </c>
@@ -41617,7 +41703,11 @@
       </c>
       <c r="Y17" s="253"/>
       <c r="Z17" s="253"/>
-      <c r="AA17" s="60"/>
+      <c r="AA17" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Mandatory; Change Expiry triggered when Yes.</t>
+        </is>
+      </c>
       <c r="AB17" s="61"/>
     </row>
     <row r="18" s="59" customFormat="1" ht="86.4" x14ac:dyDescent="0.55000000000000004" customHeight="1">
@@ -41707,7 +41797,7 @@
       <c r="Z18" s="253"/>
       <c r="AA18" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type must be Date (baseline shows 'None').</t>
+          <t xml:space="preserve">[SAM Rev2] triggered by Temporary Change. Type must be Date (baseline: None).</t>
         </is>
       </c>
       <c r="AB18" s="61"/>
@@ -41725,15 +41815,11 @@
       <c r="D19" s="57" t="s">
         <v>578</v>
       </c>
-      <c r="E19" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grade of Change</t>
-        </is>
-      </c>
-      <c r="F19" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grade of Change</t>
-        </is>
+      <c r="E19" s="196" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" s="196" t="s">
+        <v>216</v>
       </c>
       <c r="G19" s="187"/>
       <c r="H19" s="187" t="s">
@@ -41741,12 +41827,12 @@
       </c>
       <c r="I19" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tooltip: Select Minor, Moderate or Major using the descriptors shown for the selected Type of Change. Minor = Local approval (Terminal Manager); Moderate = Regional approval (HSEC + Operations); Major = Global approval (HSEC + Operations).</t>
+          <t xml:space="preserve">Tooltip: Select Minor, Moderate or Major using the guidance shown for the selected Change Type. Minor = Local approval (TM + at least one technical specialist of the terminal); Moderate = Regional (HSEC + Ops); Major = Global (HSEC + Ops).</t>
         </is>
       </c>
       <c r="J19" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lookup: L04 - Grade of Change (Minor / Moderate / Major). Mandatory. Drives auto-generated approvals, tasks and screening questions (Change Impacts parameter of the setups).</t>
+          <t xml:space="preserve">Lookup: L04 - Change Impact (Minor / Moderate / Major). Mandatory. Drives the minimum approval levels and the Change Impacts parameter of the setups.</t>
         </is>
       </c>
       <c r="K19" s="254" t="inlineStr">
@@ -41801,12 +41887,12 @@
       <c r="Z19" s="253"/>
       <c r="AA19" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Replaces Level 1-5 scoring (pending Global HSE sign-off).</t>
+          <t xml:space="preserve">[SAM Rev2] Uses terminology and guidance of the 'Change Impact' tab to drive minimum approval levels.</t>
         </is>
       </c>
       <c r="AB19" s="61"/>
     </row>
-    <row r="20" s="59" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="20" s="59" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A20" s="188">
         <v>16</v>
       </c>
@@ -41832,19 +41918,23 @@
         <v>58</v>
       </c>
       <c r="I20" s="187"/>
-      <c r="J20" s="187" t="s">
-        <v>699</v>
+      <c r="J20" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lookup: L05 - Priority. Mandatory.</t>
+        </is>
       </c>
       <c r="K20" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
+          <t xml:space="preserve">M</t>
         </is>
       </c>
       <c r="L20" s="187" t="s">
         <v>14</v>
       </c>
-      <c r="M20" s="188" t="s">
-        <v>15</v>
+      <c r="M20" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="N20" s="188" t="s">
         <v>15</v>
@@ -41885,12 +41975,12 @@
       <c r="Z20" s="253"/>
       <c r="AA20" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not used: Grade of Change is the single criticality driver (Sam 21-Oct: not sure Priority drives anything).</t>
+          <t xml:space="preserve">[SAM Rev2] KEEP, mandatory selection list. [TBC] values and what priority drives (21-Oct Sam: not sure it drives anything).</t>
         </is>
       </c>
       <c r="AB20" s="61"/>
     </row>
-    <row r="21" s="59" customFormat="1" ht="72.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="21" s="59" customFormat="1" ht="100.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A21" s="188">
         <v>17</v>
       </c>
@@ -41905,12 +41995,12 @@
       </c>
       <c r="E21" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reason for Change &amp; Technical Basis</t>
+          <t xml:space="preserve">Change Justification</t>
         </is>
       </c>
       <c r="F21" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reason for Change &amp; Technical Basis</t>
+          <t xml:space="preserve">Change Justification</t>
         </is>
       </c>
       <c r="G21" s="187" t="s">
@@ -41921,12 +42011,12 @@
       </c>
       <c r="I21" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tooltip: Why the change is needed, technical basis, scope, current situation and what approvers should look out for.</t>
+          <t xml:space="preserve">Tooltip: Explain the reason and technical basis for the change, alternatives and business value, with enough detail for approvers to understand what they are approving.</t>
         </is>
       </c>
       <c r="J21" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text (multi-line, no length limit). Mandatory.</t>
+          <t xml:space="preserve">Text (multi-line). Mandatory.</t>
         </is>
       </c>
       <c r="K21" s="254" t="inlineStr">
@@ -41981,12 +42071,12 @@
       <c r="Z21" s="253"/>
       <c r="AA21" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct (Khesar, agreed by Sam): Priority Explanation re-worded as reason / technical basis - gives approvers context. Covers BRD FR-B3-001.</t>
+          <t xml:space="preserve">[SAM Rev2] 'Priority Explanation' renamed 'Change Justification' with tooltip (Khesar 21-Oct).</t>
         </is>
       </c>
       <c r="AB21" s="61"/>
     </row>
-    <row r="22" s="59" customFormat="1" ht="100.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="22" s="59" customFormat="1" ht="72.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A22" s="188">
         <v>18</v>
       </c>
@@ -42001,12 +42091,12 @@
       </c>
       <c r="E22" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of Change</t>
+          <t xml:space="preserve">Change Type</t>
         </is>
       </c>
       <c r="F22" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of Change</t>
+          <t xml:space="preserve">Change Type</t>
         </is>
       </c>
       <c r="G22" s="187"/>
@@ -42015,12 +42105,12 @@
       </c>
       <c r="I22" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tooltip: Select the type of change. The grade descriptors for the selected type are displayed below.</t>
+          <t xml:space="preserve">Tooltip: Select the type of change. The Change Impact guidance for the selected type is displayed below.</t>
         </is>
       </c>
       <c r="J22" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">M:1 relation to MOC Category object (caption 'Type of Change'). Mandatory. Values: Lookup Values L08. If several types apply select the one with the highest grade [TBC].</t>
+          <t xml:space="preserve">M:1 relation to MOC Category object (caption 'Change Type'). Mandatory. Values: Lookup L08. Placed ABOVE Change Impact.</t>
         </is>
       </c>
       <c r="K22" s="254" t="inlineStr">
@@ -42075,12 +42165,12 @@
       <c r="Z22" s="253"/>
       <c r="AA22" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOC Category used as Type of Change (8 types) - also filters setups.</t>
+          <t xml:space="preserve">[SAM Rev2] Replaces 'Category', moved above Change Impact.</t>
         </is>
       </c>
       <c r="AB22" s="61"/>
     </row>
-    <row r="23" s="59" customFormat="1" ht="72" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" s="59" customFormat="1" ht="72.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A23" s="188">
         <v>19</v>
       </c>
@@ -42111,7 +42201,11 @@
       <c r="J23" s="187" t="s">
         <v>590</v>
       </c>
-      <c r="K23" s="187"/>
+      <c r="K23" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L23" s="187" t="s">
         <v>14</v>
       </c>
@@ -42157,7 +42251,11 @@
       </c>
       <c r="Y23" s="253"/>
       <c r="Z23" s="253"/>
-      <c r="AA23" s="60"/>
+      <c r="AA23" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Mandatory, date entry.</t>
+        </is>
+      </c>
       <c r="AB23" s="61"/>
     </row>
     <row r="24" s="59" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
@@ -42236,24 +42334,32 @@
       <c r="AA24" s="60"/>
       <c r="AB24" s="61"/>
     </row>
-    <row r="25" s="59" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="25" s="59" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A25" s="188">
         <v>21</v>
       </c>
-      <c r="B25" s="187" t="s">
-        <v>199</v>
+      <c r="B25" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approval</t>
+        </is>
       </c>
       <c r="C25" s="57" t="s">
         <v>251</v>
       </c>
-      <c r="D25" s="187" t="s">
-        <v>582</v>
-      </c>
-      <c r="E25" s="195" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" s="195" t="s">
-        <v>47</v>
+      <c r="D25" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approval Details</t>
+        </is>
+      </c>
+      <c r="E25" s="258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approval Notes</t>
+        </is>
+      </c>
+      <c r="F25" s="258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approval Notes</t>
+        </is>
       </c>
       <c r="G25" s="187" t="s">
         <v>583</v>
@@ -42262,10 +42368,14 @@
         <v>51</v>
       </c>
       <c r="I25" s="187"/>
-      <c r="J25" s="189"/>
-      <c r="K25" s="258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R</t>
+      <c r="J25" s="259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text. Feedback from approvers.</t>
+        </is>
+      </c>
+      <c r="K25" s="259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
         </is>
       </c>
       <c r="L25" s="189" t="s">
@@ -42288,8 +42398,10 @@
       <c r="Q25" s="188" t="s">
         <v>15</v>
       </c>
-      <c r="R25" s="188" t="s">
-        <v>14</v>
+      <c r="R25" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
       </c>
       <c r="S25" s="188" t="s">
         <v>15</v>
@@ -42313,7 +42425,7 @@
       <c r="Z25" s="253"/>
       <c r="AA25" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pre-Approval stage removed.</t>
+          <t xml:space="preserve">[SAM Rev2] 'Pre-Approval Detail' renamed 'Approval Notes'.</t>
         </is>
       </c>
     </row>
@@ -42346,7 +42458,7 @@
         <v>592</v>
       </c>
       <c r="J26" s="189"/>
-      <c r="K26" s="258" t="inlineStr">
+      <c r="K26" s="259" t="inlineStr">
         <is>
           <t xml:space="preserve">R</t>
         </is>
@@ -42396,18 +42508,16 @@
       <c r="Z26" s="253"/>
       <c r="AA26" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONFIRMED 21-Oct (Shaun: 'it's the point of the approval'). Approvals controlled in the Approval stage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" s="59" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+          <t xml:space="preserve">[SAM Rev2] 'Evaluation Details' removed (Shaun 21-Oct: approvals are the point of the Approval stage).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" s="59" customFormat="1" ht="14.4" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A27" s="188">
         <v>23</v>
       </c>
-      <c r="B27" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
-        </is>
+      <c r="B27" s="57" t="s">
+        <v>200</v>
       </c>
       <c r="C27" s="57" t="s">
         <v>251</v>
@@ -42415,15 +42525,11 @@
       <c r="D27" s="195" t="s">
         <v>589</v>
       </c>
-      <c r="E27" s="259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evaluation, Design &amp; Analysis Notes</t>
-        </is>
-      </c>
-      <c r="F27" s="259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evaluation, Design &amp; Analysis Notes</t>
-        </is>
+      <c r="E27" s="195" t="s">
+        <v>225</v>
+      </c>
+      <c r="F27" s="195" t="s">
+        <v>225</v>
       </c>
       <c r="G27" s="187" t="s">
         <v>593</v>
@@ -42433,9 +42539,9 @@
       </c>
       <c r="I27" s="187"/>
       <c r="J27" s="189"/>
-      <c r="K27" s="258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M</t>
+      <c r="K27" s="259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R</t>
         </is>
       </c>
       <c r="L27" s="189" t="s">
@@ -42483,7 +42589,7 @@
       <c r="Z27" s="253"/>
       <c r="AA27" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merged notes for the combined stage.</t>
+          <t xml:space="preserve">[SAM Rev2] 'Evaluation Details' removed.</t>
         </is>
       </c>
     </row>
@@ -42517,7 +42623,11 @@
       <c r="I28" s="187" t="s">
         <v>596</v>
       </c>
-      <c r="J28" s="187"/>
+      <c r="J28" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text. Mandatory.</t>
+        </is>
+      </c>
       <c r="K28" s="254" t="inlineStr">
         <is>
           <t xml:space="preserve">M</t>
@@ -42532,8 +42642,10 @@
       <c r="N28" s="188" t="s">
         <v>15</v>
       </c>
-      <c r="O28" s="188" t="s">
-        <v>15</v>
+      <c r="O28" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="P28" s="188" t="s">
         <v>15</v>
@@ -42570,7 +42682,7 @@
       <c r="Z28" s="253"/>
       <c r="AA28" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moved to combined stage. 21-Oct: keep 'Alternatives Considered' (important).</t>
+          <t xml:space="preserve">[SAM Rev2] Mandatory free form.</t>
         </is>
       </c>
     </row>
@@ -42604,7 +42716,11 @@
       <c r="I29" s="187" t="s">
         <v>598</v>
       </c>
-      <c r="J29" s="187"/>
+      <c r="J29" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No. Mandatory. Triggers 'Impact/Hazards Assessment Details' (new field).</t>
+        </is>
+      </c>
       <c r="K29" s="254" t="inlineStr">
         <is>
           <t xml:space="preserve">M</t>
@@ -42619,8 +42735,10 @@
       <c r="N29" s="188" t="s">
         <v>15</v>
       </c>
-      <c r="O29" s="188" t="s">
-        <v>15</v>
+      <c r="O29" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="P29" s="188" t="s">
         <v>15</v>
@@ -42657,7 +42775,7 @@
       <c r="Z29" s="253"/>
       <c r="AA29" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moved to combined stage.</t>
+          <t xml:space="preserve">[SAM Rev2] Mandatory; Yes = state assessment type completed and attached; No = justify.</t>
         </is>
       </c>
     </row>
@@ -42691,7 +42809,11 @@
       <c r="I30" s="187" t="s">
         <v>600</v>
       </c>
-      <c r="J30" s="197"/>
+      <c r="J30" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No. Mandatory. If No: justification (new field).</t>
+        </is>
+      </c>
       <c r="K30" s="261" t="inlineStr">
         <is>
           <t xml:space="preserve">M</t>
@@ -42706,8 +42828,10 @@
       <c r="N30" s="188" t="s">
         <v>15</v>
       </c>
-      <c r="O30" s="188" t="s">
-        <v>15</v>
+      <c r="O30" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="P30" s="188" t="s">
         <v>15</v>
@@ -42744,7 +42868,7 @@
       <c r="Z30" s="253"/>
       <c r="AA30" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moved to combined stage.</t>
+          <t xml:space="preserve">[SAM Rev2] Mandatory; if No justify.</t>
         </is>
       </c>
     </row>
@@ -42778,7 +42902,11 @@
       <c r="I31" s="187" t="s">
         <v>601</v>
       </c>
-      <c r="J31" s="197"/>
+      <c r="J31" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No. Mandatory. If No: justification (new field).</t>
+        </is>
+      </c>
       <c r="K31" s="261" t="inlineStr">
         <is>
           <t xml:space="preserve">M</t>
@@ -42793,8 +42921,10 @@
       <c r="N31" s="188" t="s">
         <v>15</v>
       </c>
-      <c r="O31" s="188" t="s">
-        <v>15</v>
+      <c r="O31" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="P31" s="188" t="s">
         <v>15</v>
@@ -42831,7 +42961,7 @@
       <c r="Z31" s="253"/>
       <c r="AA31" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moved to combined stage. 21-Oct (Sam): design documentation should be attached to the MOC here.</t>
+          <t xml:space="preserve">[SAM Rev2] Mandatory; if No justify.</t>
         </is>
       </c>
     </row>
@@ -42839,8 +42969,10 @@
       <c r="A32" s="188">
         <v>28</v>
       </c>
-      <c r="B32" s="197" t="s">
-        <v>201</v>
+      <c r="B32" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
+        </is>
       </c>
       <c r="C32" s="57" t="s">
         <v>251</v>
@@ -42863,10 +42995,14 @@
       <c r="I32" s="187" t="s">
         <v>601</v>
       </c>
-      <c r="J32" s="197"/>
+      <c r="J32" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text. Optional.</t>
+        </is>
+      </c>
       <c r="K32" s="261" t="inlineStr">
         <is>
-          <t xml:space="preserve">R</t>
+          <t xml:space="preserve">M</t>
         </is>
       </c>
       <c r="L32" s="189" t="s">
@@ -42916,11 +43052,11 @@
       <c r="Z32" s="253"/>
       <c r="AA32" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merged into Evaluation, Design &amp; Analysis Notes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+          <t xml:space="preserve">[SAM Rev2] Keep, optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="201.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A33" s="188">
         <v>29</v>
       </c>
@@ -42948,8 +43084,16 @@
       <c r="I33" s="187" t="s">
         <v>605</v>
       </c>
-      <c r="J33" s="197"/>
-      <c r="K33" s="177"/>
+      <c r="J33" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No. Mandatory [TBC: Moderate/Major only]. If No: justification (new field).</t>
+        </is>
+      </c>
+      <c r="K33" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L33" s="189" t="s">
         <v>14</v>
       </c>
@@ -42973,8 +43117,10 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S33" s="188" t="s">
-        <v>15</v>
+      <c r="S33" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="T33" s="188" t="s">
         <v>15</v>
@@ -42995,8 +43141,13 @@
       </c>
       <c r="Y33" s="253"/>
       <c r="Z33" s="253"/>
-    </row>
-    <row r="34" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA33" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] 'Mandated for Moderate/Major only?' - open question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="201.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A34" s="188">
         <v>30</v>
       </c>
@@ -43024,8 +43175,16 @@
       <c r="I34" s="187" t="s">
         <v>607</v>
       </c>
-      <c r="J34" s="197"/>
-      <c r="K34" s="177"/>
+      <c r="J34" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No. Mandatory. Triggers 'Training Details / Justification' (new field).</t>
+        </is>
+      </c>
+      <c r="K34" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L34" s="189" t="s">
         <v>14</v>
       </c>
@@ -43049,8 +43208,10 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S34" s="188" t="s">
-        <v>15</v>
+      <c r="S34" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="T34" s="188" t="s">
         <v>15</v>
@@ -43071,8 +43232,13 @@
       </c>
       <c r="Y34" s="253"/>
       <c r="Z34" s="253"/>
-    </row>
-    <row r="35" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA34" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Yes = detail training provided; No = justify why not required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="172.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A35" s="188">
         <v>31</v>
       </c>
@@ -43100,8 +43266,16 @@
       <c r="I35" s="187" t="s">
         <v>608</v>
       </c>
-      <c r="J35" s="197"/>
-      <c r="K35" s="177"/>
+      <c r="J35" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No. Mandatory. Triggers 'Communication Details / Justification' (new field).</t>
+        </is>
+      </c>
+      <c r="K35" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L35" s="189" t="s">
         <v>14</v>
       </c>
@@ -43125,8 +43299,10 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S35" s="188" t="s">
-        <v>15</v>
+      <c r="S35" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="T35" s="188" t="s">
         <v>15</v>
@@ -43147,6 +43323,11 @@
       </c>
       <c r="Y35" s="253"/>
       <c r="Z35" s="253"/>
+      <c r="AA35" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Yes = date of comms and to whom; No = justify.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="187.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A36" s="188">
@@ -43176,8 +43357,16 @@
       <c r="I36" s="187" t="s">
         <v>609</v>
       </c>
-      <c r="J36" s="197"/>
-      <c r="K36" s="177"/>
+      <c r="J36" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No. Mandatory.</t>
+        </is>
+      </c>
+      <c r="K36" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L36" s="189" t="s">
         <v>14</v>
       </c>
@@ -43201,8 +43390,10 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S36" s="188" t="s">
-        <v>15</v>
+      <c r="S36" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="T36" s="188" t="s">
         <v>15</v>
@@ -43225,7 +43416,7 @@
       <c r="Z36" s="253"/>
       <c r="AA36" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct (Sam): not sure we need both 'Installation Complete?' and 'Installation Confirmed?' - keep one [TBC].</t>
+          <t xml:space="preserve">[SAM Rev2] Mandatory.</t>
         </is>
       </c>
     </row>
@@ -43258,7 +43449,11 @@
         <v>610</v>
       </c>
       <c r="J37" s="197"/>
-      <c r="K37" s="177"/>
+      <c r="K37" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R</t>
+        </is>
+      </c>
       <c r="L37" s="189" t="s">
         <v>14</v>
       </c>
@@ -43306,11 +43501,11 @@
       <c r="Z37" s="253"/>
       <c r="AA37" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">[TBC] candidate for removal (see row above).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+          <t xml:space="preserve">[SAM Rev2] 'Installation Confirmed' removed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="187.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A38" s="188">
         <v>34</v>
       </c>
@@ -43338,8 +43533,16 @@
       <c r="I38" s="187" t="s">
         <v>611</v>
       </c>
-      <c r="J38" s="197"/>
-      <c r="K38" s="177"/>
+      <c r="J38" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No. Mandatory. If No: justification (new field).</t>
+        </is>
+      </c>
+      <c r="K38" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L38" s="189" t="s">
         <v>14</v>
       </c>
@@ -43363,8 +43566,10 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S38" s="188" t="s">
-        <v>15</v>
+      <c r="S38" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="T38" s="188" t="s">
         <v>15</v>
@@ -43385,8 +43590,13 @@
       </c>
       <c r="Y38" s="253"/>
       <c r="Z38" s="253"/>
-    </row>
-    <row r="39" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA38" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Mandatory; if No justify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="129.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A39" s="188">
         <v>35</v>
       </c>
@@ -43414,8 +43624,16 @@
       <c r="I39" s="187" t="s">
         <v>601</v>
       </c>
-      <c r="J39" s="197"/>
-      <c r="K39" s="177"/>
+      <c r="J39" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text. Optional.</t>
+        </is>
+      </c>
+      <c r="K39" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L39" s="189" t="s">
         <v>14</v>
       </c>
@@ -43461,8 +43679,13 @@
       </c>
       <c r="Y39" s="253"/>
       <c r="Z39" s="253"/>
-    </row>
-    <row r="40" ht="172.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA39" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Keep, optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="172.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A40" s="188">
         <v>36</v>
       </c>
@@ -43490,8 +43713,16 @@
       <c r="I40" s="187" t="s">
         <v>616</v>
       </c>
-      <c r="J40" s="197"/>
-      <c r="K40" s="177"/>
+      <c r="J40" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No. Mandatory.</t>
+        </is>
+      </c>
+      <c r="K40" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L40" s="189" t="s">
         <v>14</v>
       </c>
@@ -43521,8 +43752,10 @@
       <c r="T40" s="188" t="s">
         <v>15</v>
       </c>
-      <c r="U40" s="188" t="s">
-        <v>15</v>
+      <c r="U40" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="V40" s="188" t="s">
         <v>15</v>
@@ -43537,6 +43770,11 @@
       </c>
       <c r="Y40" s="253"/>
       <c r="Z40" s="253"/>
+      <c r="AA40" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Mandatory.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="187.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A41" s="188">
@@ -43551,15 +43789,11 @@
       <c r="D41" s="201" t="s">
         <v>614</v>
       </c>
-      <c r="E41" s="263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Start-Up Confirmed?</t>
-        </is>
-      </c>
-      <c r="F41" s="264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Start-Up Confirmed?</t>
-        </is>
+      <c r="E41" s="198" t="s">
+        <v>240</v>
+      </c>
+      <c r="F41" s="199" t="s">
+        <v>540</v>
       </c>
       <c r="G41" s="197" t="s">
         <v>617</v>
@@ -43573,7 +43807,7 @@
       <c r="J41" s="197"/>
       <c r="K41" s="261" t="inlineStr">
         <is>
-          <t xml:space="preserve">M</t>
+          <t xml:space="preserve">R</t>
         </is>
       </c>
       <c r="L41" s="189" t="s">
@@ -43623,11 +43857,11 @@
       <c r="Z41" s="253"/>
       <c r="AA41" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typo fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+          <t xml:space="preserve">[SAM Rev2] 'Start Up Confirmed' removed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="57.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A42" s="188">
         <v>38</v>
       </c>
@@ -43652,9 +43886,21 @@
       <c r="H42" s="200" t="s">
         <v>51</v>
       </c>
-      <c r="I42" s="201"/>
-      <c r="J42" s="197"/>
-      <c r="K42" s="177"/>
+      <c r="I42" s="262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: Provide feedback on start up, any issues encountered and improvements necessary.</t>
+        </is>
+      </c>
+      <c r="J42" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text. Optional.</t>
+        </is>
+      </c>
+      <c r="K42" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L42" s="189" t="s">
         <v>14</v>
       </c>
@@ -43700,8 +43946,13 @@
       </c>
       <c r="Y42" s="253"/>
       <c r="Z42" s="253"/>
-    </row>
-    <row r="43" ht="201.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA42" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Keep, optional, tooltip added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="201.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A43" s="188">
         <v>39</v>
       </c>
@@ -43729,8 +43980,16 @@
       <c r="I43" s="187" t="s">
         <v>623</v>
       </c>
-      <c r="J43" s="197"/>
-      <c r="K43" s="177"/>
+      <c r="J43" s="260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No. Visible and mandatory only if Temporary Change = Yes.</t>
+        </is>
+      </c>
+      <c r="K43" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L43" s="189" t="s">
         <v>14</v>
       </c>
@@ -43766,16 +44025,23 @@
       <c r="V43" s="188" t="s">
         <v>15</v>
       </c>
-      <c r="W43" s="188" t="s">
-        <v>15</v>
+      <c r="W43" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
       </c>
       <c r="X43" s="188" t="s">
         <v>15</v>
       </c>
       <c r="Y43" s="253"/>
       <c r="Z43" s="253"/>
-    </row>
-    <row r="44" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AA43" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Only for temporary changes, mandatory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="129.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A44" s="188">
         <v>40</v>
       </c>
@@ -43848,8 +44114,13 @@
       </c>
       <c r="Y44" s="253"/>
       <c r="Z44" s="253"/>
-    </row>
-    <row r="45" ht="86.4" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+      <c r="AA44" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Selection list Yes/No (keep).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="72.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A45" s="188">
         <v>41</v>
       </c>
@@ -43867,10 +44138,8 @@
           <t xml:space="preserve">Were MOC Procedures Followed?</t>
         </is>
       </c>
-      <c r="F45" s="264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Were MOC Procedures Followed?</t>
-        </is>
+      <c r="F45" s="199" t="s">
+        <v>462</v>
       </c>
       <c r="G45" s="201" t="s">
         <v>624</v>
@@ -43878,8 +44147,10 @@
       <c r="H45" s="200" t="s">
         <v>108</v>
       </c>
-      <c r="I45" s="187" t="s">
-        <v>625</v>
+      <c r="I45" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: Confirm the MOC process was followed and all necessary approvals and documentation were provided.</t>
+        </is>
       </c>
       <c r="J45" s="197"/>
       <c r="K45" s="261" t="inlineStr">
@@ -43932,7 +44203,7 @@
       <c r="Z45" s="253"/>
       <c r="AA45" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typo fix.</t>
+          <t xml:space="preserve">[SAM Rev2] Tooltip added (typo fixed).</t>
         </is>
       </c>
     </row>
@@ -43954,10 +44225,8 @@
           <t xml:space="preserve">MOC Process Effectiveness &amp; Feedback</t>
         </is>
       </c>
-      <c r="F46" s="264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC Process Effectiveness &amp; Feedback</t>
-        </is>
+      <c r="F46" s="199" t="s">
+        <v>536</v>
       </c>
       <c r="G46" s="201" t="s">
         <v>626</v>
@@ -44019,7 +44288,7 @@
       <c r="Z46" s="253"/>
       <c r="AA46" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typo fix.</t>
+          <t xml:space="preserve">[SAM Rev2] Free form (typo fixed).</t>
         </is>
       </c>
     </row>
@@ -44036,11 +44305,15 @@
       <c r="D47" s="201" t="s">
         <v>620</v>
       </c>
-      <c r="E47" s="198" t="s">
-        <v>246</v>
-      </c>
-      <c r="F47" s="199" t="s">
-        <v>246</v>
+      <c r="E47" s="263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lessons Learnt</t>
+        </is>
+      </c>
+      <c r="F47" s="264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lessons Learnt</t>
+        </is>
       </c>
       <c r="G47" s="197" t="s">
         <v>628</v>
@@ -44050,7 +44323,11 @@
       </c>
       <c r="I47" s="201"/>
       <c r="J47" s="197"/>
-      <c r="K47" s="177"/>
+      <c r="K47" s="261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L47" s="189" t="s">
         <v>14</v>
       </c>
@@ -44096,7 +44373,7 @@
       <c r="Z47" s="253"/>
       <c r="AA47" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct (Sam): add questions from the MOC audit form to Follow Up (list from Sam) [TBC].</t>
+          <t xml:space="preserve">[SAM Rev2] 'Follow Up Notes' renamed 'Lessons Learnt'. [21-Oct] audit-form questions to be added [TBC].</t>
         </is>
       </c>
     </row>
@@ -44106,9 +44383,8 @@
       </c>
       <c r="B48" s="260" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Evaluation, Design &amp; Analysis
-• Start Up
-• Follow Up</t>
+          <t xml:space="preserve">• Evaluation, Design &amp; Analysis (answer)
+• Approval / Implementation / Start Up / Follow Up (view only)</t>
         </is>
       </c>
       <c r="C48" s="57" t="s">
@@ -44183,7 +44459,7 @@
       <c r="Z48" s="253"/>
       <c r="AA48" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Checklist answered mainly in Evaluation, Design &amp; Analysis.</t>
+          <t xml:space="preserve">[SAM Rev2] Checklist answered in Evaluation, D&amp;A; later stages show previous checklist items read-only.</t>
         </is>
       </c>
     </row>
@@ -44266,7 +44542,7 @@
       <c r="Z49" s="253"/>
       <c r="AA49" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Duplicate of previous row.</t>
+          <t xml:space="preserve">[BA] Duplicate of previous row.</t>
         </is>
       </c>
     </row>
@@ -44353,7 +44629,7 @@
       <c r="Z50" s="253"/>
       <c r="AA50" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stages updated.</t>
+          <t xml:space="preserve">[SAM Rev2] Keep OOTB + 'Required Pre-Implementation / Pre-Follow Up' on each task.</t>
         </is>
       </c>
     </row>
@@ -44363,8 +44639,8 @@
       </c>
       <c r="B51" s="260" t="inlineStr">
         <is>
-          <t xml:space="preserve">• Approval (auto-generated)
-• Any stage (ad hoc)</t>
+          <t xml:space="preserve">• Approval (mandated, sequential)
+• All other stages (ad hoc)</t>
         </is>
       </c>
       <c r="C51" s="57" t="s">
@@ -44437,7 +44713,7 @@
       <c r="Z51" s="253"/>
       <c r="AA51" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approvals generated in the Approval stage.</t>
+          <t xml:space="preserve">[SAM Rev2] Mandated approvals in Approval stage; ad hoc allowed in every stage. [TBC] TM re-approval at Implementation / Start Up / Follow Up?</t>
         </is>
       </c>
     </row>
@@ -44514,11 +44790,11 @@
       <c r="Z52" s="253"/>
       <c r="AA52" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEP - 21-Oct (Shaun, Hugo): traceability, e.g. phased tank works (roof removal, new roof, return to service).</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" x14ac:dyDescent="0.55000000000000004" ht="86.4" customHeight="1">
+          <t xml:space="preserve">[SAM Rev2] Keep (21-Oct: traceability).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" x14ac:dyDescent="0.55000000000000004" ht="72.0" customHeight="1">
       <c r="A53" s="188">
         <v>49</v>
       </c>
@@ -44543,7 +44819,7 @@
       </c>
       <c r="I53" s="262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instruction text: attach all supporting documents - risk assessment / JSA, method statement, procedures, P&amp;IDs, design documents, SDS, permits and licences.</t>
+          <t xml:space="preserve">Instruction text: Please add all related procedures, method statements, risk assessments, design drawings and calculations</t>
         </is>
       </c>
       <c r="J53" s="201" t="s">
@@ -44597,7 +44873,7 @@
       <c r="Z53" s="253"/>
       <c r="AA53" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct (Khesar): explain under Attachments which documents are expected. Manual MOC form retired.</t>
+          <t xml:space="preserve">[SAM Rev2] Description added under Document Attachments (every stage).</t>
         </is>
       </c>
     </row>
@@ -44946,7 +45222,7 @@
         <v>108</v>
       </c>
       <c r="G64" s="182"/>
-      <c r="H64" s="265" t="inlineStr">
+      <c r="H64" s="267" t="inlineStr">
         <is>
           <t xml:space="preserve">Lookup</t>
         </is>
@@ -44957,7 +45233,7 @@
           <t xml:space="preserve">Values: Yes / No / N/A [TBC]</t>
         </is>
       </c>
-      <c r="K64" s="266" t="inlineStr">
+      <c r="K64" s="268" t="inlineStr">
         <is>
           <t xml:space="preserve">M</t>
         </is>
@@ -44970,7 +45246,7 @@
       </c>
       <c r="AA64" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Checklist answers usually need N/A.</t>
+          <t xml:space="preserve">[BRD] FR-B3-039 - checklist answers usually need N/A.</t>
         </is>
       </c>
     </row>
@@ -49466,7 +49742,7 @@
       <c r="K168" s="59"/>
       <c r="AA168" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct: Keep (functional approval). Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
+          <t xml:space="preserve">[21-Oct] Keep (functional approval). Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -50264,7 +50540,7 @@
       <c r="K186" s="59"/>
       <c r="AA186" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct: Keep (functional approval). Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
+          <t xml:space="preserve">[21-Oct] Keep (functional approval). Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -51062,7 +51338,7 @@
       <c r="K204" s="59"/>
       <c r="AA204" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct: [TBC] re-use for a missing type - Intelex to propose. Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
+          <t xml:space="preserve">[21-Oct] [TBC] re-use for a missing type - Intelex to propose. Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -51860,7 +52136,7 @@
       <c r="K222" s="59"/>
       <c r="AA222" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct: [TBC] re-use for a missing type - Intelex to propose. Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
+          <t xml:space="preserve">[21-Oct] [TBC] re-use for a missing type - Intelex to propose. Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -52658,7 +52934,7 @@
       <c r="K240" s="59"/>
       <c r="AA240" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct: Keep (functional approval). Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
+          <t xml:space="preserve">[21-Oct] Keep (functional approval). Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -53456,7 +53732,7 @@
       <c r="K258" s="59"/>
       <c r="AA258" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-Oct: [TBC] re-use for a missing type - Intelex to propose. Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
+          <t xml:space="preserve">[21-Oct] [TBC] re-use for a missing type - Intelex to propose. Missing: Operations, Maintenance + level approvals (TM / Regional / Global).</t>
         </is>
       </c>
     </row>
@@ -54537,7 +54813,7 @@
       </c>
       <c r="AA285" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOC Categories = Type of Change.</t>
+          <t xml:space="preserve">[SAM Rev2] MOC Categories = Change Type.</t>
         </is>
       </c>
     </row>
@@ -54616,7 +54892,7 @@
       </c>
       <c r="AA287" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">L04 = Grade of Change (Minor/Moderate/Major).</t>
+          <t xml:space="preserve">[SAM Rev2] L04 = Change Impact (Minor/Moderate/Major).</t>
         </is>
       </c>
     </row>
@@ -54657,7 +54933,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="289" ht="216" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" ht="216.0" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A289" s="179">
         <v>9</v>
       </c>
@@ -54670,11 +54946,15 @@
       <c r="D289" s="181" t="s">
         <v>267</v>
       </c>
-      <c r="E289" s="182" t="s">
-        <v>399</v>
-      </c>
-      <c r="F289" s="182" t="s">
-        <v>399</v>
+      <c r="E289" s="265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simple Change?</t>
+        </is>
+      </c>
+      <c r="F289" s="265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simple Change?</t>
+        </is>
       </c>
       <c r="G289" s="187" t="s">
         <v>740</v>
@@ -54686,12 +54966,21 @@
         <v>741</v>
       </c>
       <c r="J289" s="187"/>
-      <c r="K289" s="178"/>
+      <c r="K289" s="266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L289" s="179" t="s">
         <v>15</v>
       </c>
       <c r="M289" s="179" t="s">
         <v>15</v>
+      </c>
+      <c r="AA289" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Set to 'No' on all checklist questions so they are not generated for Simple Changes.</t>
+        </is>
       </c>
     </row>
     <row r="290" ht="201.6" x14ac:dyDescent="0.55000000000000004">
@@ -54805,7 +55094,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="293" ht="28.8" x14ac:dyDescent="0.55000000000000004" customHeight="1">
+    <row r="293" ht="43.2" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A293" s="179">
         <v>13</v>
       </c>
@@ -54843,7 +55132,7 @@
       </c>
       <c r="AA293" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Part 1 (Universal) at top location; Part 2 at Liquids segment; Part 3 at Dry segment.</t>
+          <t xml:space="preserve">[SAM Rev2] Part 1 (Universal) at top location; Part 2 Liquids; Part 3 Dry. [TBC] link items to Change Type / Impact (e.g. HAZOP mandatory for Major equipment change).</t>
         </is>
       </c>
     </row>
@@ -55163,10 +55452,10 @@
       </c>
       <c r="J303" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">L04 - Grade of Change</t>
-        </is>
-      </c>
-      <c r="K303" s="267" t="inlineStr">
+          <t xml:space="preserve">L04 - Change Impact</t>
+        </is>
+      </c>
+      <c r="K303" s="266" t="inlineStr">
         <is>
           <t xml:space="preserve">M</t>
         </is>
@@ -55179,7 +55468,7 @@
       </c>
       <c r="AA303" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Use the same list as MOC and Screening setup (baseline used L05).</t>
+          <t xml:space="preserve">[BA] Use the same list as MOC and Screening setup (baseline used L05).</t>
         </is>
       </c>
     </row>
@@ -55220,7 +55509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="305" ht="172.8" x14ac:dyDescent="0.75">
+    <row r="305" ht="201.6" x14ac:dyDescent="0.75" customHeight="1">
       <c r="A305" s="179">
         <v>9</v>
       </c>
@@ -55233,11 +55522,15 @@
       <c r="D305" s="182" t="s">
         <v>268</v>
       </c>
-      <c r="E305" s="182" t="s">
-        <v>399</v>
-      </c>
-      <c r="F305" s="182" t="s">
-        <v>399</v>
+      <c r="E305" s="265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simple Change?</t>
+        </is>
+      </c>
+      <c r="F305" s="265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simple Change?</t>
+        </is>
       </c>
       <c r="G305" s="187" t="s">
         <v>761</v>
@@ -55249,12 +55542,21 @@
         <v>760</v>
       </c>
       <c r="J305" s="187"/>
-      <c r="K305" s="178"/>
+      <c r="K305" s="266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L305" s="211" t="s">
         <v>15</v>
       </c>
       <c r="M305" s="211" t="s">
         <v>15</v>
+      </c>
+      <c r="AA305" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Replacement in Kind re-captioned.</t>
+        </is>
       </c>
     </row>
     <row r="306" ht="172.8" x14ac:dyDescent="0.75">
@@ -55747,10 +56049,10 @@
       </c>
       <c r="J320" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">L04 - Grade of Change</t>
-        </is>
-      </c>
-      <c r="K320" s="267" t="inlineStr">
+          <t xml:space="preserve">L04 - Change Impact</t>
+        </is>
+      </c>
+      <c r="K320" s="266" t="inlineStr">
         <is>
           <t xml:space="preserve">M</t>
         </is>
@@ -55763,7 +56065,7 @@
       </c>
       <c r="AA320" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Use the same list as MOC and Screening setup (baseline used L05).</t>
+          <t xml:space="preserve">[BA] Use the same list as MOC and Screening setup (baseline used L05).</t>
         </is>
       </c>
     </row>
@@ -55802,7 +56104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="322" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="322" ht="201.6" x14ac:dyDescent="0.55000000000000004" customHeight="1">
       <c r="A322" s="179">
         <v>9</v>
       </c>
@@ -55815,11 +56117,15 @@
       <c r="D322" s="181" t="s">
         <v>269</v>
       </c>
-      <c r="E322" s="182" t="s">
-        <v>399</v>
-      </c>
-      <c r="F322" s="182" t="s">
-        <v>399</v>
+      <c r="E322" s="265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simple Change?</t>
+        </is>
+      </c>
+      <c r="F322" s="265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Simple Change?</t>
+        </is>
       </c>
       <c r="G322" s="187"/>
       <c r="H322" s="183" t="s">
@@ -55829,12 +56135,21 @@
         <v>774</v>
       </c>
       <c r="J322" s="187"/>
-      <c r="K322" s="178"/>
+      <c r="K322" s="266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
       <c r="L322" s="211" t="s">
         <v>15</v>
       </c>
       <c r="M322" s="211" t="s">
         <v>15</v>
+      </c>
+      <c r="AA322" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] Replacement in Kind re-captioned.</t>
+        </is>
       </c>
     </row>
     <row r="323" ht="187.2" x14ac:dyDescent="0.55000000000000004">
@@ -56024,7 +56339,7 @@
     <row r="331">
       <c r="A331" s="190" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOC - Impala additional fields (A)</t>
+          <t xml:space="preserve">MOC - Impala additional fields (A). Source tag in 'Impala Notes': [SAM Rev2] = Sam's proposal (prevails); [21-Oct] = internal session; [BRD] = BO-61; [BA] = BA proposal to validate.</t>
         </is>
       </c>
     </row>
@@ -56155,13 +56470,13 @@
         </is>
       </c>
     </row>
-    <row r="333" ht="86.4" customHeight="1">
+    <row r="333" ht="72.0" customHeight="1">
       <c r="A333" s="253">
         <v>1</v>
       </c>
       <c r="B333" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation</t>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
         </is>
       </c>
       <c r="C333" s="255" t="inlineStr">
@@ -56171,33 +56486,33 @@
       </c>
       <c r="D333" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation Information Details</t>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis Details</t>
         </is>
       </c>
       <c r="E333" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grade Guidance - &lt;Type of Change&gt;</t>
+          <t xml:space="preserve">Impact/Hazards Assessment Details</t>
         </is>
       </c>
       <c r="F333" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grade Guidance - &lt;Type of Change&gt;</t>
+          <t xml:space="preserve">Impact/Hazards Assessment Details</t>
         </is>
       </c>
       <c r="G333" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read-only guidance with the Minor / Moderate / Major descriptors of the selected Type of Change.</t>
+          <t xml:space="preserve">Type of assessment completed and attached, or justification if not done.</t>
         </is>
       </c>
       <c r="H333" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text (read-only)</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="I333" s="254"/>
       <c r="J333" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 read-only text fields (one per Type of Change), each visible only when Type of Change = that type (hide/show). Content: Lookup Values L09.</t>
+          <t xml:space="preserve">Visible and mandatory once 'Impact/Hazards Assessment Complete?' is answered (Yes: type of assessment; No: justification).</t>
         </is>
       </c>
       <c r="K333" s="256" t="inlineStr">
@@ -56210,7 +56525,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M333" s="268" t="inlineStr">
+      <c r="M333" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -56220,69 +56535,69 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O333" s="268" t="inlineStr">
+      <c r="O333" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P333" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P333" s="268" t="inlineStr">
+      <c r="Q333" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R333" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="Q333" s="253" t="inlineStr">
+      <c r="S333" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R333" s="253" t="inlineStr">
+      <c r="T333" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S333" s="253" t="inlineStr">
+      <c r="U333" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T333" s="253" t="inlineStr">
+      <c r="V333" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="U333" s="253" t="inlineStr">
+      <c r="W333" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="V333" s="253" t="inlineStr">
+      <c r="X333" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="W333" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X333" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="AA333" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alonso: show only the descriptors of the selected type.</t>
-        </is>
-      </c>
-    </row>
-    <row r="334" ht="100.8" customHeight="1">
+          <t xml:space="preserve">[SAM Rev2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="43.2" customHeight="1">
       <c r="A334" s="253">
         <v>2</v>
       </c>
       <c r="B334" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation</t>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
         </is>
       </c>
       <c r="C334" s="255" t="inlineStr">
@@ -56292,37 +56607,33 @@
       </c>
       <c r="D334" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation Information Details</t>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis Details</t>
         </is>
       </c>
       <c r="E334" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automatic Major Activity?</t>
+          <t xml:space="preserve">Critical Design Actions - Justification</t>
         </is>
       </c>
       <c r="F334" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Automatic Major Activity?</t>
+          <t xml:space="preserve">Critical Design Actions - Justification</t>
         </is>
       </c>
       <c r="G334" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flags activities that are always graded Major.</t>
+          <t xml:space="preserve">Why critical design actions are not closed.</t>
         </is>
       </c>
       <c r="H334" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes/No</t>
-        </is>
-      </c>
-      <c r="I334" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooltip: Yes if the change includes an activity on the Automatic Major list (see L09), e.g. floating roof/deck landing, tank entry, changes to Safety Critical Equipment.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="I334" s="254"/>
       <c r="J334" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">If Yes, Grade of Change must be Major (validation, see AH13).</t>
+          <t xml:space="preserve">Visible and mandatory if 'All critical design action items closed?' = No.</t>
         </is>
       </c>
       <c r="K334" s="256" t="inlineStr">
@@ -56335,69 +56646,69 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M334" s="268" t="inlineStr">
+      <c r="M334" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N334" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="N334" s="253" t="inlineStr">
+      <c r="O334" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P334" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O334" s="268" t="inlineStr">
+      <c r="Q334" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P334" s="268" t="inlineStr">
+      <c r="R334" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="Q334" s="253" t="inlineStr">
+      <c r="S334" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R334" s="253" t="inlineStr">
+      <c r="T334" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S334" s="253" t="inlineStr">
+      <c r="U334" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T334" s="253" t="inlineStr">
+      <c r="V334" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="U334" s="253" t="inlineStr">
+      <c r="W334" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="V334" s="253" t="inlineStr">
+      <c r="X334" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="W334" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X334" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="AA334" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaun: guidance list to remove ambiguity.</t>
+          <t xml:space="preserve">[SAM Rev2]</t>
         </is>
       </c>
     </row>
@@ -56407,7 +56718,7 @@
       </c>
       <c r="B335" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation</t>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
         </is>
       </c>
       <c r="C335" s="255" t="inlineStr">
@@ -56417,22 +56728,22 @@
       </c>
       <c r="D335" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation Information Details</t>
+          <t xml:space="preserve">Evaluation, Design &amp; Analysis Details</t>
         </is>
       </c>
       <c r="E335" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emergency Justification</t>
+          <t xml:space="preserve">Documentation Not Updated - Justification</t>
         </is>
       </c>
       <c r="F335" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emergency Justification</t>
+          <t xml:space="preserve">Documentation Not Updated - Justification</t>
         </is>
       </c>
       <c r="G335" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why the change cannot follow the normal MOC process.</t>
+          <t xml:space="preserve">Why documentation has not been updated.</t>
         </is>
       </c>
       <c r="H335" s="254" t="inlineStr">
@@ -56440,14 +56751,10 @@
           <t xml:space="preserve">Text</t>
         </is>
       </c>
-      <c r="I335" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooltip: Describe the emergency and the interim controls in place.</t>
-        </is>
-      </c>
+      <c r="I335" s="254"/>
       <c r="J335" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visible and mandatory if Emergency Change = Yes.</t>
+          <t xml:space="preserve">Visible and mandatory if 'Has all documentation been updated?' = No.</t>
         </is>
       </c>
       <c r="K335" s="256" t="inlineStr">
@@ -56460,79 +56767,79 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M335" s="268" t="inlineStr">
+      <c r="M335" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N335" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="N335" s="253" t="inlineStr">
+      <c r="O335" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="P335" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O335" s="268" t="inlineStr">
+      <c r="Q335" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P335" s="268" t="inlineStr">
+      <c r="R335" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="Q335" s="253" t="inlineStr">
+      <c r="S335" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R335" s="253" t="inlineStr">
+      <c r="T335" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S335" s="253" t="inlineStr">
+      <c r="U335" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T335" s="253" t="inlineStr">
+      <c r="V335" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="U335" s="253" t="inlineStr">
+      <c r="W335" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="V335" s="253" t="inlineStr">
+      <c r="X335" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="W335" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X335" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="AA335" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emergency MOC documents the approval obtained before the operation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="336" ht="57.6" customHeight="1">
+          <t xml:space="preserve">[SAM Rev2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="28.8" customHeight="1">
       <c r="A336" s="253">
         <v>4</v>
       </c>
       <c r="B336" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation</t>
+          <t xml:space="preserve">Implementation</t>
         </is>
       </c>
       <c r="C336" s="255" t="inlineStr">
@@ -56542,37 +56849,33 @@
       </c>
       <c r="D336" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation Information Details</t>
+          <t xml:space="preserve">Implementation Details</t>
         </is>
       </c>
       <c r="E336" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Safety Critical Equipment Affected?</t>
+          <t xml:space="preserve">PSSR - Justification</t>
         </is>
       </c>
       <c r="F336" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Safety Critical Equipment Affected?</t>
+          <t xml:space="preserve">PSSR - Justification</t>
         </is>
       </c>
       <c r="G336" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indicates if the change affects Safety Critical Equipment (SCE).</t>
+          <t xml:space="preserve">Why the PSSR is not complete.</t>
         </is>
       </c>
       <c r="H336" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes/No</t>
-        </is>
-      </c>
-      <c r="I336" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooltip: Check the Safety Critical Equipment List / maintenance critical equipment register.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="I336" s="254"/>
       <c r="J336" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Default: No.</t>
+          <t xml:space="preserve">Visible and mandatory if 'PSSR Complete?' = No.</t>
         </is>
       </c>
       <c r="K336" s="256" t="inlineStr">
@@ -56585,79 +56888,79 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M336" s="268" t="inlineStr">
+      <c r="M336" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N336" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="N336" s="253" t="inlineStr">
+      <c r="O336" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O336" s="268" t="inlineStr">
+      <c r="P336" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q336" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P336" s="268" t="inlineStr">
+      <c r="R336" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="Q336" s="253" t="inlineStr">
+      <c r="S336" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="T336" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R336" s="253" t="inlineStr">
+      <c r="U336" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V336" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S336" s="253" t="inlineStr">
+      <c r="W336" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T336" s="253" t="inlineStr">
+      <c r="X336" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="U336" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="V336" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="W336" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X336" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="AA336" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Khesar: changes to critical equipment are often missed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="337" ht="28.8" customHeight="1">
+          <t xml:space="preserve">[SAM Rev2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="43.2" customHeight="1">
       <c r="A337" s="253">
         <v>5</v>
       </c>
       <c r="B337" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation</t>
+          <t xml:space="preserve">Implementation</t>
         </is>
       </c>
       <c r="C337" s="255" t="inlineStr">
@@ -56667,22 +56970,22 @@
       </c>
       <c r="D337" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation Information Details</t>
+          <t xml:space="preserve">Implementation Details</t>
         </is>
       </c>
       <c r="E337" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">SCE Description / Tag</t>
+          <t xml:space="preserve">Training Details / Justification</t>
         </is>
       </c>
       <c r="F337" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">SCE Description / Tag</t>
+          <t xml:space="preserve">Training Details / Justification</t>
         </is>
       </c>
       <c r="G337" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Affected Safety Critical Equipment.</t>
+          <t xml:space="preserve">Training provided, or why no training is required.</t>
         </is>
       </c>
       <c r="H337" s="254" t="inlineStr">
@@ -56693,7 +56996,7 @@
       <c r="I337" s="254"/>
       <c r="J337" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visible and mandatory if SCE Affected = Yes.</t>
+          <t xml:space="preserve">Visible and mandatory once 'Training Complete?' is answered.</t>
         </is>
       </c>
       <c r="K337" s="256" t="inlineStr">
@@ -56706,75 +57009,79 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M337" s="268" t="inlineStr">
+      <c r="M337" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N337" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="N337" s="253" t="inlineStr">
+      <c r="O337" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O337" s="268" t="inlineStr">
+      <c r="P337" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q337" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P337" s="268" t="inlineStr">
+      <c r="R337" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="Q337" s="253" t="inlineStr">
+      <c r="S337" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="T337" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R337" s="253" t="inlineStr">
+      <c r="U337" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V337" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S337" s="253" t="inlineStr">
+      <c r="W337" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T337" s="253" t="inlineStr">
+      <c r="X337" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="U337" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="V337" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="W337" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X337" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="AA337" s="256"/>
-    </row>
-    <row r="338" ht="72.0" customHeight="1">
+      <c r="AA337" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="43.2" customHeight="1">
       <c r="A338" s="253">
         <v>6</v>
       </c>
       <c r="B338" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation</t>
+          <t xml:space="preserve">Implementation</t>
         </is>
       </c>
       <c r="C338" s="255" t="inlineStr">
@@ -56784,33 +57091,33 @@
       </c>
       <c r="D338" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Initiation Information Details</t>
+          <t xml:space="preserve">Implementation Details</t>
         </is>
       </c>
       <c r="E338" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approval Level</t>
+          <t xml:space="preserve">Communication Details / Justification</t>
         </is>
       </c>
       <c r="F338" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approval Level</t>
+          <t xml:space="preserve">Communication Details / Justification</t>
         </is>
       </c>
       <c r="G338" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approval route derived from Grade of Change.</t>
+          <t xml:space="preserve">Date of communication and to whom, or why not required.</t>
         </is>
       </c>
       <c r="H338" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text (calculated, read-only)</t>
+          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="I338" s="254"/>
       <c r="J338" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minor = 'Local - Terminal Manager'; Moderate = 'Regional - HSEC + Operations'; Major = 'Global - HSEC + Operations'.</t>
+          <t xml:space="preserve">Visible and mandatory once 'Has change been communicated?' is answered.</t>
         </is>
       </c>
       <c r="K338" s="256" t="inlineStr">
@@ -56823,7 +57130,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M338" s="268" t="inlineStr">
+      <c r="M338" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -56833,12 +57140,12 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O338" s="268" t="inlineStr">
+      <c r="O338" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P338" s="268" t="inlineStr">
+      <c r="P338" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56855,47 +57162,47 @@
       </c>
       <c r="S338" s="253" t="inlineStr">
         <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="T338" s="253" t="inlineStr">
+        <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T338" s="253" t="inlineStr">
+      <c r="U338" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V338" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="U338" s="253" t="inlineStr">
+      <c r="W338" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="V338" s="253" t="inlineStr">
+      <c r="X338" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="W338" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X338" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="AA338" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basic calculated field (SOW Moderate).</t>
-        </is>
-      </c>
-    </row>
-    <row r="339" ht="28.8" customHeight="1">
+          <t xml:space="preserve">[SAM Rev2] Also covers BRD FR-B3-016.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="43.2" customHeight="1">
       <c r="A339" s="253">
         <v>7</v>
       </c>
       <c r="B339" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approval</t>
+          <t xml:space="preserve">Implementation</t>
         </is>
       </c>
       <c r="C339" s="255" t="inlineStr">
@@ -56905,22 +57212,22 @@
       </c>
       <c r="D339" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approval Details</t>
+          <t xml:space="preserve">Implementation Details</t>
         </is>
       </c>
       <c r="E339" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approval Notes</t>
+          <t xml:space="preserve">Critical PSSR Actions - Justification</t>
         </is>
       </c>
       <c r="F339" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approval Notes</t>
+          <t xml:space="preserve">Critical PSSR Actions - Justification</t>
         </is>
       </c>
       <c r="G339" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notes of the MOC Coordinator during approval.</t>
+          <t xml:space="preserve">Why critical PSSR action items are not closed.</t>
         </is>
       </c>
       <c r="H339" s="254" t="inlineStr">
@@ -56929,7 +57236,11 @@
         </is>
       </c>
       <c r="I339" s="254"/>
-      <c r="J339" s="256"/>
+      <c r="J339" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible and mandatory if 'All critical PSSR action items closed?' = No.</t>
+        </is>
+      </c>
       <c r="K339" s="256" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
@@ -56940,7 +57251,7 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M339" s="268" t="inlineStr">
+      <c r="M339" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
@@ -56950,12 +57261,12 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O339" s="268" t="inlineStr">
+      <c r="O339" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P339" s="268" t="inlineStr">
+      <c r="P339" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
@@ -56967,88 +57278,92 @@
       </c>
       <c r="R339" s="253" t="inlineStr">
         <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S339" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="T339" s="253" t="inlineStr">
+        <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="S339" s="253" t="inlineStr">
+      <c r="U339" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T339" s="253" t="inlineStr">
+      <c r="V339" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="U339" s="253" t="inlineStr">
+      <c r="W339" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="V339" s="253" t="inlineStr">
+      <c r="X339" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="W339" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X339" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="AA339" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Replaces Pre-Approval Notes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="340" ht="28.8" customHeight="1">
+          <t xml:space="preserve">[SAM Rev2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="86.4" customHeight="1">
       <c r="A340" s="253">
         <v>8</v>
       </c>
       <c r="B340" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implementation</t>
+          <t xml:space="preserve">Draft (MOC Task)</t>
         </is>
       </c>
       <c r="C340" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOC</t>
+          <t xml:space="preserve">MOC Task</t>
         </is>
       </c>
       <c r="D340" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Implementation Details</t>
+          <t xml:space="preserve">MOC Task Details</t>
         </is>
       </c>
       <c r="E340" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Actual Implementation Date</t>
+          <t xml:space="preserve">Required Before</t>
         </is>
       </c>
       <c r="F340" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Actual Implementation Date</t>
+          <t xml:space="preserve">Required Before</t>
         </is>
       </c>
       <c r="G340" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date the change was implemented.</t>
+          <t xml:space="preserve">Stage by which the task must be completed.</t>
         </is>
       </c>
       <c r="H340" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="I340" s="254"/>
+          <t xml:space="preserve">Lookup (Pre-Implementation / Pre-Follow Up)</t>
+        </is>
+      </c>
+      <c r="I340" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: Pre-Implementation = must be closed before the change is implemented; Pre-Follow Up = can be completed after implementation (e.g. P&amp;ID update).</t>
+        </is>
+      </c>
       <c r="J340" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Must be on or before Today.</t>
+          <t xml:space="preserve">Field on MOC Task (all task types), mandatory. MOC stage gate checks only open tasks due for that stage [Intelex to confirm].</t>
         </is>
       </c>
       <c r="K340" s="256" t="inlineStr">
@@ -57061,24 +57376,24 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M340" s="268" t="inlineStr">
+      <c r="M340" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="N340" s="253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="O340" s="268" t="inlineStr">
-        <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P340" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
+      <c r="O340" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P340" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="Q340" s="253" t="inlineStr">
@@ -57088,12 +57403,12 @@
       </c>
       <c r="R340" s="253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="S340" s="253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="T340" s="253" t="inlineStr">
@@ -57108,7 +57423,7 @@
       </c>
       <c r="V340" s="253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="W340" s="253" t="inlineStr">
@@ -57118,20 +57433,875 @@
       </c>
       <c r="X340" s="253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="AA340" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPI: requested vs actual date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="341" x14ac:dyDescent="0.55000000000000004" ht="115.2" customHeight="1">
+          <t xml:space="preserve">[SAM Rev2] 'add ability to determine if a task is required Pre-Implementation or Pre-Follow Up' (21-Oct Khesar/Sam). BRD FR-B3-032.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" x14ac:dyDescent="0.55000000000000004" ht="72.0" customHeight="1">
       <c r="A341" s="253">
         <v>9</v>
       </c>
       <c r="B341" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C341" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D341" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E341" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change Impact Guidance - &lt;Change Type&gt;</t>
+        </is>
+      </c>
+      <c r="F341" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change Impact Guidance - &lt;Change Type&gt;</t>
+        </is>
+      </c>
+      <c r="G341" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read-only guidance with the Minor / Moderate / Major descriptors of the selected Change Type.</t>
+        </is>
+      </c>
+      <c r="H341" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text (read-only)</t>
+        </is>
+      </c>
+      <c r="I341" s="254"/>
+      <c r="J341" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 read-only text fields (one per Change Type), each visible only when Change Type = that type (hide/show). Content: Lookup L09.</t>
+        </is>
+      </c>
+      <c r="K341" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L341" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M341" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N341" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O341" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P341" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q341" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R341" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S341" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T341" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U341" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V341" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W341" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X341" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA341" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[SAM Rev2] 'utilises terminology and guidance from Change Impact tab'. Display per type = [21-Oct] Alonso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="86.4" customHeight="1">
+      <c r="A342" s="253">
+        <v>10</v>
+      </c>
+      <c r="B342" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C342" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D342" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E342" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic Major Activity?</t>
+        </is>
+      </c>
+      <c r="F342" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic Major Activity?</t>
+        </is>
+      </c>
+      <c r="G342" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flags activities that are always Major.</t>
+        </is>
+      </c>
+      <c r="H342" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No</t>
+        </is>
+      </c>
+      <c r="I342" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: Yes if the change includes an activity listed as example of Major (floating roof/deck landing, tank entry, changes to Safety Critical Equipment).</t>
+        </is>
+      </c>
+      <c r="J342" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If Yes, Change Impact must be Major (AH13).</t>
+        </is>
+      </c>
+      <c r="K342" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L342" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M342" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O342" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P342" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X342" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA342" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[BA] based on Sam's Major examples + Shaun 20-Oct. Not in Rev2 requirements - validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="28.8" customHeight="1">
+      <c r="A343" s="253">
+        <v>11</v>
+      </c>
+      <c r="B343" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C343" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D343" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E343" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergency Justification</t>
+        </is>
+      </c>
+      <c r="F343" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergency Justification</t>
+        </is>
+      </c>
+      <c r="G343" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Why the change cannot follow the normal process.</t>
+        </is>
+      </c>
+      <c r="H343" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="I343" s="254"/>
+      <c r="J343" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible and mandatory if Emergency Change = Yes.</t>
+        </is>
+      </c>
+      <c r="K343" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L343" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M343" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O343" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P343" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X343" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA343" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[BA] not in Rev2 - validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="43.2" customHeight="1">
+      <c r="A344" s="253">
+        <v>12</v>
+      </c>
+      <c r="B344" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C344" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D344" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E344" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safety Critical Equipment Affected?</t>
+        </is>
+      </c>
+      <c r="F344" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safety Critical Equipment Affected?</t>
+        </is>
+      </c>
+      <c r="G344" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Change affects SCE.</t>
+        </is>
+      </c>
+      <c r="H344" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No</t>
+        </is>
+      </c>
+      <c r="I344" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tooltip: Check the Safety Critical Equipment List.</t>
+        </is>
+      </c>
+      <c r="J344" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Default: No. If Yes: 'SCE Description / Tag' mandatory.</t>
+        </is>
+      </c>
+      <c r="K344" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L344" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M344" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O344" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P344" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X344" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA344" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[20-Oct] Khesar (critical equipment changes missed). Not in Rev2 - validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="28.8" customHeight="1">
+      <c r="A345" s="253">
+        <v>13</v>
+      </c>
+      <c r="B345" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C345" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D345" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E345" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCE Description / Tag</t>
+        </is>
+      </c>
+      <c r="F345" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SCE Description / Tag</t>
+        </is>
+      </c>
+      <c r="G345" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Affected Safety Critical Equipment.</t>
+        </is>
+      </c>
+      <c r="H345" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="I345" s="254"/>
+      <c r="J345" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible and mandatory if SCE Affected = Yes.</t>
+        </is>
+      </c>
+      <c r="K345" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L345" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M345" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="O345" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P345" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X345" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA345" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[20-Oct] see above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="72.0" customHeight="1">
+      <c r="A346" s="253">
+        <v>14</v>
+      </c>
+      <c r="B346" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C346" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D346" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E346" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approval Level</t>
+        </is>
+      </c>
+      <c r="F346" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approval Level</t>
+        </is>
+      </c>
+      <c r="G346" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Approval route derived from Change Impact.</t>
+        </is>
+      </c>
+      <c r="H346" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text (calculated, read-only)</t>
+        </is>
+      </c>
+      <c r="I346" s="254"/>
+      <c r="J346" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minor = 'Local - TM + technical specialist'; Moderate = 'Regional - HSEC + Ops'; Major = 'Global - HSEC + Ops'.</t>
+        </is>
+      </c>
+      <c r="K346" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L346" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M346" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O346" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P346" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X346" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA346" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[BA] helps users see the route. Validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="28.8" customHeight="1">
+      <c r="A347" s="253">
+        <v>15</v>
+      </c>
+      <c r="B347" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementation</t>
+        </is>
+      </c>
+      <c r="C347" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D347" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementation Details</t>
+        </is>
+      </c>
+      <c r="E347" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actual Implementation Date</t>
+        </is>
+      </c>
+      <c r="F347" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actual Implementation Date</t>
+        </is>
+      </c>
+      <c r="G347" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date the change was implemented.</t>
+        </is>
+      </c>
+      <c r="H347" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="I347" s="254"/>
+      <c r="J347" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Must be on or before Today.</t>
+        </is>
+      </c>
+      <c r="K347" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L347" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M347" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O347" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P347" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="T347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="U347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X347" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA347" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[BRD] FR-B3-031 / [BA] KPI requested vs actual. Validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="86.4" customHeight="1">
+      <c r="A348" s="253">
+        <v>16</v>
+      </c>
+      <c r="B348" s="255" t="inlineStr">
         <is>
           <t xml:space="preserve">• Evaluation, Design &amp; Analysis
 • Approval
@@ -57140,899 +58310,40 @@
 • Follow Up</t>
         </is>
       </c>
-      <c r="C341" s="255" t="inlineStr">
+      <c r="C348" s="255" t="inlineStr">
         <is>
           <t xml:space="preserve">MOC</t>
         </is>
       </c>
-      <c r="D341" s="255" t="inlineStr">
+      <c r="D348" s="255" t="inlineStr">
         <is>
           <t xml:space="preserve">Action Plans</t>
         </is>
       </c>
-      <c r="E341" s="257" t="inlineStr">
+      <c r="E348" s="257" t="inlineStr">
         <is>
           <t xml:space="preserve">Action Plans (OPTIONAL)</t>
         </is>
       </c>
-      <c r="F341" s="257" t="inlineStr">
+      <c r="F348" s="257" t="inlineStr">
         <is>
           <t xml:space="preserve">Action Plans (OPTIONAL)</t>
         </is>
       </c>
-      <c r="G341" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actions arising from the MOC (permits, licences, site-specific checks).</t>
-        </is>
-      </c>
-      <c r="H341" s="254" t="inlineStr">
+      <c r="G348" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actions arising from the MOC.</t>
+        </is>
+      </c>
+      <c r="H348" s="254" t="inlineStr">
         <is>
           <t xml:space="preserve">Relations</t>
-        </is>
-      </c>
-      <c r="I341" s="254"/>
-      <c r="J341" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1:M relation to Action Plan object; columns: Action No. | Description | Person Responsible | Due Date | Status. Only if Intelex confirms low effort. Decision 21-Oct: MOC Tasks remain the MOC actions.</t>
-        </is>
-      </c>
-      <c r="K341" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="L341" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="M341" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="N341" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="O341" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="P341" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="Q341" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="R341" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="S341" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="T341" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="U341" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="V341" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="W341" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X341" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="AA341" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nice-to-have (Sam). Shaun 21-Oct: OK with tasks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="342" ht="72.0" customHeight="1">
-      <c r="A342" s="253">
-        <v>10</v>
-      </c>
-      <c r="B342" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Draft (MOC Task)</t>
-        </is>
-      </c>
-      <c r="C342" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC</t>
-        </is>
-      </c>
-      <c r="D342" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC Task Details</t>
-        </is>
-      </c>
-      <c r="E342" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Complete Before Stage</t>
-        </is>
-      </c>
-      <c r="F342" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Complete Before Stage</t>
-        </is>
-      </c>
-      <c r="G342" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC stage by which the task must be closed.</t>
-        </is>
-      </c>
-      <c r="H342" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lookup (Approval / Start Up / Follow Up)</t>
-        </is>
-      </c>
-      <c r="I342" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooltip: Pre-startup tasks = Start Up; post-change tasks (e.g. P&amp;ID update) = Follow Up.</t>
-        </is>
-      </c>
-      <c r="J342" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Field on MOC Task (all task types). MOC stage gate checks only open tasks due for that stage [Intelex to confirm].</t>
-        </is>
-      </c>
-      <c r="K342" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="L342" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="M342" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="N342" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="O342" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="P342" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="Q342" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="R342" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="S342" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="T342" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="U342" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="V342" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="W342" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X342" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="AA342" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21-Oct (Khesar / Sam): tasks due later must not block the MOC. BRD FR-B3-032.</t>
-        </is>
-      </c>
-    </row>
-    <row r="343" ht="57.6" customHeight="1">
-      <c r="A343" s="253">
-        <v>11</v>
-      </c>
-      <c r="B343" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Initiation</t>
-        </is>
-      </c>
-      <c r="C343" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC</t>
-        </is>
-      </c>
-      <c r="D343" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Initiation Information Details</t>
-        </is>
-      </c>
-      <c r="E343" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Change Owner</t>
-        </is>
-      </c>
-      <c r="F343" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Change Owner</t>
-        </is>
-      </c>
-      <c r="G343" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Accountable for the change through to closure.</t>
-        </is>
-      </c>
-      <c r="H343" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Relations</t>
-        </is>
-      </c>
-      <c r="I343" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooltip: Person accountable for the change until closure (may be the requester).</t>
-        </is>
-      </c>
-      <c r="J343" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M:1 relation to Employee. Default Value: Change Requester.</t>
-        </is>
-      </c>
-      <c r="K343" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="L343" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="M343" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="N343" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="O343" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="P343" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="Q343" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="R343" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="S343" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="T343" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="U343" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="V343" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="W343" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X343" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="AA343" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BRD FR-B3-026 (Should) / FR-B3-004: originator vs owner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="344" ht="43.2" customHeight="1">
-      <c r="A344" s="253">
-        <v>12</v>
-      </c>
-      <c r="B344" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Initiation</t>
-        </is>
-      </c>
-      <c r="C344" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC</t>
-        </is>
-      </c>
-      <c r="D344" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Initiation Information Details</t>
-        </is>
-      </c>
-      <c r="E344" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operational Owner</t>
-        </is>
-      </c>
-      <c r="F344" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operational Owner</t>
-        </is>
-      </c>
-      <c r="G344" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Owner of the affected area or asset.</t>
-        </is>
-      </c>
-      <c r="H344" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Relations</t>
-        </is>
-      </c>
-      <c r="I344" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooltip: Responsible for operational readiness before start-up.</t>
-        </is>
-      </c>
-      <c r="J344" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M:1 relation to Employee.</t>
-        </is>
-      </c>
-      <c r="K344" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="L344" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="M344" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="N344" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="O344" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="P344" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="Q344" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="R344" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="S344" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="T344" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="U344" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="V344" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="W344" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X344" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="AA344" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BRD FR-B3-004 (Must).</t>
-        </is>
-      </c>
-    </row>
-    <row r="345" ht="28.8" customHeight="1">
-      <c r="A345" s="253">
-        <v>13</v>
-      </c>
-      <c r="B345" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Initiation</t>
-        </is>
-      </c>
-      <c r="C345" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC</t>
-        </is>
-      </c>
-      <c r="D345" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Initiation Information Details</t>
-        </is>
-      </c>
-      <c r="E345" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Affected Equipment / Process / System</t>
-        </is>
-      </c>
-      <c r="F345" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Affected Equipment / Process / System</t>
-        </is>
-      </c>
-      <c r="G345" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What the change touches.</t>
-        </is>
-      </c>
-      <c r="H345" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Text</t>
-        </is>
-      </c>
-      <c r="I345" s="254"/>
-      <c r="J345" s="256"/>
-      <c r="K345" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="L345" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="M345" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="N345" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="O345" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="P345" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="Q345" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="R345" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="S345" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="T345" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="U345" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="V345" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="W345" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X345" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="AA345" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BRD FR-B3-001 (Must).</t>
-        </is>
-      </c>
-    </row>
-    <row r="346" ht="57.6" customHeight="1">
-      <c r="A346" s="253">
-        <v>14</v>
-      </c>
-      <c r="B346" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Initiation</t>
-        </is>
-      </c>
-      <c r="C346" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC</t>
-        </is>
-      </c>
-      <c r="D346" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Initiation Information Details</t>
-        </is>
-      </c>
-      <c r="E346" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Temporary Change Review Date</t>
-        </is>
-      </c>
-      <c r="F346" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Temporary Change Review Date</t>
-        </is>
-      </c>
-      <c r="G346" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Next review of the temporary change.</t>
-        </is>
-      </c>
-      <c r="H346" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="I346" s="254"/>
-      <c r="J346" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visible and mandatory if Temporary Change = Yes. Must be on or before Change Expiry.</t>
-        </is>
-      </c>
-      <c r="K346" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="L346" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="M346" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="N346" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="O346" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="P346" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="Q346" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="R346" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="S346" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="T346" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="U346" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="V346" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="W346" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X346" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="AA346" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BRD FR-B3-003 / FR-B3-014 (Must).</t>
-        </is>
-      </c>
-    </row>
-    <row r="347" ht="43.2" customHeight="1">
-      <c r="A347" s="253">
-        <v>15</v>
-      </c>
-      <c r="B347" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Follow Up</t>
-        </is>
-      </c>
-      <c r="C347" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC</t>
-        </is>
-      </c>
-      <c r="D347" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Follow-Up Details</t>
-        </is>
-      </c>
-      <c r="E347" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Number of Extensions</t>
-        </is>
-      </c>
-      <c r="F347" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Number of Extensions</t>
-        </is>
-      </c>
-      <c r="G347" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Times the temporary change has been extended.</t>
-        </is>
-      </c>
-      <c r="H347" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Number</t>
-        </is>
-      </c>
-      <c r="I347" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooltip: Each extension needs a rationale and re-approval at the MOC grade.</t>
-        </is>
-      </c>
-      <c r="J347" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visible if Temporary Change = Yes. Max 3 (AH16).</t>
-        </is>
-      </c>
-      <c r="K347" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="L347" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="M347" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="N347" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="O347" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="P347" s="268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="Q347" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="R347" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="S347" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="T347" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="U347" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="V347" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="W347" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X347" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="AA347" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BRD RULE-B3-08 (Must).</t>
-        </is>
-      </c>
-    </row>
-    <row r="348" ht="28.8" customHeight="1">
-      <c r="A348" s="253">
-        <v>16</v>
-      </c>
-      <c r="B348" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Follow Up</t>
-        </is>
-      </c>
-      <c r="C348" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOC</t>
-        </is>
-      </c>
-      <c r="D348" s="255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Follow-Up Details</t>
-        </is>
-      </c>
-      <c r="E348" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Extension Rationale</t>
-        </is>
-      </c>
-      <c r="F348" s="257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Extension Rationale</t>
-        </is>
-      </c>
-      <c r="G348" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Why the temporary change is extended.</t>
-        </is>
-      </c>
-      <c r="H348" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Text</t>
         </is>
       </c>
       <c r="I348" s="254"/>
       <c r="J348" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visible and mandatory if Number of Extensions &gt; 0.</t>
+          <t xml:space="preserve">Only if Intelex confirms low effort. Decision 21-Oct: MOC Tasks remain the MOC actions.</t>
         </is>
       </c>
       <c r="K348" s="256" t="inlineStr">
@@ -58045,26 +58356,26 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M348" s="268" t="inlineStr">
+      <c r="M348" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="N348" s="253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="O348" s="268" t="inlineStr">
-        <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P348" s="268" t="inlineStr">
+      <c r="O348" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
+      <c r="P348" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
       <c r="Q348" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
@@ -58107,11 +58418,11 @@
       </c>
       <c r="AA348" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD FR-B3-003 (Must).</t>
-        </is>
-      </c>
-    </row>
-    <row r="349" ht="57.6" customHeight="1">
+          <t xml:space="preserve">[21-Oct] nice-to-have (Sam). Shaun OK with tasks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="43.2" customHeight="1">
       <c r="A349" s="253">
         <v>17</v>
       </c>
@@ -58132,28 +58443,28 @@
       </c>
       <c r="E349" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regularisation Due Date</t>
+          <t xml:space="preserve">Change Owner</t>
         </is>
       </c>
       <c r="F349" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regularisation Due Date</t>
+          <t xml:space="preserve">Change Owner</t>
         </is>
       </c>
       <c r="G349" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deadline to complete the emergency MOC dossier.</t>
+          <t xml:space="preserve">Accountable for the change through to closure.</t>
         </is>
       </c>
       <c r="H349" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date (calculated, read-only)</t>
+          <t xml:space="preserve">Relations</t>
         </is>
       </c>
       <c r="I349" s="254"/>
       <c r="J349" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visible if Emergency Change = Yes. = date of approval + [TBC] days. Overdue flag in reports.</t>
+          <t xml:space="preserve">M:1 relation to Employee. Default: Change Requester.</t>
         </is>
       </c>
       <c r="K349" s="256" t="inlineStr">
@@ -58166,69 +58477,69 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M349" s="268" t="inlineStr">
+      <c r="M349" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N349" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="N349" s="253" t="inlineStr">
+      <c r="O349" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P349" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="O349" s="268" t="inlineStr">
+      <c r="Q349" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P349" s="268" t="inlineStr">
+      <c r="R349" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="Q349" s="253" t="inlineStr">
+      <c r="S349" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R349" s="253" t="inlineStr">
+      <c r="T349" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S349" s="253" t="inlineStr">
+      <c r="U349" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T349" s="253" t="inlineStr">
+      <c r="V349" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="U349" s="253" t="inlineStr">
+      <c r="W349" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="V349" s="253" t="inlineStr">
+      <c r="X349" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="W349" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X349" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="AA349" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD RULE-B3-14 / FR-B3-015 (Must).</t>
+          <t xml:space="preserve">[BRD] FR-B3-026 / FR-B3-004. Not in Rev2 - validate.</t>
         </is>
       </c>
     </row>
@@ -58238,7 +58549,7 @@
       </c>
       <c r="B350" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
+          <t xml:space="preserve">Initiation</t>
         </is>
       </c>
       <c r="C350" s="255" t="inlineStr">
@@ -58248,31 +58559,35 @@
       </c>
       <c r="D350" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evaluation, Design &amp; Analysis Details</t>
+          <t xml:space="preserve">Initiation Information Details</t>
         </is>
       </c>
       <c r="E350" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposed Implementation Plan</t>
+          <t xml:space="preserve">Operational Owner</t>
         </is>
       </c>
       <c r="F350" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proposed Implementation Plan</t>
+          <t xml:space="preserve">Operational Owner</t>
         </is>
       </c>
       <c r="G350" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">How and when the change will be implemented.</t>
+          <t xml:space="preserve">Owner of the affected area or asset.</t>
         </is>
       </c>
       <c r="H350" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text (multi-line)</t>
+          <t xml:space="preserve">Relations</t>
         </is>
       </c>
       <c r="I350" s="254"/>
-      <c r="J350" s="256"/>
+      <c r="J350" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M:1 relation to Employee.</t>
+        </is>
+      </c>
       <c r="K350" s="256" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
@@ -58283,79 +58598,79 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M350" s="268" t="inlineStr">
+      <c r="M350" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N350" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="N350" s="253" t="inlineStr">
+      <c r="O350" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O350" s="268" t="inlineStr">
+      <c r="P350" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="P350" s="268" t="inlineStr">
+      <c r="Q350" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="Q350" s="253" t="inlineStr">
+      <c r="R350" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S350" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R350" s="253" t="inlineStr">
+      <c r="T350" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S350" s="253" t="inlineStr">
+      <c r="U350" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T350" s="253" t="inlineStr">
+      <c r="V350" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="U350" s="253" t="inlineStr">
+      <c r="W350" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="V350" s="253" t="inlineStr">
+      <c r="X350" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="W350" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X350" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="AA350" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD FR-B3-001 (Must).</t>
-        </is>
-      </c>
-    </row>
-    <row r="351" ht="72.0" customHeight="1">
+          <t xml:space="preserve">[BRD] FR-B3-004. Not in Rev2 - validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="28.8" customHeight="1">
       <c r="A351" s="253">
         <v>19</v>
       </c>
       <c r="B351" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
+          <t xml:space="preserve">Initiation</t>
         </is>
       </c>
       <c r="C351" s="255" t="inlineStr">
@@ -58365,22 +58680,22 @@
       </c>
       <c r="D351" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evaluation, Design &amp; Analysis Details</t>
+          <t xml:space="preserve">Initiation Information Details</t>
         </is>
       </c>
       <c r="E351" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Affected Personnel / Groups</t>
+          <t xml:space="preserve">Affected Equipment / Process / System</t>
         </is>
       </c>
       <c r="F351" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Affected Personnel / Groups</t>
+          <t xml:space="preserve">Affected Equipment / Process / System</t>
         </is>
       </c>
       <c r="G351" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">People or groups to inform and train.</t>
+          <t xml:space="preserve">What the change touches.</t>
         </is>
       </c>
       <c r="H351" s="254" t="inlineStr">
@@ -58388,11 +58703,7 @@
           <t xml:space="preserve">Text</t>
         </is>
       </c>
-      <c r="I351" s="254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tooltip: e.g. all operators at the terminal, maintenance contractor. Create Change Communication and Training tasks.</t>
-        </is>
-      </c>
+      <c r="I351" s="254"/>
       <c r="J351" s="256"/>
       <c r="K351" s="256" t="inlineStr">
         <is>
@@ -58404,69 +58715,69 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M351" s="268" t="inlineStr">
+      <c r="M351" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N351" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="N351" s="253" t="inlineStr">
+      <c r="O351" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O351" s="268" t="inlineStr">
+      <c r="P351" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="P351" s="268" t="inlineStr">
+      <c r="Q351" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="Q351" s="253" t="inlineStr">
+      <c r="R351" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S351" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R351" s="253" t="inlineStr">
+      <c r="T351" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="S351" s="253" t="inlineStr">
+      <c r="U351" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T351" s="253" t="inlineStr">
+      <c r="V351" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="U351" s="253" t="inlineStr">
+      <c r="W351" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="V351" s="253" t="inlineStr">
+      <c r="X351" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="W351" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="X351" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="AA351" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD FR-B3-016 (Must) / RULE-B3-10.</t>
+          <t xml:space="preserve">[BRD] FR-B3-001. Not in Rev2 - validate.</t>
         </is>
       </c>
     </row>
@@ -58476,7 +58787,7 @@
       </c>
       <c r="B352" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Follow Up</t>
+          <t xml:space="preserve">Initiation</t>
         </is>
       </c>
       <c r="C352" s="255" t="inlineStr">
@@ -58486,31 +58797,35 @@
       </c>
       <c r="D352" s="255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Follow-Up Details</t>
+          <t xml:space="preserve">Initiation Information Details</t>
         </is>
       </c>
       <c r="E352" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field Verification (walk-around) Completed?</t>
+          <t xml:space="preserve">Temporary Change Review Date</t>
         </is>
       </c>
       <c r="F352" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Field Verification (walk-around) Completed?</t>
+          <t xml:space="preserve">Temporary Change Review Date</t>
         </is>
       </c>
       <c r="G352" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post-MoC field check.</t>
+          <t xml:space="preserve">Next review of the temporary change.</t>
         </is>
       </c>
       <c r="H352" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes/No</t>
+          <t xml:space="preserve">Date</t>
         </is>
       </c>
       <c r="I352" s="254"/>
-      <c r="J352" s="256"/>
+      <c r="J352" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible and mandatory if Temporary Change = Yes.</t>
+        </is>
+      </c>
       <c r="K352" s="256" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
@@ -58521,61 +58836,61 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M352" s="268" t="inlineStr">
+      <c r="M352" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="N352" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="N352" s="253" t="inlineStr">
+      <c r="O352" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O352" s="268" t="inlineStr">
+      <c r="P352" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P352" s="268" t="inlineStr">
+      <c r="Q352" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="Q352" s="253" t="inlineStr">
+      <c r="R352" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R352" s="253" t="inlineStr">
+      <c r="S352" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="S352" s="253" t="inlineStr">
+      <c r="T352" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T352" s="253" t="inlineStr">
+      <c r="U352" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="U352" s="253" t="inlineStr">
+      <c r="V352" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="V352" s="253" t="inlineStr">
+      <c r="W352" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="W352" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="X352" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
@@ -58583,7 +58898,7 @@
       </c>
       <c r="AA352" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD FR-B3-012 (Must).</t>
+          <t xml:space="preserve">[BRD] FR-B3-014. Not in Rev2 - validate.</t>
         </is>
       </c>
     </row>
@@ -58608,26 +58923,30 @@
       </c>
       <c r="E353" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Affected Personnel Interviewed / Communication Confirmed?</t>
+          <t xml:space="preserve">Number of Extensions</t>
         </is>
       </c>
       <c r="F353" s="257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Affected Personnel Interviewed / Communication Confirmed?</t>
+          <t xml:space="preserve">Number of Extensions</t>
         </is>
       </c>
       <c r="G353" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post-MoC communication check.</t>
+          <t xml:space="preserve">Times the temporary change has been extended.</t>
         </is>
       </c>
       <c r="H353" s="254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes/No</t>
+          <t xml:space="preserve">Number</t>
         </is>
       </c>
       <c r="I353" s="254"/>
-      <c r="J353" s="256"/>
+      <c r="J353" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible if Temporary Change = Yes. Max 3 (AH16).</t>
+        </is>
+      </c>
       <c r="K353" s="256" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
@@ -58638,61 +58957,61 @@
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M353" s="268" t="inlineStr">
+      <c r="M353" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="N353" s="253" t="inlineStr">
         <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O353" s="269" t="inlineStr">
+        <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O353" s="268" t="inlineStr">
+      <c r="P353" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P353" s="268" t="inlineStr">
+      <c r="Q353" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="Q353" s="253" t="inlineStr">
+      <c r="R353" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R353" s="253" t="inlineStr">
+      <c r="S353" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="S353" s="253" t="inlineStr">
+      <c r="T353" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="T353" s="253" t="inlineStr">
+      <c r="U353" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="U353" s="253" t="inlineStr">
+      <c r="V353" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="V353" s="253" t="inlineStr">
+      <c r="W353" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="W353" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
       <c r="X353" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
@@ -58700,7 +59019,7 @@
       </c>
       <c r="AA353" s="256" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD FR-B3-012 (Must).</t>
+          <t xml:space="preserve">[BRD] RULE-B3-08. Not in Rev2 - validate.</t>
         </is>
       </c>
     </row>
@@ -58725,99 +59044,458 @@
       </c>
       <c r="E354" s="257" t="inlineStr">
         <is>
+          <t xml:space="preserve">Extension Rationale</t>
+        </is>
+      </c>
+      <c r="F354" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extension Rationale</t>
+        </is>
+      </c>
+      <c r="G354" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Why the temporary change is extended.</t>
+        </is>
+      </c>
+      <c r="H354" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Text</t>
+        </is>
+      </c>
+      <c r="I354" s="254"/>
+      <c r="J354" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible and mandatory if Number of Extensions &gt; 0.</t>
+        </is>
+      </c>
+      <c r="K354" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L354" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M354" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O354" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P354" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="Q354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="S354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="U354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="W354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X354" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="AA354" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[BRD] FR-B3-003. Not in Rev2 - validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="43.2" customHeight="1">
+      <c r="A355" s="253">
+        <v>23</v>
+      </c>
+      <c r="B355" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation</t>
+        </is>
+      </c>
+      <c r="C355" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D355" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiation Information Details</t>
+        </is>
+      </c>
+      <c r="E355" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regularisation Due Date</t>
+        </is>
+      </c>
+      <c r="F355" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regularisation Due Date</t>
+        </is>
+      </c>
+      <c r="G355" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deadline to complete the emergency MOC dossier.</t>
+        </is>
+      </c>
+      <c r="H355" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date (calculated, read-only)</t>
+        </is>
+      </c>
+      <c r="I355" s="254"/>
+      <c r="J355" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visible if Emergency Change = Yes. = approval date + [TBC] days.</t>
+        </is>
+      </c>
+      <c r="K355" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L355" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M355" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N355" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O355" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P355" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q355" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R355" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S355" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T355" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U355" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V355" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W355" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="X355" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="AA355" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[BRD] RULE-B3-14. Not in Rev2 - validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="28.8" customHeight="1">
+      <c r="A356" s="253">
+        <v>24</v>
+      </c>
+      <c r="B356" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow Up</t>
+        </is>
+      </c>
+      <c r="C356" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D356" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow-Up Details</t>
+        </is>
+      </c>
+      <c r="E356" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field Verification (walk-around) Completed?</t>
+        </is>
+      </c>
+      <c r="F356" s="257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field Verification (walk-around) Completed?</t>
+        </is>
+      </c>
+      <c r="G356" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post-MoC field check.</t>
+        </is>
+      </c>
+      <c r="H356" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes/No</t>
+        </is>
+      </c>
+      <c r="I356" s="254"/>
+      <c r="J356" s="256"/>
+      <c r="K356" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="L356" s="254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="M356" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N356" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O356" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="P356" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q356" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="R356" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S356" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="T356" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U356" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="V356" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W356" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="X356" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="AA356" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[BRD] FR-B3-012. Not in Rev2 - validate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="28.8" customHeight="1">
+      <c r="A357" s="253">
+        <v>25</v>
+      </c>
+      <c r="B357" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow Up</t>
+        </is>
+      </c>
+      <c r="C357" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC</t>
+        </is>
+      </c>
+      <c r="D357" s="255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Follow-Up Details</t>
+        </is>
+      </c>
+      <c r="E357" s="257" t="inlineStr">
+        <is>
           <t xml:space="preserve">Downstream &amp; Cumulative Impacts Reviewed?</t>
         </is>
       </c>
-      <c r="F354" s="257" t="inlineStr">
+      <c r="F357" s="257" t="inlineStr">
         <is>
           <t xml:space="preserve">Downstream &amp; Cumulative Impacts Reviewed?</t>
         </is>
       </c>
-      <c r="G354" s="254" t="inlineStr">
+      <c r="G357" s="254" t="inlineStr">
         <is>
           <t xml:space="preserve">Post-MoC impact review.</t>
         </is>
       </c>
-      <c r="H354" s="254" t="inlineStr">
+      <c r="H357" s="254" t="inlineStr">
         <is>
           <t xml:space="preserve">Yes/No</t>
         </is>
       </c>
-      <c r="I354" s="254"/>
-      <c r="J354" s="256"/>
-      <c r="K354" s="256" t="inlineStr">
+      <c r="I357" s="254"/>
+      <c r="J357" s="256"/>
+      <c r="K357" s="256" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c r="L354" s="254" t="inlineStr">
+      <c r="L357" s="254" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="M354" s="268" t="inlineStr">
+      <c r="M357" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="N354" s="253" t="inlineStr">
+      <c r="N357" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="O357" s="269" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="O354" s="268" t="inlineStr">
+      <c r="P357" s="269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q357" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="P354" s="268" t="inlineStr">
+      <c r="R357" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="S357" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="Q354" s="253" t="inlineStr">
+      <c r="T357" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="U357" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="R354" s="253" t="inlineStr">
+      <c r="V357" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="W357" s="253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="X357" s="253" t="inlineStr">
         <is>
           <t xml:space="preserve">N</t>
         </is>
       </c>
-      <c r="S354" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="T354" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="U354" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="V354" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="W354" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="X354" s="253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="AA354" s="256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BRD FR-B3-012 (Must).</t>
+      <c r="AA357" s="256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[BRD] FR-B3-012. Not in Rev2 - validate.</t>
         </is>
       </c>
     </row>
@@ -64089,9 +64767,9 @@
         <v>387</v>
       </c>
       <c r="B4" s="74"/>
-      <c r="C4" s="269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R - Priority field removed (Grade of Change is the single driver).</t>
+      <c r="C4" s="270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duplicate of L05. Priority KEPT (Sam Rev2) using L05; values [TBC].</t>
         </is>
       </c>
     </row>
@@ -64140,7 +64818,7 @@
         <v>190</v>
       </c>
       <c r="B11" s="74"/>
-      <c r="C11" s="269" t="inlineStr">
+      <c r="C11" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Check: values are the Approval objects (same as L07); Task Type should list MOC Task children (L06). Intelex to confirm.</t>
         </is>
@@ -64223,7 +64901,7 @@
         <v>197</v>
       </c>
       <c r="B20" s="74"/>
-      <c r="C20" s="269" t="inlineStr">
+      <c r="C20" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">M - aligned to the new 6-stage workflow.</t>
         </is>
@@ -64252,12 +64930,12 @@
       <c r="E22" s="13"/>
     </row>
     <row r="23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="269" t="inlineStr">
+      <c r="A23" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
         </is>
       </c>
-      <c r="B23" s="269" t="inlineStr">
+      <c r="B23" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Evaluation, Design &amp; Analysis</t>
         </is>
@@ -64266,12 +64944,12 @@
       <c r="E23" s="13"/>
     </row>
     <row r="24" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="270" t="inlineStr">
+      <c r="A24" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">Approval</t>
         </is>
       </c>
-      <c r="B24" s="270" t="inlineStr">
+      <c r="B24" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">Approval</t>
         </is>
@@ -64280,12 +64958,12 @@
       <c r="E24" s="13"/>
     </row>
     <row r="25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="270" t="inlineStr">
+      <c r="A25" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">Implementation</t>
         </is>
       </c>
-      <c r="B25" s="270" t="inlineStr">
+      <c r="B25" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">Implementation</t>
         </is>
@@ -64294,12 +64972,12 @@
       <c r="E25" s="13"/>
     </row>
     <row r="26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="270" t="inlineStr">
+      <c r="A26" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">Start-Up</t>
         </is>
       </c>
-      <c r="B26" s="270" t="inlineStr">
+      <c r="B26" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">Start-Up</t>
         </is>
@@ -64308,12 +64986,12 @@
       <c r="E26" s="13"/>
     </row>
     <row r="27" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="270" t="inlineStr">
+      <c r="A27" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">Follow-Up</t>
         </is>
       </c>
-      <c r="B27" s="270" t="inlineStr">
+      <c r="B27" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">Follow-Up</t>
         </is>
@@ -64322,17 +65000,17 @@
       <c r="E27" s="13"/>
     </row>
     <row r="28" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="270"/>
-      <c r="B28" s="270"/>
+      <c r="A28" s="271"/>
+      <c r="B28" s="271"/>
     </row>
     <row r="30" ht="43.2" x14ac:dyDescent="0.85" customHeight="1">
-      <c r="A30" s="271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L04 - Grade of Change (Change Impact)</t>
+      <c r="A30" s="272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L04 - Change Impact</t>
         </is>
       </c>
       <c r="B30" s="74"/>
-      <c r="C30" s="269" t="inlineStr">
+      <c r="C30" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">M - single criticality list used by MOC and by Screening / Task / Approval setups. Minor = Local, Moderate = Regional, Major = Global approval.</t>
         </is>
@@ -64347,49 +65025,49 @@
       </c>
     </row>
     <row r="32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="269" t="inlineStr">
+      <c r="A32" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Minor</t>
         </is>
       </c>
-      <c r="B32" s="269" t="inlineStr">
+      <c r="B32" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Minor</t>
         </is>
       </c>
     </row>
     <row r="33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="269" t="inlineStr">
+      <c r="A33" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Moderate</t>
         </is>
       </c>
-      <c r="B33" s="269" t="inlineStr">
+      <c r="B33" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Moderate</t>
         </is>
       </c>
     </row>
     <row r="34" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="270" t="inlineStr">
+      <c r="A34" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">Major</t>
         </is>
       </c>
-      <c r="B34" s="270" t="inlineStr">
+      <c r="B34" s="271" t="inlineStr">
         <is>
           <t xml:space="preserve">Major</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="28.8" x14ac:dyDescent="0.85" customHeight="1">
+    <row r="36" ht="43.2" x14ac:dyDescent="0.85" customHeight="1">
       <c r="A36" s="61" t="s">
         <v>382</v>
       </c>
       <c r="B36" s="74"/>
-      <c r="C36" s="269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R - duplicate of L01; replace its references (Task/Approval setup, Change Impact) by L04.</t>
+      <c r="C36" s="270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L05 = Priority values (Sam Rev2 keeps Priority) [TBC values]. Task/Approval setups and Change Impact must use L04, not L05.</t>
         </is>
       </c>
     </row>
@@ -64430,7 +65108,7 @@
         <v>447</v>
       </c>
       <c r="B42" s="74"/>
-      <c r="C42" s="269" t="inlineStr">
+      <c r="C42" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Keep. Mapping to checklist sections: Impact/Hazard Assessment (B), Process (C, E-H), Documentation (D), Training + Change Communication (I), PSSR (K), Checklist (generic).</t>
         </is>
@@ -64505,7 +65183,7 @@
         <v>769</v>
       </c>
       <c r="B52" s="74"/>
-      <c r="C52" s="269" t="inlineStr">
+      <c r="C52" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">[TBC] 21-Oct: keep OOTB types for functional approvals; add Operations (Khesar) and Maintenance; level approvals (TM / Regional HSEC-Ops / Global HSEC-Ops) also needed. Intelex to propose re-caption vs new objects.</t>
         </is>
@@ -64570,12 +65248,12 @@
     <row r="62">
       <c r="A62" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve">L08 - Type of Change (MOC Category data)</t>
-        </is>
-      </c>
-      <c r="C62" s="269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A - records of the MOC Category object (caption 'Type of Change').</t>
+          <t xml:space="preserve">L08 - Change Type (MOC Category data)</t>
+        </is>
+      </c>
+      <c r="C62" s="270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A - records of the MOC Category object (caption 'Change Type').</t>
         </is>
       </c>
     </row>
@@ -64592,96 +65270,96 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="269" t="inlineStr">
+      <c r="A64" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Change of Design / Equipment</t>
         </is>
       </c>
-      <c r="B64" s="269" t="inlineStr">
+      <c r="B64" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Change of Design / Equipment</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="269" t="inlineStr">
+      <c r="A65" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Change of Process</t>
         </is>
       </c>
-      <c r="B65" s="269" t="inlineStr">
+      <c r="B65" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Change of Process</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="269" t="inlineStr">
+      <c r="A66" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Change of Procedure</t>
         </is>
       </c>
-      <c r="B66" s="269" t="inlineStr">
+      <c r="B66" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Change of Procedure</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="269" t="inlineStr">
+      <c r="A67" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Change of Control Systems / IT / SIS</t>
         </is>
       </c>
-      <c r="B67" s="269" t="inlineStr">
+      <c r="B67" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Change of Control Systems / IT / SIS</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="269" t="inlineStr">
+      <c r="A68" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">5. Organisational / Personnel Change</t>
         </is>
       </c>
-      <c r="B68" s="269" t="inlineStr">
+      <c r="B68" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">5. Organisational / Personnel Change</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="269" t="inlineStr">
+      <c r="A69" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">6. Temporary Change</t>
         </is>
       </c>
-      <c r="B69" s="269" t="inlineStr">
+      <c r="B69" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">6. Temporary Change</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="269" t="inlineStr">
+      <c r="A70" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Regulatory / Permit-Driven Change</t>
         </is>
       </c>
-      <c r="B70" s="269" t="inlineStr">
+      <c r="B70" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Regulatory / Permit-Driven Change</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="269" t="inlineStr">
+      <c r="A71" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">8. Changes to Utility &amp; HSE Protection Systems</t>
         </is>
       </c>
-      <c r="B71" s="269" t="inlineStr">
+      <c r="B71" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">8. Changes to Utility &amp; HSE Protection Systems</t>
         </is>
@@ -64690,19 +65368,19 @@
     <row r="74">
       <c r="A74" s="61" t="inlineStr">
         <is>
-          <t xml:space="preserve">L09 - Grade Guidance by Type of Change (content of the 'Grade Guidance' read-only fields)</t>
+          <t xml:space="preserve">L09 - Change Impact Guidance by Change Type (Sam Rev2 matrix - content of the guidance read-only fields)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Type of Change</t>
+          <t xml:space="preserve">Change Type</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Minor - Local Approval (TM)</t>
+          <t xml:space="preserve">Minor - Local Approval (TM + technical specialist)</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -64717,176 +65395,176 @@
       </c>
     </row>
     <row r="76" ht="144.0" customHeight="1">
-      <c r="A76" s="269" t="inlineStr">
+      <c r="A76" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Change of Design / Equipment</t>
         </is>
       </c>
-      <c r="B76" s="269" t="inlineStr">
+      <c r="B76" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Replace for an identical one. Replacement by an identical component with the same engineering specifications, construction material, and design range. Includes relocation of equipment within the same service and operating conditions</t>
         </is>
       </c>
-      <c r="C76" s="269" t="inlineStr">
+      <c r="C76" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Replace for a similar one. Replacement by a functionally similar component; may differ in brand or model but remains within the same design range. Includes relocation to a different service or operating environment, or decommissioning of non-safety-critical equipment</t>
         </is>
       </c>
-      <c r="D76" s="269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Replace for a different one. Technologically different component, different construction material, or outside the original design range. Includes any departure from original design intent, decommissioning of safety-critical equipment, or permanent removal of equipment with associated safeguard implications</t>
+      <c r="D76" s="270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Replace for a different one. Technologically different component, different construction material, or outside the original design range. Includes any departure from original design intent, decommissioning of safety-critical equipment, or permanent removal of equipment with associated safeguard implications or calibration of equipment or negatively affecting any safety device, change is reasonably likely to generate an accident of high potential</t>
         </is>
       </c>
     </row>
     <row r="77" ht="144.0" customHeight="1">
-      <c r="A77" s="269" t="inlineStr">
+      <c r="A77" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Change of Process</t>
         </is>
       </c>
-      <c r="B77" s="269" t="inlineStr">
+      <c r="B77" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Change of environment. Process carried out in same-size equipment with same construction materials and instrumentation. Capacity change ≤ 10%. Substitution of a non-hazardous material with an equivalent; no change to process parameters</t>
         </is>
       </c>
-      <c r="C77" s="269" t="inlineStr">
+      <c r="C77" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Change of scale. Capacity change &gt; 10% in volume, weight, or flow. Substitution of a hazardous material (Risk Class ≥ 3) with an equivalent within the same risk class and quantity variation ≤ 20%. Modifications to process systems (vessels, piping, relief devices) within existing design parameters</t>
         </is>
       </c>
-      <c r="D77" s="269" t="inlineStr">
+      <c r="D77" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Change of conditions. a) New process or component; b) New hazardous materials not currently present; c) Change of any process parameter that affects system integrity, the Safe Operating Envelope, or existing safeguards; d) Modifications to process systems (vessels, piping, relief devices) outside existing design parameters or affecting safeguard integrity</t>
         </is>
       </c>
     </row>
     <row r="78" ht="86.4" customHeight="1">
-      <c r="A78" s="269" t="inlineStr">
+      <c r="A78" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Change of Procedure</t>
         </is>
       </c>
-      <c r="B78" s="269" t="inlineStr">
+      <c r="B78" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Minor update. Editorial correction or clarification of an existing procedure with no change to operational sequence, frequency, or responsibilities</t>
         </is>
       </c>
-      <c r="C78" s="269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operational modification. Change of sequence, frequency, or responsible party in a key operational, maintenance, or emergency response procedure</t>
-        </is>
-      </c>
-      <c r="D78" s="269" t="inlineStr">
+      <c r="C78" s="270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operational modification. Change of sequence, or responsible party in a key operational, maintenance, or emergency response procedure</t>
+        </is>
+      </c>
+      <c r="D78" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">New procedure or elimination of control. Creation of a procedure for a previously undefined operation, or removal of an existing safety critical control step. Includes changes to emergency response plans</t>
         </is>
       </c>
     </row>
     <row r="79" ht="86.4" customHeight="1">
-      <c r="A79" s="269" t="inlineStr">
+      <c r="A79" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Change of Control Systems / IT / SIS</t>
         </is>
       </c>
-      <c r="B79" s="269" t="inlineStr">
+      <c r="B79" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Configuration change. Minor adjustment to alarm setpoints or display parameters within approved operating ranges; no change to logic or interlocks</t>
         </is>
       </c>
-      <c r="C79" s="269" t="inlineStr">
+      <c r="C79" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Software or logic modification. Modification to control system logic, PLC/DCS programming, or alarm management system; no change to SIS/SIL functions</t>
         </is>
       </c>
-      <c r="D79" s="269" t="inlineStr">
+      <c r="D79" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Safety system modification. Any change to Safety Instrumented Systems (SIS/SIL), emergency shutdown systems, or IT/OT systems that interface with safety-critical functions; or introduction of new control system architecture</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="86.4" customHeight="1">
-      <c r="A80" s="269" t="inlineStr">
+    <row r="80" ht="115.2" customHeight="1">
+      <c r="A80" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">5. Organisational / Personnel Change</t>
         </is>
       </c>
-      <c r="B80" s="269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Minor role change. Temporary reassignment of an operator within the same competency level, with no impact on critical safety roles or staffing levels</t>
-        </is>
-      </c>
-      <c r="C80" s="269" t="inlineStr">
+      <c r="B80" s="270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minor role change. Reassignment of an operator within the same competency level, transfering of operators within the same competency level, with no impact on critical safety roles or staffing levels</t>
+        </is>
+      </c>
+      <c r="C80" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Change of area responsible. Change of supervisor, coordinator, or key contractor in an operational area; safety-critical roles remain filled by competent personnel</t>
         </is>
       </c>
-      <c r="D80" s="269" t="inlineStr">
+      <c r="D80" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Loss or change of critical competency. Team restructuring, contractor change-out, or reduction of staffing in a risk-critical area. Includes situations where inexperienced personnel assume critical decision-making roles</t>
         </is>
       </c>
     </row>
     <row r="81" ht="129.6" customHeight="1">
-      <c r="A81" s="269" t="inlineStr">
+      <c r="A81" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">6. Temporary Change</t>
         </is>
       </c>
-      <c r="B81" s="269" t="inlineStr">
+      <c r="B81" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Short duration, low risk. Fully reversible, no impact on safeguards or safety-critical systems. Includes installation of temporary equipment with no safeguard implications. Removal date defined prior to implementation</t>
         </is>
       </c>
-      <c r="C81" s="269" t="inlineStr">
+      <c r="C81" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Extended duration, moderate risk. Reversible, with defined monitoring plan, removal date, and re-approval authority. Includes temporary equipment that affects operating procedures or non-safety-critical instrumentation. Scope clearly bounded and documented</t>
         </is>
       </c>
-      <c r="D81" s="269" t="inlineStr">
+      <c r="D81" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Safeguard-affecting. Any duration if it affects safety devices, alarms, interlocks, or passive safeguards. Includes installation or removal of temporary equipment that bypasses or impairs any safeguard. Scope or duration must not be exceeded without formal review and re-approval</t>
         </is>
       </c>
     </row>
     <row r="82" ht="72.0" customHeight="1">
-      <c r="A82" s="269" t="inlineStr">
+      <c r="A82" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">7. Regulatory / Permit-Driven Change</t>
         </is>
       </c>
-      <c r="B82" s="269" t="inlineStr">
+      <c r="B82" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Administrative update. Change requires notification to a regulatory body but no amendment to existing permits or licences</t>
         </is>
       </c>
-      <c r="C82" s="269" t="inlineStr">
+      <c r="C82" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Permit amendment. Change requires amendment to one or more existing environmental or operating permits</t>
         </is>
       </c>
-      <c r="D82" s="269" t="inlineStr">
+      <c r="D82" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">New permit or consent required. Change requires a new licence, permit, or regulatory consent (e.g. Environmental Permit, HSE Reports, Hazardous Substances Consent) prior to implementation</t>
         </is>
       </c>
     </row>
     <row r="83" ht="144.0" customHeight="1">
-      <c r="A83" s="269" t="inlineStr">
+      <c r="A83" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">8. Changes to Utility &amp; HSE Protection Systems</t>
         </is>
       </c>
-      <c r="B83" s="269" t="inlineStr">
+      <c r="B83" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Minor adjustment. Modification to utility systems (steam, air, nitrogen, water) or HSE protection infrastructure (bunding, drainage, fire suppression, gas detection) within existing design parameters and with no reduction in protection standard</t>
         </is>
       </c>
-      <c r="C83" s="269" t="inlineStr">
+      <c r="C83" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Moderate modification. Change to utility systems or HSE protection infrastructure that temporarily reduces protection standard but with compensatory measures defined and in place; or change that requires review and update of inspection or maintenance schedules</t>
         </is>
       </c>
-      <c r="D83" s="269" t="inlineStr">
+      <c r="D83" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Significant modification or removal. Change that permanently reduces the standard of HSE protection (e.g. reduction in bund capacity, removal or relocation of gas detection, modification to fire suppression coverage); or change to utility systems that affects the operability of safety-critical equipment</t>
         </is>
@@ -64900,35 +65578,35 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="269" t="inlineStr">
+      <c r="A86" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Landing of a floating deck / roof (IFR landing)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="269" t="inlineStr">
+      <c r="A87" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Tank entry</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="269" t="inlineStr">
+      <c r="A88" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Any change to Safety Critical Equipment purchasing, maintenance or spares holding</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="269" t="inlineStr">
+      <c r="A89" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Safety Critical Equipment out of service / safeguard bypassed (any duration)</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="269" t="inlineStr">
+      <c r="A90" s="270" t="inlineStr">
         <is>
           <t xml:space="preserve">Over-capacity of a dry bulk terminal [TBC]</t>
         </is>

--- a/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
+++ b/docs/moc/Impala - Configuration Workbook - Management of Change v1.2 (Impala requirements DRAFT).xlsx
@@ -28352,61 +28352,6 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>99060</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>9</xdr:col>
-          <xdr:colOff>495300</xdr:colOff>
-          <xdr:row>64</xdr:row>
-          <xdr:rowOff>22860</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2049" name="Object 1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2049"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001080000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a:ln>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -28575,6 +28520,39 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18097500" cy="7077075"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3001" name="Impala MOC Workflow TO-BE" descr="MOC workflow - Impala proposal (TO-BE), MOC Proposal Rev2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18097500" cy="7077075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -37274,7 +37252,7 @@
       </c>
       <c r="J68" s="239" t="inlineStr">
         <is>
-          <t xml:space="preserve">M - Impala proposal (internal pre-design 20-Oct-2026, 'MOC Proposal.xlsx'). 6 stages instead of 7. Replacement in Kind path ON HOLD: may be re-used as the 'Simplified MOC' route [TBC]. The diagram above shows the OOTB workflow and must be redrawn by Intelex.</t>
+          <t xml:space="preserve">M - Impala proposal (internal pre-design 20-Oct-2026, 'MOC Proposal.xlsx'). 6 stages instead of 7. Replacement in Kind re-used as 'Simple Change?' (same workflow, no checklist). The diagram above has been redrawn by Impala as the TO-BE workflow (replaces the OOTB Visio); Intelex may re-draw it in Visio.</t>
         </is>
       </c>
     </row>
@@ -37984,31 +37962,6 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
   <oleObjects>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <oleObject progId="Visio.Drawing.15" shapeId="2049" r:id="rId4">
-          <objectPr defaultSize="0" autoPict="0" r:id="rId5">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>22</xdr:row>
-                <xdr:rowOff>99060</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>495300</xdr:colOff>
-                <xdr:row>64</xdr:row>
-                <xdr:rowOff>22860</xdr:rowOff>
-              </to>
-            </anchor>
-          </objectPr>
-        </oleObject>
-      </mc:Choice>
-      <mc:Fallback>
-        <oleObject progId="Visio.Drawing.15" shapeId="2049" r:id="rId4"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
         <oleObject progId="Visio.Drawing.15" shapeId="2050" r:id="rId6">
